--- a/reports/latest/nasdaq100_qqq_daily_tracker.xlsx
+++ b/reports/latest/nasdaq100_qqq_daily_tracker.xlsx
@@ -16,12 +16,12 @@
     <sheet name="运行日志" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">AI输入层!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">AI输入层!$A$1:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">FMP关键指标!$A$1:$AV$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">FMP可用性!$A$1:$D$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">价格摘要!$A$1:$O$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">分析判断层!$A$1:$C$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">宏观摘要!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">宏观摘要!$A$1:$G$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">运行日志!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="231">
   <si>
     <t>symbol</t>
   </si>
@@ -79,510 +79,591 @@
     <t>QQQ</t>
   </si>
   <si>
+    <t>alpha_vantage</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>绿色</t>
+  </si>
+  <si>
+    <t>series_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>latest_date</t>
+  </si>
+  <si>
+    <t>latest_value</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>threshold</t>
+  </si>
+  <si>
+    <t>direction</t>
+  </si>
+  <si>
+    <t>DGS10</t>
+  </si>
+  <si>
+    <t>DGS2</t>
+  </si>
+  <si>
+    <t>DGS3MO</t>
+  </si>
+  <si>
+    <t>DFF</t>
+  </si>
+  <si>
+    <t>CPIAUCSL</t>
+  </si>
+  <si>
+    <t>PCEPI</t>
+  </si>
+  <si>
+    <t>UNRATE</t>
+  </si>
+  <si>
+    <t>DGS10_LEVEL_SIGNAL</t>
+  </si>
+  <si>
+    <t>DGS10_1M_CHANGE_SIGNAL</t>
+  </si>
+  <si>
+    <t>DGS10_DGS2_SPREAD_SIGNAL</t>
+  </si>
+  <si>
+    <t>CPIAUCSL_3_CHANGE_SIGNAL</t>
+  </si>
+  <si>
+    <t>PCEPI_3_CHANGE_SIGNAL</t>
+  </si>
+  <si>
+    <t>UNRATE_3M_CHANGE_SIGNAL</t>
+  </si>
+  <si>
+    <t>美国10年期国债收益率</t>
+  </si>
+  <si>
+    <t>美国2年期国债收益率</t>
+  </si>
+  <si>
+    <t>美国3个月国债收益率</t>
+  </si>
+  <si>
+    <t>有效联邦基金利率</t>
+  </si>
+  <si>
+    <t>美国消费者价格指数</t>
+  </si>
+  <si>
+    <t>美国个人消费支出价格指数</t>
+  </si>
+  <si>
+    <t>美国失业率</t>
+  </si>
+  <si>
+    <t>美国10年期国债收益率水平</t>
+  </si>
+  <si>
+    <t>美国10年期国债收益率1月变化</t>
+  </si>
+  <si>
+    <t>2年/10年利差</t>
+  </si>
+  <si>
+    <t>CPI近3次变化</t>
+  </si>
+  <si>
+    <t>PCE近3次变化</t>
+  </si>
+  <si>
+    <t>失业率3个月变化</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>信息</t>
+  </si>
+  <si>
+    <t>黄色</t>
+  </si>
+  <si>
+    <t>原始FRED观测值，衍生信号见下方</t>
+  </si>
+  <si>
+    <t>&lt;4.25%绿色，4.25%-5%黄色，&gt;=5%红色</t>
+  </si>
+  <si>
+    <t>&lt;0.15个百分点绿色，0.15-0.30黄色，&gt;=0.30红色</t>
+  </si>
+  <si>
+    <t>正利差绿色，倒挂黄色，深度倒挂或倒挂加深红色</t>
+  </si>
+  <si>
+    <t>近3次环比变化连续上行且最新为正红色，最新上行黄色，否则绿色</t>
+  </si>
+  <si>
+    <t>&lt;0.30个百分点绿色，0.30-0.50黄色，&gt;=0.50红色</t>
+  </si>
+  <si>
+    <t>宏观原始数据</t>
+  </si>
+  <si>
+    <t>长期利率压力</t>
+  </si>
+  <si>
+    <t>长期利率上行速度</t>
+  </si>
+  <si>
+    <t>收益率曲线压力</t>
+  </si>
+  <si>
+    <t>通胀压力，最新指数=332.407</t>
+  </si>
+  <si>
+    <t>通胀压力，最新指数=130.902</t>
+  </si>
+  <si>
+    <t>就业降温速度，最新失业率=4.3</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>rows</t>
+  </si>
+  <si>
+    <t>message</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>META</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>AAPL: quote rows=1</t>
+  </si>
+  <si>
+    <t>MSFT: quote rows=1</t>
+  </si>
+  <si>
+    <t>NVDA: quote rows=1</t>
+  </si>
+  <si>
+    <t>AMZN: quote rows=1</t>
+  </si>
+  <si>
+    <t>META: quote rows=1</t>
+  </si>
+  <si>
+    <t>GOOGL: quote rows=1</t>
+  </si>
+  <si>
+    <t>402 Client Error: Payment Required for url: https://financialmodelingprep.com/stable/quote?symbol=AVGO&amp;apikey=%2A%2A%2AREDACTED%2A%2A%2A</t>
+  </si>
+  <si>
+    <t>TSLA: quote rows=1</t>
+  </si>
+  <si>
+    <t>COST: quote rows=1</t>
+  </si>
+  <si>
+    <t>AMD: quote rows=1</t>
+  </si>
+  <si>
+    <t>fiscalYear</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t>reportedCurrency</t>
+  </si>
+  <si>
+    <t>marketCap</t>
+  </si>
+  <si>
+    <t>enterpriseValue</t>
+  </si>
+  <si>
+    <t>evToSales</t>
+  </si>
+  <si>
+    <t>evToOperatingCashFlow</t>
+  </si>
+  <si>
+    <t>evToFreeCashFlow</t>
+  </si>
+  <si>
+    <t>evToEBITDA</t>
+  </si>
+  <si>
+    <t>netDebtToEBITDA</t>
+  </si>
+  <si>
+    <t>currentRatio</t>
+  </si>
+  <si>
+    <t>incomeQuality</t>
+  </si>
+  <si>
+    <t>grahamNumber</t>
+  </si>
+  <si>
+    <t>grahamNetNet</t>
+  </si>
+  <si>
+    <t>taxBurden</t>
+  </si>
+  <si>
+    <t>interestBurden</t>
+  </si>
+  <si>
+    <t>workingCapital</t>
+  </si>
+  <si>
+    <t>investedCapital</t>
+  </si>
+  <si>
+    <t>returnOnAssets</t>
+  </si>
+  <si>
+    <t>operatingReturnOnAssets</t>
+  </si>
+  <si>
+    <t>returnOnTangibleAssets</t>
+  </si>
+  <si>
+    <t>returnOnEquity</t>
+  </si>
+  <si>
+    <t>returnOnInvestedCapital</t>
+  </si>
+  <si>
+    <t>returnOnCapitalEmployed</t>
+  </si>
+  <si>
+    <t>earningsYield</t>
+  </si>
+  <si>
+    <t>freeCashFlowYield</t>
+  </si>
+  <si>
+    <t>capexToOperatingCashFlow</t>
+  </si>
+  <si>
+    <t>capexToDepreciation</t>
+  </si>
+  <si>
+    <t>capexToRevenue</t>
+  </si>
+  <si>
+    <t>salesGeneralAndAdministrativeToRevenue</t>
+  </si>
+  <si>
+    <t>researchAndDevelopementToRevenue</t>
+  </si>
+  <si>
+    <t>stockBasedCompensationToRevenue</t>
+  </si>
+  <si>
+    <t>intangiblesToTotalAssets</t>
+  </si>
+  <si>
+    <t>averageReceivables</t>
+  </si>
+  <si>
+    <t>averagePayables</t>
+  </si>
+  <si>
+    <t>averageInventory</t>
+  </si>
+  <si>
+    <t>daysOfSalesOutstanding</t>
+  </si>
+  <si>
+    <t>daysOfPayablesOutstanding</t>
+  </si>
+  <si>
+    <t>daysOfInventoryOutstanding</t>
+  </si>
+  <si>
+    <t>operatingCycle</t>
+  </si>
+  <si>
+    <t>cashConversionCycle</t>
+  </si>
+  <si>
+    <t>freeCashFlowToEquity</t>
+  </si>
+  <si>
+    <t>freeCashFlowToFirm</t>
+  </si>
+  <si>
+    <t>tangibleAssetValue</t>
+  </si>
+  <si>
+    <t>netCurrentAssetValue</t>
+  </si>
+  <si>
+    <t>2025-09-27</t>
+  </si>
+  <si>
+    <t>2024-09-28</t>
+  </si>
+  <si>
+    <t>2023-09-30</t>
+  </si>
+  <si>
+    <t>2022-09-24</t>
+  </si>
+  <si>
+    <t>2021-09-25</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>2024-06-30</t>
+  </si>
+  <si>
+    <t>2023-06-30</t>
+  </si>
+  <si>
+    <t>2022-06-30</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2026-01-25</t>
+  </si>
+  <si>
+    <t>2025-01-26</t>
+  </si>
+  <si>
+    <t>2024-01-28</t>
+  </si>
+  <si>
+    <t>2023-01-29</t>
+  </si>
+  <si>
+    <t>2022-01-30</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>FY</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>fmp</t>
+  </si>
+  <si>
+    <t>指标类别</t>
+  </si>
+  <si>
+    <t>指标名称</t>
+  </si>
+  <si>
+    <t>当前值</t>
+  </si>
+  <si>
+    <t>阈值/比较基准</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>数据日期</t>
+  </si>
+  <si>
+    <t>方向/解读</t>
+  </si>
+  <si>
+    <t>来源</t>
+  </si>
+  <si>
+    <t>价格</t>
+  </si>
+  <si>
+    <t>风险</t>
+  </si>
+  <si>
+    <t>宏观原始</t>
+  </si>
+  <si>
+    <t>宏观</t>
+  </si>
+  <si>
+    <t>基本面</t>
+  </si>
+  <si>
+    <t>QQQ 20日收益率</t>
+  </si>
+  <si>
+    <t>QQQ 60日收益率</t>
+  </si>
+  <si>
+    <t>QQQ 20日年化波动率</t>
+  </si>
+  <si>
+    <t>QQQ 当前回撤</t>
+  </si>
+  <si>
+    <t>FMP报价可用率</t>
+  </si>
+  <si>
+    <t>&gt;=0绿色，-5%到0黄色，&lt;-5%红色</t>
+  </si>
+  <si>
+    <t>&gt;=0绿色，-10%到0黄色，&lt;-10%红色</t>
+  </si>
+  <si>
+    <t>&lt;25%绿色，25%-35%黄色，&gt;35%红色</t>
+  </si>
+  <si>
+    <t>&gt;-10%绿色，-10%到-15%黄色，&lt;-15%红色</t>
+  </si>
+  <si>
+    <t>&gt;=80%绿色，50%-80%黄色，&lt;50%灰色</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>价格趋势</t>
+  </si>
+  <si>
+    <t>中期趋势</t>
+  </si>
+  <si>
+    <t>波动风险</t>
+  </si>
+  <si>
+    <t>回撤风险</t>
+  </si>
+  <si>
+    <t>基本面数据质量</t>
+  </si>
+  <si>
+    <t>FRED</t>
+  </si>
+  <si>
+    <t>FMP</t>
+  </si>
+  <si>
+    <t>项目</t>
+  </si>
+  <si>
+    <t>结果</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>综合风险状态</t>
+  </si>
+  <si>
+    <t>数据质量</t>
+  </si>
+  <si>
+    <t>是否允许强化买入</t>
+  </si>
+  <si>
+    <t>较完整</t>
+  </si>
+  <si>
+    <t>仍需仓位确认</t>
+  </si>
+  <si>
+    <t>可按计划执行，但仍需遵守仓位上限。</t>
+  </si>
+  <si>
+    <t>绿色10项，黄色1项，红色0项，灰色0项。</t>
+  </si>
+  <si>
+    <t>本项目不输出无条件买入；所有动作受仓位和风险约束。</t>
+  </si>
+  <si>
+    <t>provider</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
     <t>tiingo</t>
   </si>
   <si>
-    <t>2026-06-03</t>
-  </si>
-  <si>
-    <t>绿色</t>
-  </si>
-  <si>
-    <t>series_id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>latest_date</t>
-  </si>
-  <si>
-    <t>latest_value</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>DGS10</t>
-  </si>
-  <si>
-    <t>DGS2</t>
-  </si>
-  <si>
-    <t>DGS3MO</t>
-  </si>
-  <si>
-    <t>DFF</t>
-  </si>
-  <si>
-    <t>CPIAUCSL</t>
-  </si>
-  <si>
-    <t>PCEPI</t>
-  </si>
-  <si>
-    <t>UNRATE</t>
-  </si>
-  <si>
-    <t>美国10年期国债收益率</t>
-  </si>
-  <si>
-    <t>美国2年期国债收益率</t>
-  </si>
-  <si>
-    <t>美国3个月国债收益率</t>
-  </si>
-  <si>
-    <t>有效联邦基金利率</t>
-  </si>
-  <si>
-    <t>美国消费者价格指数</t>
-  </si>
-  <si>
-    <t>美国个人消费支出价格指数</t>
-  </si>
-  <si>
-    <t>美国失业率</t>
-  </si>
-  <si>
-    <t>2026-06-02</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>信息</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>rows</t>
-  </si>
-  <si>
-    <t>message</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>META</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>COST</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>AAPL: quote rows=1</t>
-  </si>
-  <si>
-    <t>MSFT: quote rows=1</t>
-  </si>
-  <si>
-    <t>NVDA: quote rows=1</t>
-  </si>
-  <si>
-    <t>AMZN: quote rows=1</t>
-  </si>
-  <si>
-    <t>META: quote rows=1</t>
-  </si>
-  <si>
-    <t>GOOGL: quote rows=1</t>
-  </si>
-  <si>
-    <t>402 Client Error: Payment Required for url: https://financialmodelingprep.com/stable/quote?symbol=AVGO&amp;apikey=%2A%2A%2AREDACTED%2A%2A%2A</t>
-  </si>
-  <si>
-    <t>TSLA: quote rows=1</t>
-  </si>
-  <si>
-    <t>COST: quote rows=1</t>
-  </si>
-  <si>
-    <t>AMD: quote rows=1</t>
-  </si>
-  <si>
-    <t>fiscalYear</t>
-  </si>
-  <si>
-    <t>period</t>
-  </si>
-  <si>
-    <t>reportedCurrency</t>
-  </si>
-  <si>
-    <t>marketCap</t>
-  </si>
-  <si>
-    <t>enterpriseValue</t>
-  </si>
-  <si>
-    <t>evToSales</t>
-  </si>
-  <si>
-    <t>evToOperatingCashFlow</t>
-  </si>
-  <si>
-    <t>evToFreeCashFlow</t>
-  </si>
-  <si>
-    <t>evToEBITDA</t>
-  </si>
-  <si>
-    <t>netDebtToEBITDA</t>
-  </si>
-  <si>
-    <t>currentRatio</t>
-  </si>
-  <si>
-    <t>incomeQuality</t>
-  </si>
-  <si>
-    <t>grahamNumber</t>
-  </si>
-  <si>
-    <t>grahamNetNet</t>
-  </si>
-  <si>
-    <t>taxBurden</t>
-  </si>
-  <si>
-    <t>interestBurden</t>
-  </si>
-  <si>
-    <t>workingCapital</t>
-  </si>
-  <si>
-    <t>investedCapital</t>
-  </si>
-  <si>
-    <t>returnOnAssets</t>
-  </si>
-  <si>
-    <t>operatingReturnOnAssets</t>
-  </si>
-  <si>
-    <t>returnOnTangibleAssets</t>
-  </si>
-  <si>
-    <t>returnOnEquity</t>
-  </si>
-  <si>
-    <t>returnOnInvestedCapital</t>
-  </si>
-  <si>
-    <t>returnOnCapitalEmployed</t>
-  </si>
-  <si>
-    <t>earningsYield</t>
-  </si>
-  <si>
-    <t>freeCashFlowYield</t>
-  </si>
-  <si>
-    <t>capexToOperatingCashFlow</t>
-  </si>
-  <si>
-    <t>capexToDepreciation</t>
-  </si>
-  <si>
-    <t>capexToRevenue</t>
-  </si>
-  <si>
-    <t>salesGeneralAndAdministrativeToRevenue</t>
-  </si>
-  <si>
-    <t>researchAndDevelopementToRevenue</t>
-  </si>
-  <si>
-    <t>stockBasedCompensationToRevenue</t>
-  </si>
-  <si>
-    <t>intangiblesToTotalAssets</t>
-  </si>
-  <si>
-    <t>averageReceivables</t>
-  </si>
-  <si>
-    <t>averagePayables</t>
-  </si>
-  <si>
-    <t>averageInventory</t>
-  </si>
-  <si>
-    <t>daysOfSalesOutstanding</t>
-  </si>
-  <si>
-    <t>daysOfPayablesOutstanding</t>
-  </si>
-  <si>
-    <t>daysOfInventoryOutstanding</t>
-  </si>
-  <si>
-    <t>operatingCycle</t>
-  </si>
-  <si>
-    <t>cashConversionCycle</t>
-  </si>
-  <si>
-    <t>freeCashFlowToEquity</t>
-  </si>
-  <si>
-    <t>freeCashFlowToFirm</t>
-  </si>
-  <si>
-    <t>tangibleAssetValue</t>
-  </si>
-  <si>
-    <t>netCurrentAssetValue</t>
-  </si>
-  <si>
-    <t>2025-09-27</t>
-  </si>
-  <si>
-    <t>2024-09-28</t>
-  </si>
-  <si>
-    <t>2023-09-30</t>
-  </si>
-  <si>
-    <t>2022-09-24</t>
-  </si>
-  <si>
-    <t>2021-09-25</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>2024-06-30</t>
-  </si>
-  <si>
-    <t>2023-06-30</t>
-  </si>
-  <si>
-    <t>2022-06-30</t>
-  </si>
-  <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2026-01-25</t>
-  </si>
-  <si>
-    <t>2025-01-26</t>
-  </si>
-  <si>
-    <t>2024-01-28</t>
-  </si>
-  <si>
-    <t>2023-01-29</t>
-  </si>
-  <si>
-    <t>2022-01-30</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2026</t>
-  </si>
-  <si>
-    <t>FY</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>fmp</t>
-  </si>
-  <si>
-    <t>指标类别</t>
-  </si>
-  <si>
-    <t>指标名称</t>
-  </si>
-  <si>
-    <t>当前值</t>
-  </si>
-  <si>
-    <t>阈值/比较基准</t>
-  </si>
-  <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>数据日期</t>
-  </si>
-  <si>
-    <t>方向/解读</t>
-  </si>
-  <si>
-    <t>来源</t>
-  </si>
-  <si>
-    <t>价格</t>
-  </si>
-  <si>
-    <t>风险</t>
-  </si>
-  <si>
-    <t>宏观</t>
-  </si>
-  <si>
-    <t>基本面</t>
-  </si>
-  <si>
-    <t>QQQ 20日收益率</t>
-  </si>
-  <si>
-    <t>QQQ 60日收益率</t>
-  </si>
-  <si>
-    <t>QQQ 20日年化波动率</t>
-  </si>
-  <si>
-    <t>QQQ 当前回撤</t>
-  </si>
-  <si>
-    <t>FMP报价可用率</t>
-  </si>
-  <si>
-    <t>&gt;=0绿色，-5%到0黄色，&lt;-5%红色</t>
-  </si>
-  <si>
-    <t>&gt;=0绿色，-10%到0黄色，&lt;-10%红色</t>
-  </si>
-  <si>
-    <t>&lt;25%绿色，25%-35%黄色，&gt;35%红色</t>
-  </si>
-  <si>
-    <t>&gt;-10%绿色，-10%到-15%黄色，&lt;-15%红色</t>
-  </si>
-  <si>
-    <t>用于方向判断</t>
-  </si>
-  <si>
-    <t>&gt;=80%绿色，50%-80%黄色，&lt;50%灰色</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>价格趋势</t>
-  </si>
-  <si>
-    <t>中期趋势</t>
-  </si>
-  <si>
-    <t>波动风险</t>
-  </si>
-  <si>
-    <t>回撤风险</t>
-  </si>
-  <si>
-    <t>宏观环境</t>
-  </si>
-  <si>
-    <t>基本面数据质量</t>
-  </si>
-  <si>
-    <t>FRED</t>
-  </si>
-  <si>
-    <t>FMP</t>
-  </si>
-  <si>
-    <t>项目</t>
-  </si>
-  <si>
-    <t>结果</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>综合风险状态</t>
-  </si>
-  <si>
-    <t>数据质量</t>
-  </si>
-  <si>
-    <t>是否允许强化买入</t>
-  </si>
-  <si>
-    <t>较完整</t>
-  </si>
-  <si>
-    <t>仍需仓位确认</t>
-  </si>
-  <si>
-    <t>可按计划执行，但仍需遵守仓位上限。</t>
-  </si>
-  <si>
-    <t>绿色5项，黄色0项，红色0项，灰色0项。</t>
-  </si>
-  <si>
-    <t>本项目不输出无条件买入；所有动作受仓位和风险约束。</t>
-  </si>
-  <si>
-    <t>provider</t>
-  </si>
-  <si>
-    <t>method</t>
-  </si>
-  <si>
-    <t>alpha_vantage</t>
-  </si>
-  <si>
     <t>fred</t>
   </si>
   <si>
@@ -601,7 +682,7 @@
     <t>key_metrics</t>
   </si>
   <si>
-    <t>Thank you for using Alpha Vantage! This is a premium endpoint. You may subscribe to any of the premium plans at https://www.alphavantage.co/premium/ to instantly unlock all premium endpoints</t>
+    <t>QQQ: 100 rows</t>
   </si>
   <si>
     <t>QQQ: 288 rows</t>
@@ -1087,7 +1168,7 @@
         <v>0.09184137556667316</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2260390669904588</v>
+        <v>0.2245129656443334</v>
       </c>
       <c r="G2" s="1">
         <v>0.1576653841519145</v>
@@ -1096,13 +1177,10 @@
         <v>-0.002613380508201923</v>
       </c>
       <c r="I2" s="1">
-        <v>-0.1196618032822726</v>
+        <v>-0.1183474937620417</v>
       </c>
       <c r="J2">
         <v>662.3317999999999</v>
-      </c>
-      <c r="K2">
-        <v>619.3427941110641</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>18</v>
@@ -1125,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -1133,9 +1211,10 @@
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>19</v>
       </c>
@@ -1151,128 +1230,314 @@
       <c r="E1" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D2">
         <v>4.46</v>
       </c>
       <c r="E2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D3">
         <v>4.05</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>54</v>
+      </c>
+      <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>3.77</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D5">
         <v>3.62</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>54</v>
+      </c>
+      <c r="F5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D6">
         <v>332.407</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>54</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D7">
         <v>130.902</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D8">
         <v>4.3</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9">
+        <v>4.46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10">
+        <v>0.07000000000000028</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11">
+        <v>0.4100000000000001</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12">
+        <v>0.006400377846336402</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13">
+        <v>0.003995981009502714</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:G14"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1290,18 +1555,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
@@ -1310,12 +1575,12 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
@@ -1324,12 +1589,12 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
@@ -1338,12 +1603,12 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
@@ -1352,12 +1617,12 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B6" t="b">
         <v>1</v>
@@ -1366,12 +1631,12 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
@@ -1380,12 +1645,12 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B8" t="b">
         <v>0</v>
@@ -1394,12 +1659,12 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B9" t="b">
         <v>1</v>
@@ -1408,12 +1673,12 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="B10" t="b">
         <v>1</v>
@@ -1422,12 +1687,12 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
@@ -1436,7 +1701,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1503,139 +1768,139 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="AJ1" s="2" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="AK1" s="2" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="AL1" s="2" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="AM1" s="2" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="AN1" s="2" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="AO1" s="2" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="AP1" s="2" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="AQ1" s="2" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="AR1" s="2" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AS1" s="2" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="AT1" s="2" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="AU1" s="2" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="AV1" s="2" t="s">
         <v>1</v>
@@ -1643,19 +1908,19 @@
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E2" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F2">
         <v>3818743810000</v>
@@ -1784,24 +2049,24 @@
         <v>-137551000000</v>
       </c>
       <c r="AV2" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E3" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F3">
         <v>3495160329570</v>
@@ -1930,24 +2195,24 @@
         <v>-155043000000</v>
       </c>
       <c r="AV3" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E4" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F4">
         <v>2695569789510</v>
@@ -2076,24 +2341,24 @@
         <v>-146871000000</v>
       </c>
       <c r="AV4" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F5">
         <v>2439367314090</v>
@@ -2222,24 +2487,24 @@
         <v>-166678000000</v>
       </c>
       <c r="AV5" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E6" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F6">
         <v>2453750882240</v>
@@ -2368,24 +2633,24 @@
         <v>-153076000000</v>
       </c>
       <c r="AV6" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E7" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F7">
         <v>3697248530000</v>
@@ -2514,24 +2779,24 @@
         <v>-84393000000</v>
       </c>
       <c r="AV7" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E8" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F8">
         <v>3393960630000</v>
@@ -2660,24 +2925,24 @@
         <v>-83952000000</v>
       </c>
       <c r="AV8" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F9">
         <v>2535660840000</v>
@@ -2806,24 +3071,24 @@
         <v>-21496000000</v>
       </c>
       <c r="AV9" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E10" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F10">
         <v>1925197680000</v>
@@ -2952,24 +3217,24 @@
         <v>-28614000000</v>
       </c>
       <c r="AV10" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E11" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F11">
         <v>2044482300000</v>
@@ -3098,24 +3363,24 @@
         <v>-7385000000</v>
       </c>
       <c r="AV11" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E12" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F12">
         <v>4542222730000</v>
@@ -3244,24 +3509,24 @@
         <v>76095000000</v>
       </c>
       <c r="AV12" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E13" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F13">
         <v>2907803100000</v>
@@ -3390,24 +3655,24 @@
         <v>47852000000</v>
       </c>
       <c r="AV13" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E14" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F14">
         <v>1542384300000</v>
@@ -3536,24 +3801,24 @@
         <v>21595000000</v>
       </c>
       <c r="AV14" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="C15" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F15">
         <v>476509200000</v>
@@ -3682,24 +3947,24 @@
         <v>3992000000</v>
       </c>
       <c r="AV15" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F16">
         <v>611270400000</v>
@@ -3828,24 +4093,24 @@
         <v>11254000000</v>
       </c>
       <c r="AV16" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:48">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F17">
         <v>2459617920000</v>
@@ -3974,24 +4239,24 @@
         <v>-177894000000</v>
       </c>
       <c r="AV17" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:48">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="C18" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F18">
         <v>2297671470000</v>
@@ -4120,24 +4385,24 @@
         <v>-148057000000</v>
       </c>
       <c r="AV18" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:48">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E19" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F19">
         <v>1565589760000</v>
@@ -4266,24 +4531,24 @@
         <v>-153628000000</v>
       </c>
       <c r="AV19" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:48">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E20" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F20">
         <v>855876000000</v>
@@ -4409,24 +4674,24 @@
         <v>-169841000000</v>
       </c>
       <c r="AV20" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:48">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E21" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F21">
         <v>1687206400000</v>
@@ -4555,24 +4820,24 @@
         <v>-120724000000</v>
       </c>
       <c r="AV21" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:48">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E22" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F22">
         <v>1664086890000</v>
@@ -4701,24 +4966,24 @@
         <v>-40056000000</v>
       </c>
       <c r="AV22" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:48">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E23" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F23">
         <v>1483682340000</v>
@@ -4847,24 +5112,24 @@
         <v>6628000000</v>
       </c>
       <c r="AV23" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:48">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E24" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F24">
         <v>911093040000</v>
@@ -4993,24 +5258,24 @@
         <v>8910000000</v>
       </c>
       <c r="AV24" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:48">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E25" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F25">
         <v>323353580000</v>
@@ -5139,24 +5404,24 @@
         <v>-465000000</v>
       </c>
       <c r="AV25" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:48">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E26" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F26">
         <v>946825250000.0001</v>
@@ -5285,7 +5550,7 @@
         <v>25558000000</v>
       </c>
       <c r="AV26" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -5296,7 +5561,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="12.7109375" customWidth="1"/>
@@ -5304,42 +5569,42 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="C2">
         <v>0.09184137556667316</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -5348,7 +5613,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
@@ -5356,16 +5621,16 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="C3">
-        <v>0.2260390669904588</v>
+        <v>0.2245129656443334</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
@@ -5374,7 +5639,7 @@
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
@@ -5382,16 +5647,16 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="C4">
         <v>0.1576653841519145</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
@@ -5400,7 +5665,7 @@
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -5408,16 +5673,16 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="C5">
         <v>-0.002613380508201923</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="E5" t="s">
         <v>18</v>
@@ -5426,7 +5691,7 @@
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
@@ -5434,214 +5699,370 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C6">
         <v>4.46</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H6" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C7">
         <v>4.05</v>
       </c>
       <c r="D7" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H7" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C8">
         <v>3.77</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G8" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H8" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C9">
         <v>3.62</v>
       </c>
       <c r="D9" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H9" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C10">
         <v>332.407</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C11">
         <v>130.902</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G11" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H11" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C12">
         <v>4.3</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G12" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H12" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="B13" t="s">
-        <v>154</v>
+        <v>46</v>
       </c>
       <c r="C13">
+        <v>4.46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>177</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14">
+        <v>0.07000000000000028</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>177</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15">
+        <v>0.4100000000000001</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16">
+        <v>0.006400377846336402</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>177</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17">
+        <v>0.003995981009502714</v>
+      </c>
+      <c r="D17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" t="s">
+        <v>68</v>
+      </c>
+      <c r="H18" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C19">
         <v>0.9</v>
       </c>
-      <c r="D13" t="s">
-        <v>160</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D19" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" t="s">
         <v>18</v>
       </c>
-      <c r="F13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G13" t="s">
-        <v>167</v>
-      </c>
-      <c r="H13" t="s">
-        <v>169</v>
+      <c r="F19" t="s">
+        <v>189</v>
+      </c>
+      <c r="G19" t="s">
+        <v>194</v>
+      </c>
+      <c r="H19" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5656,46 +6077,46 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="B3" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="B4" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="C4" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -5714,44 +6135,44 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>183</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>210</v>
       </c>
       <c r="B3" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -5760,381 +6181,381 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B6" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B11" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B18" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B19" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B20" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B21" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B22" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B23" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B25" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/nasdaq100_qqq_daily_tracker.xlsx
+++ b/reports/latest/nasdaq100_qqq_daily_tracker.xlsx
@@ -22,7 +22,7 @@
     <sheet name="运行日志" sheetId="13" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">API调用!$A$1:$O$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">API调用!$A$1:$O$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">FMP可用性!$A$1:$D$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">QQQ持仓!$A$1:$H$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">QQQ股票池!$A$1:$H$99</definedName>
@@ -32,8 +32,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">宏观原始!$A$1:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">宏观指标!$A$1:$E$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">市场广度!$A$1:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">数据质量!$A$1:$O$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">模型输入指标!$A$1:$F$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">数据质量!$A$1:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">模型输入指标!$A$1:$F$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">运行日志!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2490" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="549">
   <si>
     <t>date</t>
   </si>
@@ -70,9 +70,6 @@
     <t>source</t>
   </si>
   <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
     <t>2026-01-13</t>
   </si>
   <si>
@@ -370,6 +367,9 @@
     <t>2026-06-04</t>
   </si>
   <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
     <t>QQQ</t>
   </si>
   <si>
@@ -1273,6 +1273,9 @@
     <t>quote_time</t>
   </si>
   <si>
+    <t>twelve_data</t>
+  </si>
+  <si>
     <t>dataset</t>
   </si>
   <si>
@@ -1330,6 +1333,9 @@
     <t>fmp_summary</t>
   </si>
   <si>
+    <t>top_holdings_quotes</t>
+  </si>
+  <si>
     <t>breadth_metrics</t>
   </si>
   <si>
@@ -1342,19 +1348,22 @@
     <t>fmp</t>
   </si>
   <si>
+    <t>fmp+twelve_data</t>
+  </si>
+  <si>
     <t>ARM,ASML,NQM6,NQM6_,PDD,USD</t>
   </si>
   <si>
     <t>NVDA,AAPL,MSFT,MU,AMZN,AMD,GOOGL,TSLA,GOOG,AVGO,META,WMT,INTC,CSCO,COST,LRCX,AMAT,NFLX,PLTR,KLAC,TXN,MRVL,QCOM,SNDK,LIN,PANW,ADI,STX,TMUS,WDC,PEP,AMGN,CRWD,APP,GILD,ISRG,SHOP,HON,BKNG,CDNS,VRTX,FTNT,SBUX,ADBE,MAR,CEG,SNPS,ADP,MNST,CSX,CMCSA,INTU,MELI,NXPI,MPWR,DDOG,MDLZ,ROST,ORLY,CTAS,AEP,LITE,WBD,DASH,BKR,REGN,PCAR,FANG,ABNB,FAST,MCHP,ODFL,EA,ADSK,XEL,FER,EXC,IDXX,CCEP,AXON,KDP,MSTR,ALNY,TTWO,PYPL,TRI,PAYX,ROP,WDAY,CPRT,GEHC,DXCM,KHC,CTSH,VRSK,INSM,ZS,CHTR</t>
   </si>
   <si>
-    <t>AAPL,ADI,ALNY,AMAT,AMD,AMZN,AVGO,AXON,CCEP,CHTR,COST,CPRT,CSCO,CTSH,DXCM,GEHC,GOOG,GOOGL,IDXX,INSM,INTC,KDP,KHC,KLAC,LIN,LRCX,META,MRVL,MSFT,MSTR,MU,NFLX,PANW,PAYX,PLTR,PYPL,QCOM,ROP,SNDK,STX,TRI,TSLA,TTWO,TXN,VRSK,WDAY,WMT,ZS</t>
-  </si>
-  <si>
-    <t>AAPL,MSFT,MU,AMZN,AMD,GOOGL,TSLA,GOOG,AVGO,META</t>
-  </si>
-  <si>
-    <t>tiingo_history_only</t>
+    <t>ADI,ALNY,AMAT,AMD,AMZN,AVGO,AXON,CCEP,CHTR,COST,CPRT,CSCO,CTSH,DXCM,GEHC,GOOG,GOOGL,IDXX,INSM,INTC,KDP,KHC,KLAC,LIN,LRCX,META,MRVL,MSTR,NFLX,PANW,PAYX,PLTR,PYPL,QCOM,ROP,SNDK,STX,TRI,TSLA,TTWO,TXN,VRSK,WDAY,WMT,ZS</t>
+  </si>
+  <si>
+    <t>AMZN,AMD,GOOGL,TSLA,GOOG,AVGO,META,WMT,INTC,CSCO</t>
+  </si>
+  <si>
+    <t>mixed_fmp+tiingo_history_only</t>
   </si>
   <si>
     <t>QQQ: 100 rows</t>
@@ -1390,7 +1399,10 @@
     <t>0/98 quotes fetched</t>
   </si>
   <si>
-    <t>50/98 symbols with history+quote coverage; coverage insufficient for top-weight symbols</t>
+    <t>20/20 top20 quotes available; 10/10 top10 quotes available</t>
+  </si>
+  <si>
+    <t>53/98 symbols with history+quote coverage; coverage insufficient for top-weight symbols</t>
   </si>
   <si>
     <t>run_date</t>
@@ -1441,6 +1453,9 @@
     <t>batch_quote</t>
   </si>
   <si>
+    <t>quote_fallback</t>
+  </si>
+  <si>
     <t>not_called</t>
   </si>
   <si>
@@ -1450,6 +1465,9 @@
     <t>run</t>
   </si>
   <si>
+    <t>minute</t>
+  </si>
+  <si>
     <t>hour</t>
   </si>
   <si>
@@ -1459,13 +1477,19 @@
     <t>98 symbols</t>
   </si>
   <si>
+    <t>NVDA,AAPL,MSFT,MU,AMZN,AMD,GOOGL,TSLA,GOOG,AVGO,META,WMT,INTC,CSCO,COST,LRCX,AMAT,NFLX,PLTR,KLAC</t>
+  </si>
+  <si>
     <t>DGS10: DGS10: 365 rows; DGS2: DGS2: 365 rows; DGS3MO: DGS3MO: 365 rows; ...</t>
   </si>
   <si>
     <t>holdings rows=104</t>
   </si>
   <si>
-    <t>429 Client Error: Too Many Requests for url: https://financialmodelingprep.com/stable/quote?symbol=NVDA%2CAAPL%2CMSFT%2CMU%2CAMZN%2CAMD%2CGOOGL%2CTSLA%2CGOOG%2CAVGO%2CMETA%2CWMT%2CINTC%2CCSCO%2CCOST%2CLRCX%2CAMAT%2CNFLX%2CPLTR%2CKLAC%2CTXN%2CMRVL%2CQCOM%2CSNDK%2CLIN&amp;apikey=%2A%2A%2AREDACTED%2A%2A%2A</t>
+    <t>402 Client Error: Payment Required for url: https://financialmodelingprep.com/stable/quote?symbol=NVDA%2CAAPL%2CMSFT%2CMU%2CAMZN%2CAMD%2CGOOGL%2CTSLA%2CGOOG%2CAVGO%2CMETA%2CWMT%2CINTC%2CCSCO%2CCOST%2CLRCX%2CAMAT%2CNFLX%2CPLTR%2CKLAC%2CTXN%2CMRVL%2CQCOM%2CSNDK%2CLIN&amp;apikey=%2A%2A%2AREDACTED%2A%2A%2A</t>
+  </si>
+  <si>
+    <t>NVDA: quote loaded; AAPL: quote loaded; MSFT: quote loaded; MU: quote loaded; AMZN: quote loaded; ...</t>
   </si>
   <si>
     <t>provider not called in this daily pipeline run</t>
@@ -1561,6 +1585,15 @@
     <t>fmp_summary_fmp_rate_limited</t>
   </si>
   <si>
+    <t>top_holdings_quotes_fmp+twelve_data_symbol_coverage_ratio</t>
+  </si>
+  <si>
+    <t>top_holdings_quotes_fmp+twelve_data_weight_coverage_ratio</t>
+  </si>
+  <si>
+    <t>top_holdings_quotes_fmp+twelve_data_rate_limited</t>
+  </si>
+  <si>
     <t>breadth_metrics_fmp+tiingo_cache_symbol_coverage_ratio</t>
   </si>
   <si>
@@ -1600,7 +1633,7 @@
     <t>successful quote responses / requested symbols</t>
   </si>
   <si>
-    <t>breadth metric; denominator=50</t>
+    <t>breadth metric; denominator=53</t>
   </si>
   <si>
     <t>data quality symbol coverage; ok=True; rows=100</t>
@@ -1624,16 +1657,16 @@
     <t>data quality symbol coverage; ok=False; rows=98</t>
   </si>
   <si>
-    <t>data quality weight coverage; rate_limited=True; fallback_provider=</t>
-  </si>
-  <si>
-    <t>1 means provider hit 429 and breadth stopped_after_429=True</t>
+    <t>data quality symbol coverage; ok=True; rows=20</t>
+  </si>
+  <si>
+    <t>data quality weight coverage; rate_limited=False; fallback_provider=twelve_data</t>
   </si>
   <si>
     <t>data quality symbol coverage; ok=True; rows=8</t>
   </si>
   <si>
-    <t>data quality weight coverage; rate_limited=False; fallback_provider=tiingo_history_only</t>
+    <t>data quality weight coverage; rate_limited=False; fallback_provider=mixed_fmp+tiingo_history_only</t>
   </si>
   <si>
     <t>FMP</t>
@@ -1654,7 +1687,7 @@
     <t>load_cached_history_for_breadth</t>
   </si>
   <si>
-    <t>50/98 symbols loaded from local cache/raw seed</t>
+    <t>53/98 symbols loaded from local cache/raw seed</t>
   </si>
 </sst>
 </file>
@@ -2068,22 +2101,22 @@
         <v>109</v>
       </c>
       <c r="C2">
-        <v>622.3099999999999</v>
+        <v>627.27</v>
       </c>
       <c r="D2">
-        <v>628.845</v>
+        <v>629.47</v>
       </c>
       <c r="E2">
-        <v>622.26</v>
+        <v>623.6950000000001</v>
       </c>
       <c r="F2">
-        <v>627.17</v>
+        <v>626.24</v>
       </c>
       <c r="G2">
-        <v>627.17</v>
+        <v>626.24</v>
       </c>
       <c r="H2" s="1">
-        <v>37388651</v>
+        <v>44481380</v>
       </c>
       <c r="I2" t="s">
         <v>110</v>
@@ -2097,22 +2130,22 @@
         <v>109</v>
       </c>
       <c r="C3">
-        <v>627.27</v>
+        <v>622.24</v>
       </c>
       <c r="D3">
-        <v>629.47</v>
+        <v>623.45</v>
       </c>
       <c r="E3">
-        <v>623.6950000000001</v>
+        <v>614.5599999999999</v>
       </c>
       <c r="F3">
-        <v>626.24</v>
+        <v>619.55</v>
       </c>
       <c r="G3">
-        <v>626.24</v>
+        <v>619.55</v>
       </c>
       <c r="H3" s="1">
-        <v>44481380</v>
+        <v>72598700</v>
       </c>
       <c r="I3" t="s">
         <v>110</v>
@@ -2126,22 +2159,22 @@
         <v>109</v>
       </c>
       <c r="C4">
-        <v>622.24</v>
+        <v>626.6</v>
       </c>
       <c r="D4">
-        <v>623.45</v>
+        <v>630</v>
       </c>
       <c r="E4">
-        <v>614.5599999999999</v>
+        <v>620.75</v>
       </c>
       <c r="F4">
-        <v>619.55</v>
+        <v>621.78</v>
       </c>
       <c r="G4">
-        <v>619.55</v>
+        <v>621.78</v>
       </c>
       <c r="H4" s="1">
-        <v>72598700</v>
+        <v>53934892</v>
       </c>
       <c r="I4" t="s">
         <v>110</v>
@@ -2155,22 +2188,22 @@
         <v>109</v>
       </c>
       <c r="C5">
-        <v>626.6</v>
+        <v>625.5</v>
       </c>
       <c r="D5">
-        <v>630</v>
+        <v>626.08</v>
       </c>
       <c r="E5">
-        <v>620.75</v>
+        <v>618.88</v>
       </c>
       <c r="F5">
-        <v>621.78</v>
+        <v>621.26</v>
       </c>
       <c r="G5">
-        <v>621.78</v>
+        <v>621.26</v>
       </c>
       <c r="H5" s="1">
-        <v>53934892</v>
+        <v>61058094</v>
       </c>
       <c r="I5" t="s">
         <v>110</v>
@@ -2184,22 +2217,22 @@
         <v>109</v>
       </c>
       <c r="C6">
-        <v>625.5</v>
+        <v>610.53</v>
       </c>
       <c r="D6">
-        <v>626.08</v>
+        <v>615.0549999999999</v>
       </c>
       <c r="E6">
-        <v>618.88</v>
+        <v>607.05</v>
       </c>
       <c r="F6">
-        <v>621.26</v>
+        <v>608.0599999999999</v>
       </c>
       <c r="G6">
-        <v>621.26</v>
+        <v>608.0599999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>61058094</v>
+        <v>80764676</v>
       </c>
       <c r="I6" t="s">
         <v>110</v>
@@ -2213,22 +2246,22 @@
         <v>109</v>
       </c>
       <c r="C7">
-        <v>610.53</v>
+        <v>609.47</v>
       </c>
       <c r="D7">
-        <v>615.0549999999999</v>
+        <v>620.42</v>
       </c>
       <c r="E7">
-        <v>607.05</v>
+        <v>607.8635</v>
       </c>
       <c r="F7">
-        <v>608.0599999999999</v>
+        <v>616.28</v>
       </c>
       <c r="G7">
-        <v>608.0599999999999</v>
+        <v>616.28</v>
       </c>
       <c r="H7" s="1">
-        <v>80764676</v>
+        <v>79837881</v>
       </c>
       <c r="I7" t="s">
         <v>110</v>
@@ -2242,22 +2275,22 @@
         <v>109</v>
       </c>
       <c r="C8">
-        <v>609.47</v>
+        <v>622.35</v>
       </c>
       <c r="D8">
-        <v>620.42</v>
+        <v>622.46</v>
       </c>
       <c r="E8">
-        <v>607.8635</v>
+        <v>617.78</v>
       </c>
       <c r="F8">
-        <v>616.28</v>
+        <v>620.76</v>
       </c>
       <c r="G8">
-        <v>616.28</v>
+        <v>620.76</v>
       </c>
       <c r="H8" s="1">
-        <v>79837881</v>
+        <v>42254757</v>
       </c>
       <c r="I8" t="s">
         <v>110</v>
@@ -2271,22 +2304,22 @@
         <v>109</v>
       </c>
       <c r="C9">
-        <v>622.35</v>
+        <v>619.73</v>
       </c>
       <c r="D9">
-        <v>622.46</v>
+        <v>625.3999</v>
       </c>
       <c r="E9">
-        <v>617.78</v>
+        <v>618.65</v>
       </c>
       <c r="F9">
-        <v>620.76</v>
+        <v>622.72</v>
       </c>
       <c r="G9">
-        <v>620.76</v>
+        <v>622.72</v>
       </c>
       <c r="H9" s="1">
-        <v>42254757</v>
+        <v>43645825</v>
       </c>
       <c r="I9" t="s">
         <v>110</v>
@@ -2300,22 +2333,22 @@
         <v>109</v>
       </c>
       <c r="C10">
-        <v>619.73</v>
+        <v>623.21</v>
       </c>
       <c r="D10">
-        <v>625.3999</v>
+        <v>627.61</v>
       </c>
       <c r="E10">
-        <v>618.65</v>
+        <v>622.12</v>
       </c>
       <c r="F10">
-        <v>622.72</v>
+        <v>625.46</v>
       </c>
       <c r="G10">
-        <v>622.72</v>
+        <v>625.46</v>
       </c>
       <c r="H10" s="1">
-        <v>43645825</v>
+        <v>35983008</v>
       </c>
       <c r="I10" t="s">
         <v>110</v>
@@ -2329,22 +2362,22 @@
         <v>109</v>
       </c>
       <c r="C11">
-        <v>623.21</v>
+        <v>628.91</v>
       </c>
       <c r="D11">
-        <v>627.61</v>
+        <v>632.0427</v>
       </c>
       <c r="E11">
-        <v>622.12</v>
+        <v>627.34</v>
       </c>
       <c r="F11">
-        <v>625.46</v>
+        <v>631.13</v>
       </c>
       <c r="G11">
-        <v>625.46</v>
+        <v>631.13</v>
       </c>
       <c r="H11" s="1">
-        <v>35983008</v>
+        <v>38344052</v>
       </c>
       <c r="I11" t="s">
         <v>110</v>
@@ -2358,22 +2391,22 @@
         <v>109</v>
       </c>
       <c r="C12">
-        <v>628.91</v>
+        <v>635.46</v>
       </c>
       <c r="D12">
-        <v>632.0427</v>
+        <v>636.6</v>
       </c>
       <c r="E12">
-        <v>627.34</v>
+        <v>631.8099999999999</v>
       </c>
       <c r="F12">
-        <v>631.13</v>
+        <v>633.22</v>
       </c>
       <c r="G12">
-        <v>631.13</v>
+        <v>633.22</v>
       </c>
       <c r="H12" s="1">
-        <v>38344052</v>
+        <v>50691691</v>
       </c>
       <c r="I12" t="s">
         <v>110</v>
@@ -2387,22 +2420,22 @@
         <v>109</v>
       </c>
       <c r="C13">
-        <v>635.46</v>
+        <v>632.65</v>
       </c>
       <c r="D13">
-        <v>636.6</v>
+        <v>633.67</v>
       </c>
       <c r="E13">
-        <v>631.8099999999999</v>
+        <v>618.27</v>
       </c>
       <c r="F13">
-        <v>633.22</v>
+        <v>629.4299999999999</v>
       </c>
       <c r="G13">
-        <v>633.22</v>
+        <v>629.4299999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>50691691</v>
+        <v>79944047</v>
       </c>
       <c r="I13" t="s">
         <v>110</v>
@@ -2416,22 +2449,22 @@
         <v>109</v>
       </c>
       <c r="C14">
-        <v>632.65</v>
+        <v>625.71</v>
       </c>
       <c r="D14">
-        <v>633.67</v>
+        <v>628.256</v>
       </c>
       <c r="E14">
-        <v>618.27</v>
+        <v>619.2975</v>
       </c>
       <c r="F14">
-        <v>629.4299999999999</v>
+        <v>621.87</v>
       </c>
       <c r="G14">
-        <v>629.4299999999999</v>
+        <v>621.87</v>
       </c>
       <c r="H14" s="1">
-        <v>79944047</v>
+        <v>65650714</v>
       </c>
       <c r="I14" t="s">
         <v>110</v>
@@ -2445,22 +2478,22 @@
         <v>109</v>
       </c>
       <c r="C15">
-        <v>625.71</v>
+        <v>618.7</v>
       </c>
       <c r="D15">
-        <v>628.256</v>
+        <v>628.49</v>
       </c>
       <c r="E15">
-        <v>619.2975</v>
+        <v>618.66</v>
       </c>
       <c r="F15">
-        <v>621.87</v>
+        <v>626.14</v>
       </c>
       <c r="G15">
-        <v>621.87</v>
+        <v>626.14</v>
       </c>
       <c r="H15" s="1">
-        <v>65650714</v>
+        <v>49020292</v>
       </c>
       <c r="I15" t="s">
         <v>110</v>
@@ -2474,22 +2507,22 @@
         <v>109</v>
       </c>
       <c r="C16">
-        <v>618.7</v>
+        <v>628.3</v>
       </c>
       <c r="D16">
-        <v>628.49</v>
+        <v>629.98</v>
       </c>
       <c r="E16">
-        <v>618.66</v>
+        <v>610.96</v>
       </c>
       <c r="F16">
-        <v>626.14</v>
+        <v>616.52</v>
       </c>
       <c r="G16">
-        <v>626.14</v>
+        <v>616.52</v>
       </c>
       <c r="H16" s="1">
-        <v>49020292</v>
+        <v>80522875</v>
       </c>
       <c r="I16" t="s">
         <v>110</v>
@@ -2503,22 +2536,22 @@
         <v>109</v>
       </c>
       <c r="C17">
-        <v>628.3</v>
+        <v>615.02</v>
       </c>
       <c r="D17">
-        <v>629.98</v>
+        <v>615.1</v>
       </c>
       <c r="E17">
-        <v>610.96</v>
+        <v>600.47</v>
       </c>
       <c r="F17">
-        <v>616.52</v>
+        <v>605.75</v>
       </c>
       <c r="G17">
-        <v>616.52</v>
+        <v>605.75</v>
       </c>
       <c r="H17" s="1">
-        <v>80522875</v>
+        <v>81850748</v>
       </c>
       <c r="I17" t="s">
         <v>110</v>
@@ -2532,22 +2565,22 @@
         <v>109</v>
       </c>
       <c r="C18">
-        <v>615.02</v>
+        <v>600.21</v>
       </c>
       <c r="D18">
-        <v>615.1</v>
+        <v>604.8099999999999</v>
       </c>
       <c r="E18">
-        <v>600.47</v>
+        <v>594.76</v>
       </c>
       <c r="F18">
-        <v>605.75</v>
+        <v>597.03</v>
       </c>
       <c r="G18">
-        <v>605.75</v>
+        <v>597.03</v>
       </c>
       <c r="H18" s="1">
-        <v>81850748</v>
+        <v>89354492</v>
       </c>
       <c r="I18" t="s">
         <v>110</v>
@@ -2561,22 +2594,22 @@
         <v>109</v>
       </c>
       <c r="C19">
-        <v>600.21</v>
+        <v>600.1900000000001</v>
       </c>
       <c r="D19">
-        <v>604.8099999999999</v>
+        <v>611.41</v>
       </c>
       <c r="E19">
-        <v>594.76</v>
+        <v>598.77</v>
       </c>
       <c r="F19">
-        <v>597.03</v>
+        <v>609.65</v>
       </c>
       <c r="G19">
-        <v>597.03</v>
+        <v>609.65</v>
       </c>
       <c r="H19" s="1">
-        <v>89354492</v>
+        <v>78019338</v>
       </c>
       <c r="I19" t="s">
         <v>110</v>
@@ -2590,22 +2623,22 @@
         <v>109</v>
       </c>
       <c r="C20">
-        <v>600.1900000000001</v>
+        <v>607.54</v>
       </c>
       <c r="D20">
-        <v>611.41</v>
+        <v>616.46</v>
       </c>
       <c r="E20">
-        <v>598.77</v>
+        <v>605.0700000000001</v>
       </c>
       <c r="F20">
-        <v>609.65</v>
+        <v>614.3200000000001</v>
       </c>
       <c r="G20">
-        <v>609.65</v>
+        <v>614.3200000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>78019338</v>
+        <v>56797557</v>
       </c>
       <c r="I20" t="s">
         <v>110</v>
@@ -2619,22 +2652,22 @@
         <v>109</v>
       </c>
       <c r="C21">
-        <v>607.54</v>
+        <v>615.3049999999999</v>
       </c>
       <c r="D21">
-        <v>616.46</v>
+        <v>617.02</v>
       </c>
       <c r="E21">
-        <v>605.0700000000001</v>
+        <v>611.01</v>
       </c>
       <c r="F21">
-        <v>614.3200000000001</v>
+        <v>611.47</v>
       </c>
       <c r="G21">
-        <v>614.3200000000001</v>
+        <v>611.47</v>
       </c>
       <c r="H21" s="1">
-        <v>56797557</v>
+        <v>53938859</v>
       </c>
       <c r="I21" t="s">
         <v>110</v>
@@ -2648,22 +2681,22 @@
         <v>109</v>
       </c>
       <c r="C22">
-        <v>615.3049999999999</v>
+        <v>616.38</v>
       </c>
       <c r="D22">
-        <v>617.02</v>
+        <v>617.52</v>
       </c>
       <c r="E22">
-        <v>611.01</v>
+        <v>607.6900000000001</v>
       </c>
       <c r="F22">
-        <v>611.47</v>
+        <v>613.11</v>
       </c>
       <c r="G22">
-        <v>611.47</v>
+        <v>613.11</v>
       </c>
       <c r="H22" s="1">
-        <v>53938859</v>
+        <v>58575101</v>
       </c>
       <c r="I22" t="s">
         <v>110</v>
@@ -2677,22 +2710,22 @@
         <v>109</v>
       </c>
       <c r="C23">
-        <v>616.38</v>
+        <v>614.71</v>
       </c>
       <c r="D23">
-        <v>617.52</v>
+        <v>615.8099999999999</v>
       </c>
       <c r="E23">
-        <v>607.6900000000001</v>
+        <v>599.5700000000001</v>
       </c>
       <c r="F23">
-        <v>613.11</v>
+        <v>600.64</v>
       </c>
       <c r="G23">
-        <v>613.11</v>
+        <v>600.64</v>
       </c>
       <c r="H23" s="1">
-        <v>58575101</v>
+        <v>81378903</v>
       </c>
       <c r="I23" t="s">
         <v>110</v>
@@ -2706,22 +2739,22 @@
         <v>109</v>
       </c>
       <c r="C24">
-        <v>614.71</v>
+        <v>600.4299999999999</v>
       </c>
       <c r="D24">
-        <v>615.8099999999999</v>
+        <v>606.48</v>
       </c>
       <c r="E24">
-        <v>599.5700000000001</v>
+        <v>596.42</v>
       </c>
       <c r="F24">
-        <v>600.64</v>
+        <v>601.92</v>
       </c>
       <c r="G24">
-        <v>600.64</v>
+        <v>601.92</v>
       </c>
       <c r="H24" s="1">
-        <v>81378903</v>
+        <v>69237547</v>
       </c>
       <c r="I24" t="s">
         <v>110</v>
@@ -2735,22 +2768,22 @@
         <v>109</v>
       </c>
       <c r="C25">
-        <v>600.4299999999999</v>
+        <v>598.375</v>
       </c>
       <c r="D25">
-        <v>606.48</v>
+        <v>603.95</v>
       </c>
       <c r="E25">
-        <v>596.42</v>
+        <v>593.34</v>
       </c>
       <c r="F25">
-        <v>601.92</v>
+        <v>601.3</v>
       </c>
       <c r="G25">
-        <v>601.92</v>
+        <v>601.3</v>
       </c>
       <c r="H25" s="1">
-        <v>69237547</v>
+        <v>69013763</v>
       </c>
       <c r="I25" t="s">
         <v>110</v>
@@ -2764,22 +2797,22 @@
         <v>109</v>
       </c>
       <c r="C26">
-        <v>598.375</v>
+        <v>602.11</v>
       </c>
       <c r="D26">
-        <v>603.95</v>
+        <v>609.771</v>
       </c>
       <c r="E26">
-        <v>593.34</v>
+        <v>600.72</v>
       </c>
       <c r="F26">
-        <v>601.3</v>
+        <v>605.79</v>
       </c>
       <c r="G26">
-        <v>601.3</v>
+        <v>605.79</v>
       </c>
       <c r="H26" s="1">
-        <v>69013763</v>
+        <v>64250668</v>
       </c>
       <c r="I26" t="s">
         <v>110</v>
@@ -2793,22 +2826,22 @@
         <v>109</v>
       </c>
       <c r="C27">
-        <v>602.11</v>
+        <v>602.8099999999999</v>
       </c>
       <c r="D27">
-        <v>609.771</v>
+        <v>605.8150000000001</v>
       </c>
       <c r="E27">
-        <v>600.72</v>
+        <v>600.75</v>
       </c>
       <c r="F27">
-        <v>605.79</v>
+        <v>603.47</v>
       </c>
       <c r="G27">
-        <v>605.79</v>
+        <v>603.47</v>
       </c>
       <c r="H27" s="1">
-        <v>64250668</v>
+        <v>60960839</v>
       </c>
       <c r="I27" t="s">
         <v>110</v>
@@ -2822,22 +2855,22 @@
         <v>109</v>
       </c>
       <c r="C28">
-        <v>602.8099999999999</v>
+        <v>600.12</v>
       </c>
       <c r="D28">
-        <v>605.8150000000001</v>
+        <v>610.35</v>
       </c>
       <c r="E28">
-        <v>600.75</v>
+        <v>599.23</v>
       </c>
       <c r="F28">
-        <v>603.47</v>
+        <v>608.8099999999999</v>
       </c>
       <c r="G28">
-        <v>603.47</v>
+        <v>608.8099999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>60960839</v>
+        <v>74127323</v>
       </c>
       <c r="I28" t="s">
         <v>110</v>
@@ -2851,22 +2884,22 @@
         <v>109</v>
       </c>
       <c r="C29">
-        <v>600.12</v>
+        <v>606.605</v>
       </c>
       <c r="D29">
-        <v>610.35</v>
+        <v>608.01</v>
       </c>
       <c r="E29">
-        <v>599.23</v>
+        <v>599.05</v>
       </c>
       <c r="F29">
-        <v>608.8099999999999</v>
+        <v>601.41</v>
       </c>
       <c r="G29">
-        <v>608.8099999999999</v>
+        <v>601.41</v>
       </c>
       <c r="H29" s="1">
-        <v>74127323</v>
+        <v>63859111</v>
       </c>
       <c r="I29" t="s">
         <v>110</v>
@@ -2880,22 +2913,22 @@
         <v>109</v>
       </c>
       <c r="C30">
-        <v>606.605</v>
+        <v>602.4</v>
       </c>
       <c r="D30">
-        <v>608.01</v>
+        <v>608.99</v>
       </c>
       <c r="E30">
-        <v>599.05</v>
+        <v>599.73</v>
       </c>
       <c r="F30">
-        <v>601.41</v>
+        <v>607.87</v>
       </c>
       <c r="G30">
-        <v>601.41</v>
+        <v>607.87</v>
       </c>
       <c r="H30" s="1">
-        <v>63859111</v>
+        <v>55023732</v>
       </c>
       <c r="I30" t="s">
         <v>110</v>
@@ -2909,22 +2942,22 @@
         <v>109</v>
       </c>
       <c r="C31">
-        <v>602.4</v>
+        <v>611.0700000000001</v>
       </c>
       <c r="D31">
-        <v>608.99</v>
+        <v>616.83</v>
       </c>
       <c r="E31">
-        <v>599.73</v>
+        <v>611</v>
       </c>
       <c r="F31">
-        <v>607.87</v>
+        <v>616.6799999999999</v>
       </c>
       <c r="G31">
-        <v>607.87</v>
+        <v>616.6799999999999</v>
       </c>
       <c r="H31" s="1">
-        <v>55023732</v>
+        <v>55710653</v>
       </c>
       <c r="I31" t="s">
         <v>110</v>
@@ -2938,22 +2971,22 @@
         <v>109</v>
       </c>
       <c r="C32">
-        <v>611.0700000000001</v>
+        <v>615.59</v>
       </c>
       <c r="D32">
-        <v>616.83</v>
+        <v>615.59</v>
       </c>
       <c r="E32">
-        <v>611</v>
+        <v>603.98</v>
       </c>
       <c r="F32">
-        <v>616.6799999999999</v>
+        <v>609.24</v>
       </c>
       <c r="G32">
-        <v>616.6799999999999</v>
+        <v>609.24</v>
       </c>
       <c r="H32" s="1">
-        <v>55710653</v>
+        <v>96178870</v>
       </c>
       <c r="I32" t="s">
         <v>110</v>
@@ -2967,22 +3000,22 @@
         <v>109</v>
       </c>
       <c r="C33">
-        <v>615.59</v>
+        <v>602.98</v>
       </c>
       <c r="D33">
-        <v>615.59</v>
+        <v>608.3200000000001</v>
       </c>
       <c r="E33">
-        <v>603.98</v>
+        <v>602.1900000000001</v>
       </c>
       <c r="F33">
-        <v>609.24</v>
+        <v>607.29</v>
       </c>
       <c r="G33">
-        <v>609.24</v>
+        <v>607.29</v>
       </c>
       <c r="H33" s="1">
-        <v>96178870</v>
+        <v>68125196</v>
       </c>
       <c r="I33" t="s">
         <v>110</v>
@@ -2996,22 +3029,22 @@
         <v>109</v>
       </c>
       <c r="C34">
-        <v>602.98</v>
+        <v>598.86</v>
       </c>
       <c r="D34">
-        <v>608.3200000000001</v>
+        <v>609.92</v>
       </c>
       <c r="E34">
-        <v>602.1900000000001</v>
+        <v>597.99</v>
       </c>
       <c r="F34">
-        <v>607.29</v>
+        <v>608.09</v>
       </c>
       <c r="G34">
-        <v>607.29</v>
+        <v>608.09</v>
       </c>
       <c r="H34" s="1">
-        <v>68125196</v>
+        <v>75264644</v>
       </c>
       <c r="I34" t="s">
         <v>110</v>
@@ -3025,22 +3058,22 @@
         <v>109</v>
       </c>
       <c r="C35">
-        <v>598.86</v>
+        <v>596.33</v>
       </c>
       <c r="D35">
-        <v>609.92</v>
+        <v>603.96</v>
       </c>
       <c r="E35">
-        <v>597.99</v>
+        <v>591.87</v>
       </c>
       <c r="F35">
-        <v>608.09</v>
+        <v>601.58</v>
       </c>
       <c r="G35">
-        <v>608.09</v>
+        <v>601.58</v>
       </c>
       <c r="H35" s="1">
-        <v>75264644</v>
+        <v>97015532</v>
       </c>
       <c r="I35" t="s">
         <v>110</v>
@@ -3054,22 +3087,22 @@
         <v>109</v>
       </c>
       <c r="C36">
-        <v>596.33</v>
+        <v>604.16</v>
       </c>
       <c r="D36">
-        <v>603.96</v>
+        <v>612.88</v>
       </c>
       <c r="E36">
-        <v>591.87</v>
+        <v>603.4299999999999</v>
       </c>
       <c r="F36">
-        <v>601.58</v>
+        <v>610.75</v>
       </c>
       <c r="G36">
-        <v>601.58</v>
+        <v>610.75</v>
       </c>
       <c r="H36" s="1">
-        <v>97015532</v>
+        <v>70943888</v>
       </c>
       <c r="I36" t="s">
         <v>110</v>
@@ -3083,22 +3116,22 @@
         <v>109</v>
       </c>
       <c r="C37">
-        <v>604.16</v>
+        <v>607.4</v>
       </c>
       <c r="D37">
-        <v>612.88</v>
+        <v>612.76</v>
       </c>
       <c r="E37">
-        <v>603.4299999999999</v>
+        <v>602.26</v>
       </c>
       <c r="F37">
-        <v>610.75</v>
+        <v>608.91</v>
       </c>
       <c r="G37">
-        <v>610.75</v>
+        <v>608.91</v>
       </c>
       <c r="H37" s="1">
-        <v>70943888</v>
+        <v>89602407</v>
       </c>
       <c r="I37" t="s">
         <v>110</v>
@@ -3112,22 +3145,22 @@
         <v>109</v>
       </c>
       <c r="C38">
-        <v>607.4</v>
+        <v>600.3099999999999</v>
       </c>
       <c r="D38">
-        <v>612.76</v>
+        <v>606</v>
       </c>
       <c r="E38">
-        <v>602.26</v>
+        <v>598.33</v>
       </c>
       <c r="F38">
-        <v>608.91</v>
+        <v>599.75</v>
       </c>
       <c r="G38">
-        <v>608.91</v>
+        <v>599.75</v>
       </c>
       <c r="H38" s="1">
-        <v>89602407</v>
+        <v>86302307</v>
       </c>
       <c r="I38" t="s">
         <v>110</v>
@@ -3141,22 +3174,22 @@
         <v>109</v>
       </c>
       <c r="C39">
-        <v>600.3099999999999</v>
+        <v>594.225</v>
       </c>
       <c r="D39">
-        <v>606</v>
+        <v>609.27</v>
       </c>
       <c r="E39">
-        <v>598.33</v>
+        <v>591.33</v>
       </c>
       <c r="F39">
-        <v>599.75</v>
+        <v>607.76</v>
       </c>
       <c r="G39">
-        <v>599.75</v>
+        <v>607.76</v>
       </c>
       <c r="H39" s="1">
-        <v>86302307</v>
+        <v>93068170</v>
       </c>
       <c r="I39" t="s">
         <v>110</v>
@@ -3170,22 +3203,22 @@
         <v>109</v>
       </c>
       <c r="C40">
-        <v>594.225</v>
+        <v>607.78</v>
       </c>
       <c r="D40">
-        <v>609.27</v>
+        <v>613.29</v>
       </c>
       <c r="E40">
-        <v>591.33</v>
+        <v>605.42</v>
       </c>
       <c r="F40">
-        <v>607.76</v>
+        <v>607.77</v>
       </c>
       <c r="G40">
-        <v>607.76</v>
+        <v>607.77</v>
       </c>
       <c r="H40" s="1">
-        <v>93068170</v>
+        <v>64078867</v>
       </c>
       <c r="I40" t="s">
         <v>110</v>
@@ -3199,22 +3232,22 @@
         <v>109</v>
       </c>
       <c r="C41">
-        <v>607.78</v>
+        <v>608.95</v>
       </c>
       <c r="D41">
-        <v>613.29</v>
+        <v>612.4299999999999</v>
       </c>
       <c r="E41">
-        <v>605.42</v>
+        <v>605.03</v>
       </c>
       <c r="F41">
-        <v>607.77</v>
+        <v>607.6900000000001</v>
       </c>
       <c r="G41">
-        <v>607.77</v>
+        <v>607.6900000000001</v>
       </c>
       <c r="H41" s="1">
-        <v>64078867</v>
+        <v>60114800</v>
       </c>
       <c r="I41" t="s">
         <v>110</v>
@@ -3228,22 +3261,22 @@
         <v>109</v>
       </c>
       <c r="C42">
-        <v>608.95</v>
+        <v>602.76</v>
       </c>
       <c r="D42">
-        <v>612.4299999999999</v>
+        <v>604.14</v>
       </c>
       <c r="E42">
-        <v>605.03</v>
+        <v>597.05</v>
       </c>
       <c r="F42">
-        <v>607.6900000000001</v>
+        <v>597.26</v>
       </c>
       <c r="G42">
-        <v>607.6900000000001</v>
+        <v>597.26</v>
       </c>
       <c r="H42" s="1">
-        <v>60114800</v>
+        <v>71836629</v>
       </c>
       <c r="I42" t="s">
         <v>110</v>
@@ -3257,22 +3290,22 @@
         <v>109</v>
       </c>
       <c r="C43">
-        <v>602.76</v>
+        <v>599.73</v>
       </c>
       <c r="D43">
-        <v>604.14</v>
+        <v>603.5999</v>
       </c>
       <c r="E43">
-        <v>597.05</v>
+        <v>592.5700000000001</v>
       </c>
       <c r="F43">
-        <v>597.26</v>
+        <v>593.72</v>
       </c>
       <c r="G43">
-        <v>597.26</v>
+        <v>593.72</v>
       </c>
       <c r="H43" s="1">
-        <v>71836629</v>
+        <v>63145490</v>
       </c>
       <c r="I43" t="s">
         <v>110</v>
@@ -3286,22 +3319,22 @@
         <v>109</v>
       </c>
       <c r="C44">
-        <v>599.73</v>
+        <v>600.04</v>
       </c>
       <c r="D44">
-        <v>603.5999</v>
+        <v>603.86</v>
       </c>
       <c r="E44">
-        <v>592.5700000000001</v>
+        <v>599.11</v>
       </c>
       <c r="F44">
-        <v>593.72</v>
+        <v>600.38</v>
       </c>
       <c r="G44">
-        <v>593.72</v>
+        <v>600.38</v>
       </c>
       <c r="H44" s="1">
-        <v>63145490</v>
+        <v>49077155</v>
       </c>
       <c r="I44" t="s">
         <v>110</v>
@@ -3315,22 +3348,22 @@
         <v>109</v>
       </c>
       <c r="C45">
-        <v>600.04</v>
+        <v>603.14</v>
       </c>
       <c r="D45">
-        <v>603.86</v>
+        <v>605.9</v>
       </c>
       <c r="E45">
-        <v>599.11</v>
+        <v>601.87</v>
       </c>
       <c r="F45">
-        <v>600.38</v>
+        <v>603.3099999999999</v>
       </c>
       <c r="G45">
-        <v>600.38</v>
+        <v>603.3099999999999</v>
       </c>
       <c r="H45" s="1">
-        <v>49077155</v>
+        <v>47106607</v>
       </c>
       <c r="I45" t="s">
         <v>110</v>
@@ -3344,22 +3377,22 @@
         <v>109</v>
       </c>
       <c r="C46">
-        <v>603.14</v>
+        <v>601.49</v>
       </c>
       <c r="D46">
-        <v>605.9</v>
+        <v>603.16</v>
       </c>
       <c r="E46">
-        <v>601.87</v>
+        <v>594.5599999999999</v>
       </c>
       <c r="F46">
-        <v>603.3099999999999</v>
+        <v>594.9</v>
       </c>
       <c r="G46">
-        <v>603.3099999999999</v>
+        <v>594.9</v>
       </c>
       <c r="H46" s="1">
-        <v>47106607</v>
+        <v>56127962</v>
       </c>
       <c r="I46" t="s">
         <v>110</v>
@@ -3373,22 +3406,22 @@
         <v>109</v>
       </c>
       <c r="C47">
-        <v>601.49</v>
+        <v>589.51</v>
       </c>
       <c r="D47">
-        <v>603.16</v>
+        <v>595.8</v>
       </c>
       <c r="E47">
-        <v>594.5599999999999</v>
+        <v>587.08</v>
       </c>
       <c r="F47">
-        <v>594.9</v>
+        <v>593.02</v>
       </c>
       <c r="G47">
-        <v>594.9</v>
+        <v>593.02</v>
       </c>
       <c r="H47" s="1">
-        <v>56127962</v>
+        <v>75597578</v>
       </c>
       <c r="I47" t="s">
         <v>110</v>
@@ -3402,22 +3435,22 @@
         <v>109</v>
       </c>
       <c r="C48">
-        <v>589.51</v>
+        <v>591.0599999999999</v>
       </c>
       <c r="D48">
-        <v>595.8</v>
+        <v>591.17</v>
       </c>
       <c r="E48">
-        <v>587.08</v>
+        <v>578.54</v>
       </c>
       <c r="F48">
-        <v>593.02</v>
+        <v>582.0599999999999</v>
       </c>
       <c r="G48">
-        <v>593.02</v>
+        <v>582.0599999999999</v>
       </c>
       <c r="H48" s="1">
-        <v>75597578</v>
+        <v>91964677</v>
       </c>
       <c r="I48" t="s">
         <v>110</v>
@@ -3431,22 +3464,22 @@
         <v>109</v>
       </c>
       <c r="C49">
-        <v>591.0599999999999</v>
+        <v>590.52</v>
       </c>
       <c r="D49">
-        <v>591.17</v>
+        <v>595.08</v>
       </c>
       <c r="E49">
-        <v>578.54</v>
+        <v>585.96</v>
       </c>
       <c r="F49">
-        <v>582.0599999999999</v>
+        <v>588</v>
       </c>
       <c r="G49">
-        <v>582.0599999999999</v>
+        <v>588</v>
       </c>
       <c r="H49" s="1">
-        <v>91964677</v>
+        <v>89936118</v>
       </c>
       <c r="I49" t="s">
         <v>110</v>
@@ -3460,22 +3493,22 @@
         <v>109</v>
       </c>
       <c r="C50">
-        <v>590.52</v>
+        <v>584.8099999999999</v>
       </c>
       <c r="D50">
-        <v>595.08</v>
+        <v>587.9299999999999</v>
       </c>
       <c r="E50">
-        <v>585.96</v>
+        <v>581.9299999999999</v>
       </c>
       <c r="F50">
-        <v>588</v>
+        <v>583.98</v>
       </c>
       <c r="G50">
-        <v>588</v>
+        <v>583.98</v>
       </c>
       <c r="H50" s="1">
-        <v>89936118</v>
+        <v>57750895</v>
       </c>
       <c r="I50" t="s">
         <v>110</v>
@@ -3489,22 +3522,22 @@
         <v>109</v>
       </c>
       <c r="C51">
-        <v>584.8099999999999</v>
+        <v>589.14</v>
       </c>
       <c r="D51">
-        <v>587.9299999999999</v>
+        <v>591.37</v>
       </c>
       <c r="E51">
-        <v>581.9299999999999</v>
+        <v>585.6900000000001</v>
       </c>
       <c r="F51">
-        <v>583.98</v>
+        <v>587.8200000000001</v>
       </c>
       <c r="G51">
-        <v>583.98</v>
+        <v>587.8200000000001</v>
       </c>
       <c r="H51" s="1">
-        <v>57750895</v>
+        <v>60475491</v>
       </c>
       <c r="I51" t="s">
         <v>110</v>
@@ -3518,22 +3551,22 @@
         <v>109</v>
       </c>
       <c r="C52">
-        <v>589.14</v>
+        <v>582.6</v>
       </c>
       <c r="D52">
-        <v>591.37</v>
+        <v>584.63</v>
       </c>
       <c r="E52">
-        <v>585.6900000000001</v>
+        <v>573.4299999999999</v>
       </c>
       <c r="F52">
-        <v>587.8200000000001</v>
+        <v>573.79</v>
       </c>
       <c r="G52">
-        <v>587.8200000000001</v>
+        <v>573.79</v>
       </c>
       <c r="H52" s="1">
-        <v>60475491</v>
+        <v>81492124</v>
       </c>
       <c r="I52" t="s">
         <v>110</v>
@@ -3547,22 +3580,22 @@
         <v>109</v>
       </c>
       <c r="C53">
-        <v>582.6</v>
+        <v>570.8099999999999</v>
       </c>
       <c r="D53">
-        <v>584.63</v>
+        <v>571.02</v>
       </c>
       <c r="E53">
-        <v>573.4299999999999</v>
+        <v>561.5700000000001</v>
       </c>
       <c r="F53">
-        <v>573.79</v>
+        <v>562.58</v>
       </c>
       <c r="G53">
-        <v>573.79</v>
+        <v>562.58</v>
       </c>
       <c r="H53" s="1">
-        <v>81492124</v>
+        <v>82702240</v>
       </c>
       <c r="I53" t="s">
         <v>110</v>
@@ -3576,22 +3609,22 @@
         <v>109</v>
       </c>
       <c r="C54">
-        <v>570.8099999999999</v>
+        <v>567.38</v>
       </c>
       <c r="D54">
-        <v>571.02</v>
+        <v>568.05</v>
       </c>
       <c r="E54">
-        <v>561.5700000000001</v>
+        <v>555.6</v>
       </c>
       <c r="F54">
-        <v>562.58</v>
+        <v>558.28</v>
       </c>
       <c r="G54">
-        <v>562.58</v>
+        <v>558.28</v>
       </c>
       <c r="H54" s="1">
-        <v>82702240</v>
+        <v>70602622</v>
       </c>
       <c r="I54" t="s">
         <v>110</v>
@@ -3605,22 +3638,22 @@
         <v>109</v>
       </c>
       <c r="C55">
-        <v>567.38</v>
+        <v>564.29</v>
       </c>
       <c r="D55">
-        <v>568.05</v>
+        <v>578.64</v>
       </c>
       <c r="E55">
-        <v>555.6</v>
+        <v>564.21</v>
       </c>
       <c r="F55">
-        <v>558.28</v>
+        <v>577.1799999999999</v>
       </c>
       <c r="G55">
-        <v>558.28</v>
+        <v>577.1799999999999</v>
       </c>
       <c r="H55" s="1">
-        <v>70602622</v>
+        <v>95877997</v>
       </c>
       <c r="I55" t="s">
         <v>110</v>
@@ -3634,22 +3667,22 @@
         <v>109</v>
       </c>
       <c r="C56">
-        <v>564.29</v>
+        <v>581.48</v>
       </c>
       <c r="D56">
-        <v>578.64</v>
+        <v>587.739</v>
       </c>
       <c r="E56">
-        <v>564.21</v>
+        <v>580.42</v>
       </c>
       <c r="F56">
-        <v>577.1799999999999</v>
+        <v>584.3099999999999</v>
       </c>
       <c r="G56">
-        <v>577.1799999999999</v>
+        <v>584.3099999999999</v>
       </c>
       <c r="H56" s="1">
-        <v>95877997</v>
+        <v>79435132</v>
       </c>
       <c r="I56" t="s">
         <v>110</v>
@@ -3663,22 +3696,22 @@
         <v>109</v>
       </c>
       <c r="C57">
-        <v>581.48</v>
+        <v>573.97</v>
       </c>
       <c r="D57">
-        <v>587.739</v>
+        <v>586.05</v>
       </c>
       <c r="E57">
-        <v>580.42</v>
+        <v>571.92</v>
       </c>
       <c r="F57">
-        <v>584.3099999999999</v>
+        <v>584.98</v>
       </c>
       <c r="G57">
-        <v>584.3099999999999</v>
+        <v>584.98</v>
       </c>
       <c r="H57" s="1">
-        <v>79435132</v>
+        <v>50941709</v>
       </c>
       <c r="I57" t="s">
         <v>110</v>
@@ -3692,22 +3725,22 @@
         <v>109</v>
       </c>
       <c r="C58">
-        <v>573.97</v>
+        <v>586.23</v>
       </c>
       <c r="D58">
-        <v>586.05</v>
+        <v>590.61</v>
       </c>
       <c r="E58">
-        <v>571.92</v>
+        <v>584.6900000000001</v>
       </c>
       <c r="F58">
-        <v>584.98</v>
+        <v>588.5</v>
       </c>
       <c r="G58">
-        <v>584.98</v>
+        <v>588.5</v>
       </c>
       <c r="H58" s="1">
-        <v>50941709</v>
+        <v>35108496</v>
       </c>
       <c r="I58" t="s">
         <v>110</v>
@@ -3721,22 +3754,22 @@
         <v>109</v>
       </c>
       <c r="C59">
-        <v>586.23</v>
+        <v>585.64</v>
       </c>
       <c r="D59">
-        <v>590.61</v>
+        <v>588.98</v>
       </c>
       <c r="E59">
-        <v>584.6900000000001</v>
+        <v>578.4001</v>
       </c>
       <c r="F59">
-        <v>588.5</v>
+        <v>588.59</v>
       </c>
       <c r="G59">
-        <v>588.5</v>
+        <v>588.59</v>
       </c>
       <c r="H59" s="1">
-        <v>35108496</v>
+        <v>49948195</v>
       </c>
       <c r="I59" t="s">
         <v>110</v>
@@ -3750,22 +3783,22 @@
         <v>109</v>
       </c>
       <c r="C60">
-        <v>585.64</v>
+        <v>608.71</v>
       </c>
       <c r="D60">
-        <v>588.98</v>
+        <v>609.9</v>
       </c>
       <c r="E60">
-        <v>578.4001</v>
+        <v>602.12</v>
       </c>
       <c r="F60">
-        <v>588.59</v>
+        <v>606.09</v>
       </c>
       <c r="G60">
-        <v>588.59</v>
+        <v>606.09</v>
       </c>
       <c r="H60" s="1">
-        <v>49948195</v>
+        <v>63085996</v>
       </c>
       <c r="I60" t="s">
         <v>110</v>
@@ -3779,22 +3812,22 @@
         <v>109</v>
       </c>
       <c r="C61">
-        <v>608.71</v>
+        <v>605.9299999999999</v>
       </c>
       <c r="D61">
-        <v>609.9</v>
+        <v>610.5</v>
       </c>
       <c r="E61">
-        <v>602.12</v>
+        <v>603.03</v>
       </c>
       <c r="F61">
-        <v>606.09</v>
+        <v>610.1900000000001</v>
       </c>
       <c r="G61">
-        <v>606.09</v>
+        <v>610.1900000000001</v>
       </c>
       <c r="H61" s="1">
-        <v>63085996</v>
+        <v>37837538</v>
       </c>
       <c r="I61" t="s">
         <v>110</v>
@@ -3808,22 +3841,22 @@
         <v>109</v>
       </c>
       <c r="C62">
-        <v>605.9299999999999</v>
+        <v>611.84</v>
       </c>
       <c r="D62">
-        <v>610.5</v>
+        <v>613.67</v>
       </c>
       <c r="E62">
-        <v>603.03</v>
+        <v>609.58</v>
       </c>
       <c r="F62">
-        <v>610.1900000000001</v>
+        <v>611.0700000000001</v>
       </c>
       <c r="G62">
-        <v>610.1900000000001</v>
+        <v>611.0700000000001</v>
       </c>
       <c r="H62" s="1">
-        <v>37837538</v>
+        <v>34038533</v>
       </c>
       <c r="I62" t="s">
         <v>110</v>
@@ -3837,22 +3870,22 @@
         <v>109</v>
       </c>
       <c r="C63">
-        <v>611.84</v>
+        <v>609.48</v>
       </c>
       <c r="D63">
-        <v>613.67</v>
+        <v>626.74</v>
       </c>
       <c r="E63">
-        <v>609.58</v>
+        <v>608.11</v>
       </c>
       <c r="F63">
-        <v>611.0700000000001</v>
+        <v>617.39</v>
       </c>
       <c r="G63">
-        <v>611.0700000000001</v>
+        <v>617.39</v>
       </c>
       <c r="H63" s="1">
-        <v>34038533</v>
+        <v>32972110</v>
       </c>
       <c r="I63" t="s">
         <v>110</v>
@@ -3866,22 +3899,22 @@
         <v>109</v>
       </c>
       <c r="C64">
-        <v>609.48</v>
+        <v>620.22</v>
       </c>
       <c r="D64">
-        <v>626.74</v>
+        <v>628.6</v>
       </c>
       <c r="E64">
-        <v>608.11</v>
+        <v>620.1</v>
       </c>
       <c r="F64">
-        <v>617.39</v>
+        <v>628.6</v>
       </c>
       <c r="G64">
-        <v>617.39</v>
+        <v>628.6</v>
       </c>
       <c r="H64" s="1">
-        <v>32972110</v>
+        <v>49921081</v>
       </c>
       <c r="I64" t="s">
         <v>110</v>
@@ -3895,22 +3928,22 @@
         <v>109</v>
       </c>
       <c r="C65">
-        <v>620.22</v>
+        <v>629.08</v>
       </c>
       <c r="D65">
-        <v>628.6</v>
+        <v>637.83</v>
       </c>
       <c r="E65">
-        <v>620.1</v>
+        <v>628.2</v>
       </c>
       <c r="F65">
-        <v>628.6</v>
+        <v>637.4</v>
       </c>
       <c r="G65">
-        <v>628.6</v>
+        <v>637.4</v>
       </c>
       <c r="H65" s="1">
-        <v>49921081</v>
+        <v>50102386</v>
       </c>
       <c r="I65" t="s">
         <v>110</v>
@@ -3924,22 +3957,22 @@
         <v>109</v>
       </c>
       <c r="C66">
-        <v>629.08</v>
+        <v>639.21</v>
       </c>
       <c r="D66">
-        <v>637.83</v>
+        <v>642.1799999999999</v>
       </c>
       <c r="E66">
-        <v>628.2</v>
+        <v>635.255</v>
       </c>
       <c r="F66">
-        <v>637.4</v>
+        <v>640.47</v>
       </c>
       <c r="G66">
-        <v>637.4</v>
+        <v>640.47</v>
       </c>
       <c r="H66" s="1">
-        <v>50102386</v>
+        <v>42320581</v>
       </c>
       <c r="I66" t="s">
         <v>110</v>
@@ -3953,22 +3986,22 @@
         <v>109</v>
       </c>
       <c r="C67">
-        <v>639.21</v>
+        <v>645.59</v>
       </c>
       <c r="D67">
-        <v>642.1799999999999</v>
+        <v>650</v>
       </c>
       <c r="E67">
-        <v>635.255</v>
+        <v>644.0700000000001</v>
       </c>
       <c r="F67">
-        <v>640.47</v>
+        <v>648.85</v>
       </c>
       <c r="G67">
-        <v>640.47</v>
+        <v>648.85</v>
       </c>
       <c r="H67" s="1">
-        <v>42320581</v>
+        <v>53488871</v>
       </c>
       <c r="I67" t="s">
         <v>110</v>
@@ -3982,22 +4015,22 @@
         <v>109</v>
       </c>
       <c r="C68">
-        <v>645.59</v>
+        <v>648.04</v>
       </c>
       <c r="D68">
-        <v>650</v>
+        <v>648.76</v>
       </c>
       <c r="E68">
-        <v>644.0700000000001</v>
+        <v>642.52</v>
       </c>
       <c r="F68">
-        <v>648.85</v>
+        <v>646.79</v>
       </c>
       <c r="G68">
-        <v>648.85</v>
+        <v>646.79</v>
       </c>
       <c r="H68" s="1">
-        <v>53488871</v>
+        <v>37138511</v>
       </c>
       <c r="I68" t="s">
         <v>110</v>
@@ -4011,22 +4044,22 @@
         <v>109</v>
       </c>
       <c r="C69">
-        <v>648.04</v>
+        <v>648.41</v>
       </c>
       <c r="D69">
-        <v>648.76</v>
+        <v>650.2</v>
       </c>
       <c r="E69">
-        <v>642.52</v>
+        <v>642.21</v>
       </c>
       <c r="F69">
-        <v>646.79</v>
+        <v>644.33</v>
       </c>
       <c r="G69">
-        <v>646.79</v>
+        <v>644.33</v>
       </c>
       <c r="H69" s="1">
-        <v>37138511</v>
+        <v>39580523</v>
       </c>
       <c r="I69" t="s">
         <v>110</v>
@@ -4040,22 +4073,22 @@
         <v>109</v>
       </c>
       <c r="C70">
-        <v>648.41</v>
+        <v>650.15</v>
       </c>
       <c r="D70">
-        <v>650.2</v>
+        <v>655.33</v>
       </c>
       <c r="E70">
-        <v>642.21</v>
+        <v>648.52</v>
       </c>
       <c r="F70">
-        <v>644.33</v>
+        <v>655.11</v>
       </c>
       <c r="G70">
-        <v>644.33</v>
+        <v>655.11</v>
       </c>
       <c r="H70" s="1">
-        <v>39580523</v>
+        <v>37368402</v>
       </c>
       <c r="I70" t="s">
         <v>110</v>
@@ -4069,22 +4102,22 @@
         <v>109</v>
       </c>
       <c r="C71">
-        <v>650.15</v>
+        <v>653.55</v>
       </c>
       <c r="D71">
-        <v>655.33</v>
+        <v>656.92</v>
       </c>
       <c r="E71">
-        <v>648.52</v>
+        <v>645.52</v>
       </c>
       <c r="F71">
-        <v>655.11</v>
+        <v>651.42</v>
       </c>
       <c r="G71">
-        <v>655.11</v>
+        <v>651.42</v>
       </c>
       <c r="H71" s="1">
-        <v>37368402</v>
+        <v>40099827</v>
       </c>
       <c r="I71" t="s">
         <v>110</v>
@@ -4098,22 +4131,22 @@
         <v>109</v>
       </c>
       <c r="C72">
-        <v>653.55</v>
+        <v>658.51</v>
       </c>
       <c r="D72">
-        <v>656.92</v>
+        <v>664.51</v>
       </c>
       <c r="E72">
-        <v>645.52</v>
+        <v>656.5300999999999</v>
       </c>
       <c r="F72">
-        <v>651.42</v>
+        <v>663.88</v>
       </c>
       <c r="G72">
-        <v>651.42</v>
+        <v>663.88</v>
       </c>
       <c r="H72" s="1">
-        <v>40099827</v>
+        <v>45563050</v>
       </c>
       <c r="I72" t="s">
         <v>110</v>
@@ -4127,22 +4160,22 @@
         <v>109</v>
       </c>
       <c r="C73">
-        <v>658.51</v>
+        <v>663.4</v>
       </c>
       <c r="D73">
-        <v>664.51</v>
+        <v>664.4299999999999</v>
       </c>
       <c r="E73">
-        <v>656.5300999999999</v>
+        <v>660.6900000000001</v>
       </c>
       <c r="F73">
-        <v>663.88</v>
+        <v>664.23</v>
       </c>
       <c r="G73">
-        <v>663.88</v>
+        <v>664.23</v>
       </c>
       <c r="H73" s="1">
-        <v>45563050</v>
+        <v>32717030</v>
       </c>
       <c r="I73" t="s">
         <v>110</v>
@@ -4156,22 +4189,22 @@
         <v>109</v>
       </c>
       <c r="C74">
-        <v>663.4</v>
+        <v>657.41</v>
       </c>
       <c r="D74">
-        <v>664.4299999999999</v>
+        <v>659.64</v>
       </c>
       <c r="E74">
-        <v>660.6900000000001</v>
+        <v>653.8099999999999</v>
       </c>
       <c r="F74">
-        <v>664.23</v>
+        <v>657.55</v>
       </c>
       <c r="G74">
-        <v>664.23</v>
+        <v>657.55</v>
       </c>
       <c r="H74" s="1">
-        <v>32717030</v>
+        <v>34147916</v>
       </c>
       <c r="I74" t="s">
         <v>110</v>
@@ -4185,22 +4218,22 @@
         <v>109</v>
       </c>
       <c r="C75">
-        <v>657.41</v>
+        <v>658.63</v>
       </c>
       <c r="D75">
-        <v>659.64</v>
+        <v>661.72</v>
       </c>
       <c r="E75">
-        <v>653.8099999999999</v>
+        <v>656.5898999999999</v>
       </c>
       <c r="F75">
-        <v>657.55</v>
+        <v>661.5700000000001</v>
       </c>
       <c r="G75">
-        <v>657.55</v>
+        <v>661.5700000000001</v>
       </c>
       <c r="H75" s="1">
-        <v>34147916</v>
+        <v>31724860</v>
       </c>
       <c r="I75" t="s">
         <v>110</v>
@@ -4214,22 +4247,22 @@
         <v>109</v>
       </c>
       <c r="C76">
-        <v>658.63</v>
+        <v>665.35</v>
       </c>
       <c r="D76">
-        <v>661.72</v>
+        <v>668.9</v>
       </c>
       <c r="E76">
-        <v>656.5898999999999</v>
+        <v>657.5599999999999</v>
       </c>
       <c r="F76">
-        <v>661.5700000000001</v>
+        <v>667.74</v>
       </c>
       <c r="G76">
-        <v>661.5700000000001</v>
+        <v>667.74</v>
       </c>
       <c r="H76" s="1">
-        <v>31724860</v>
+        <v>40622226</v>
       </c>
       <c r="I76" t="s">
         <v>110</v>
@@ -4243,22 +4276,22 @@
         <v>109</v>
       </c>
       <c r="C77">
-        <v>665.35</v>
+        <v>669.16</v>
       </c>
       <c r="D77">
-        <v>668.9</v>
+        <v>675.97</v>
       </c>
       <c r="E77">
-        <v>657.5599999999999</v>
+        <v>668.8</v>
       </c>
       <c r="F77">
-        <v>667.74</v>
+        <v>674.15</v>
       </c>
       <c r="G77">
-        <v>667.74</v>
+        <v>674.15</v>
       </c>
       <c r="H77" s="1">
-        <v>40622226</v>
+        <v>39172607</v>
       </c>
       <c r="I77" t="s">
         <v>110</v>
@@ -4272,22 +4305,22 @@
         <v>109</v>
       </c>
       <c r="C78">
-        <v>669.16</v>
+        <v>674.66</v>
       </c>
       <c r="D78">
-        <v>675.97</v>
+        <v>676.73</v>
       </c>
       <c r="E78">
-        <v>668.8</v>
+        <v>668.9</v>
       </c>
       <c r="F78">
-        <v>674.15</v>
+        <v>672.88</v>
       </c>
       <c r="G78">
-        <v>674.15</v>
+        <v>672.88</v>
       </c>
       <c r="H78" s="1">
-        <v>39172607</v>
+        <v>34541990</v>
       </c>
       <c r="I78" t="s">
         <v>110</v>
@@ -4301,22 +4334,22 @@
         <v>109</v>
       </c>
       <c r="C79">
-        <v>674.66</v>
+        <v>677.96</v>
       </c>
       <c r="D79">
-        <v>676.73</v>
+        <v>682.7734</v>
       </c>
       <c r="E79">
-        <v>668.9</v>
+        <v>677.51</v>
       </c>
       <c r="F79">
-        <v>672.88</v>
+        <v>681.61</v>
       </c>
       <c r="G79">
-        <v>672.88</v>
+        <v>681.61</v>
       </c>
       <c r="H79" s="1">
-        <v>34541990</v>
+        <v>37101063</v>
       </c>
       <c r="I79" t="s">
         <v>110</v>
@@ -4330,22 +4363,22 @@
         <v>109</v>
       </c>
       <c r="C80">
-        <v>677.96</v>
+        <v>687.78</v>
       </c>
       <c r="D80">
-        <v>682.7734</v>
+        <v>695.9299999999999</v>
       </c>
       <c r="E80">
-        <v>677.51</v>
+        <v>686.48</v>
       </c>
       <c r="F80">
-        <v>681.61</v>
+        <v>695.77</v>
       </c>
       <c r="G80">
-        <v>681.61</v>
+        <v>695.77</v>
       </c>
       <c r="H80" s="1">
-        <v>37101063</v>
+        <v>38778492</v>
       </c>
       <c r="I80" t="s">
         <v>110</v>
@@ -4359,22 +4392,22 @@
         <v>109</v>
       </c>
       <c r="C81">
-        <v>687.78</v>
+        <v>696.58</v>
       </c>
       <c r="D81">
-        <v>695.9299999999999</v>
+        <v>701.24</v>
       </c>
       <c r="E81">
-        <v>686.48</v>
+        <v>691.77</v>
       </c>
       <c r="F81">
-        <v>695.77</v>
+        <v>694.9400000000001</v>
       </c>
       <c r="G81">
-        <v>695.77</v>
+        <v>694.9400000000001</v>
       </c>
       <c r="H81" s="1">
-        <v>38778492</v>
+        <v>43779087</v>
       </c>
       <c r="I81" t="s">
         <v>110</v>
@@ -4388,22 +4421,22 @@
         <v>109</v>
       </c>
       <c r="C82">
-        <v>696.58</v>
+        <v>699.92</v>
       </c>
       <c r="D82">
-        <v>701.24</v>
+        <v>711.23</v>
       </c>
       <c r="E82">
-        <v>691.77</v>
+        <v>699.5</v>
       </c>
       <c r="F82">
-        <v>694.9400000000001</v>
+        <v>711.23</v>
       </c>
       <c r="G82">
-        <v>694.9400000000001</v>
+        <v>711.23</v>
       </c>
       <c r="H82" s="1">
-        <v>43779087</v>
+        <v>44320421</v>
       </c>
       <c r="I82" t="s">
         <v>110</v>
@@ -4417,22 +4450,22 @@
         <v>109</v>
       </c>
       <c r="C83">
-        <v>699.92</v>
+        <v>710.36</v>
       </c>
       <c r="D83">
-        <v>711.23</v>
+        <v>714.59</v>
       </c>
       <c r="E83">
-        <v>699.5</v>
+        <v>708.91</v>
       </c>
       <c r="F83">
-        <v>711.23</v>
+        <v>713.29</v>
       </c>
       <c r="G83">
-        <v>711.23</v>
+        <v>713.29</v>
       </c>
       <c r="H83" s="1">
-        <v>44320421</v>
+        <v>36019146</v>
       </c>
       <c r="I83" t="s">
         <v>110</v>
@@ -4446,22 +4479,22 @@
         <v>109</v>
       </c>
       <c r="C84">
-        <v>710.36</v>
+        <v>708.22</v>
       </c>
       <c r="D84">
-        <v>714.59</v>
+        <v>710.1799999999999</v>
       </c>
       <c r="E84">
-        <v>708.91</v>
+        <v>696.64</v>
       </c>
       <c r="F84">
-        <v>713.29</v>
+        <v>707.24</v>
       </c>
       <c r="G84">
-        <v>713.29</v>
+        <v>707.24</v>
       </c>
       <c r="H84" s="1">
-        <v>36019146</v>
+        <v>45873009</v>
       </c>
       <c r="I84" t="s">
         <v>110</v>
@@ -4475,22 +4508,22 @@
         <v>109</v>
       </c>
       <c r="C85">
-        <v>708.22</v>
+        <v>709.96</v>
       </c>
       <c r="D85">
-        <v>710.1799999999999</v>
+        <v>716.65</v>
       </c>
       <c r="E85">
-        <v>696.64</v>
+        <v>704.83</v>
       </c>
       <c r="F85">
-        <v>707.24</v>
+        <v>714.71</v>
       </c>
       <c r="G85">
-        <v>707.24</v>
+        <v>714.71</v>
       </c>
       <c r="H85" s="1">
-        <v>45873009</v>
+        <v>40012526</v>
       </c>
       <c r="I85" t="s">
         <v>110</v>
@@ -4504,22 +4537,22 @@
         <v>109</v>
       </c>
       <c r="C86">
-        <v>709.96</v>
+        <v>714.62</v>
       </c>
       <c r="D86">
-        <v>716.65</v>
+        <v>722.03</v>
       </c>
       <c r="E86">
-        <v>704.83</v>
+        <v>714.22</v>
       </c>
       <c r="F86">
-        <v>714.71</v>
+        <v>719.79</v>
       </c>
       <c r="G86">
-        <v>714.71</v>
+        <v>719.79</v>
       </c>
       <c r="H86" s="1">
-        <v>40012526</v>
+        <v>33327545</v>
       </c>
       <c r="I86" t="s">
         <v>110</v>
@@ -4533,22 +4566,22 @@
         <v>109</v>
       </c>
       <c r="C87">
-        <v>714.62</v>
+        <v>710.14</v>
       </c>
       <c r="D87">
-        <v>722.03</v>
+        <v>715.13</v>
       </c>
       <c r="E87">
-        <v>714.22</v>
+        <v>705.55</v>
       </c>
       <c r="F87">
-        <v>719.79</v>
+        <v>708.9299999999999</v>
       </c>
       <c r="G87">
-        <v>719.79</v>
+        <v>708.9299999999999</v>
       </c>
       <c r="H87" s="1">
-        <v>33327545</v>
+        <v>51792656</v>
       </c>
       <c r="I87" t="s">
         <v>110</v>
@@ -4562,22 +4595,22 @@
         <v>109</v>
       </c>
       <c r="C88">
-        <v>710.14</v>
+        <v>711.54</v>
       </c>
       <c r="D88">
-        <v>715.13</v>
+        <v>712.0700000000001</v>
       </c>
       <c r="E88">
-        <v>705.55</v>
+        <v>698.85</v>
       </c>
       <c r="F88">
-        <v>708.9299999999999</v>
+        <v>705.88</v>
       </c>
       <c r="G88">
-        <v>708.9299999999999</v>
+        <v>705.88</v>
       </c>
       <c r="H88" s="1">
-        <v>51792656</v>
+        <v>49834549</v>
       </c>
       <c r="I88" t="s">
         <v>110</v>
@@ -4591,22 +4624,22 @@
         <v>109</v>
       </c>
       <c r="C89">
-        <v>711.54</v>
+        <v>699.8099999999999</v>
       </c>
       <c r="D89">
-        <v>712.0700000000001</v>
+        <v>706.49</v>
       </c>
       <c r="E89">
-        <v>698.85</v>
+        <v>695.25</v>
       </c>
       <c r="F89">
-        <v>705.88</v>
+        <v>701.53</v>
       </c>
       <c r="G89">
-        <v>705.88</v>
+        <v>701.53</v>
       </c>
       <c r="H89" s="1">
-        <v>49834549</v>
+        <v>46827529</v>
       </c>
       <c r="I89" t="s">
         <v>110</v>
@@ -4620,22 +4653,22 @@
         <v>109</v>
       </c>
       <c r="C90">
-        <v>699.8099999999999</v>
+        <v>705.29</v>
       </c>
       <c r="D90">
-        <v>706.49</v>
+        <v>713.15</v>
       </c>
       <c r="E90">
-        <v>695.25</v>
+        <v>703.79</v>
       </c>
       <c r="F90">
-        <v>701.53</v>
+        <v>713.15</v>
       </c>
       <c r="G90">
-        <v>701.53</v>
+        <v>713.15</v>
       </c>
       <c r="H90" s="1">
-        <v>46827529</v>
+        <v>35403154</v>
       </c>
       <c r="I90" t="s">
         <v>110</v>
@@ -4649,22 +4682,22 @@
         <v>109</v>
       </c>
       <c r="C91">
-        <v>705.29</v>
+        <v>708.99</v>
       </c>
       <c r="D91">
-        <v>713.15</v>
+        <v>717.12</v>
       </c>
       <c r="E91">
-        <v>703.79</v>
+        <v>706.77</v>
       </c>
       <c r="F91">
-        <v>713.15</v>
+        <v>714.51</v>
       </c>
       <c r="G91">
-        <v>713.15</v>
+        <v>714.51</v>
       </c>
       <c r="H91" s="1">
-        <v>35403154</v>
+        <v>36415360</v>
       </c>
       <c r="I91" t="s">
         <v>110</v>
@@ -4678,22 +4711,22 @@
         <v>109</v>
       </c>
       <c r="C92">
-        <v>708.99</v>
+        <v>718.0700000000001</v>
       </c>
       <c r="D92">
-        <v>717.12</v>
+        <v>722.12</v>
       </c>
       <c r="E92">
-        <v>706.77</v>
+        <v>715.95</v>
       </c>
       <c r="F92">
-        <v>714.51</v>
+        <v>717.54</v>
       </c>
       <c r="G92">
-        <v>714.51</v>
+        <v>717.54</v>
       </c>
       <c r="H92" s="1">
-        <v>36415360</v>
+        <v>33118575</v>
       </c>
       <c r="I92" t="s">
         <v>110</v>
@@ -4707,22 +4740,22 @@
         <v>109</v>
       </c>
       <c r="C93">
-        <v>718.0700000000001</v>
+        <v>725.96</v>
       </c>
       <c r="D93">
-        <v>722.12</v>
+        <v>731.17</v>
       </c>
       <c r="E93">
-        <v>715.95</v>
+        <v>724.16</v>
       </c>
       <c r="F93">
-        <v>717.54</v>
+        <v>730.28</v>
       </c>
       <c r="G93">
-        <v>717.54</v>
+        <v>730.28</v>
       </c>
       <c r="H93" s="1">
-        <v>33118575</v>
+        <v>34254692</v>
       </c>
       <c r="I93" t="s">
         <v>110</v>
@@ -4736,22 +4769,22 @@
         <v>109</v>
       </c>
       <c r="C94">
-        <v>725.96</v>
+        <v>732.96</v>
       </c>
       <c r="D94">
-        <v>731.17</v>
+        <v>733.3200000000001</v>
       </c>
       <c r="E94">
-        <v>724.16</v>
+        <v>725.4400000000001</v>
       </c>
       <c r="F94">
-        <v>730.28</v>
+        <v>729.45</v>
       </c>
       <c r="G94">
-        <v>730.28</v>
+        <v>729.45</v>
       </c>
       <c r="H94" s="1">
-        <v>34254692</v>
+        <v>35148674</v>
       </c>
       <c r="I94" t="s">
         <v>110</v>
@@ -4765,22 +4798,22 @@
         <v>109</v>
       </c>
       <c r="C95">
-        <v>732.96</v>
+        <v>729.73</v>
       </c>
       <c r="D95">
-        <v>733.3200000000001</v>
+        <v>736.6</v>
       </c>
       <c r="E95">
-        <v>725.4400000000001</v>
+        <v>726.41</v>
       </c>
       <c r="F95">
-        <v>729.45</v>
+        <v>735.6</v>
       </c>
       <c r="G95">
-        <v>729.45</v>
+        <v>735.6</v>
       </c>
       <c r="H95" s="1">
-        <v>35148674</v>
+        <v>32839952</v>
       </c>
       <c r="I95" t="s">
         <v>110</v>
@@ -4794,22 +4827,22 @@
         <v>109</v>
       </c>
       <c r="C96">
-        <v>729.73</v>
+        <v>737.84</v>
       </c>
       <c r="D96">
-        <v>736.6</v>
+        <v>741.63</v>
       </c>
       <c r="E96">
-        <v>726.41</v>
+        <v>735.25</v>
       </c>
       <c r="F96">
-        <v>735.6</v>
+        <v>738.3099999999999</v>
       </c>
       <c r="G96">
-        <v>735.6</v>
+        <v>738.3099999999999</v>
       </c>
       <c r="H96" s="1">
-        <v>32839952</v>
+        <v>37541668</v>
       </c>
       <c r="I96" t="s">
         <v>110</v>
@@ -4823,22 +4856,22 @@
         <v>109</v>
       </c>
       <c r="C97">
-        <v>737.84</v>
+        <v>737.04</v>
       </c>
       <c r="D97">
-        <v>741.63</v>
+        <v>745.65</v>
       </c>
       <c r="E97">
-        <v>735.25</v>
+        <v>735.99</v>
       </c>
       <c r="F97">
-        <v>738.3099999999999</v>
+        <v>742.74</v>
       </c>
       <c r="G97">
-        <v>738.3099999999999</v>
+        <v>742.74</v>
       </c>
       <c r="H97" s="1">
-        <v>37541668</v>
+        <v>33890559</v>
       </c>
       <c r="I97" t="s">
         <v>110</v>
@@ -4852,22 +4885,22 @@
         <v>109</v>
       </c>
       <c r="C98">
-        <v>737.04</v>
+        <v>742.4</v>
       </c>
       <c r="D98">
-        <v>745.65</v>
+        <v>746.4400000000001</v>
       </c>
       <c r="E98">
-        <v>735.99</v>
+        <v>739.23</v>
       </c>
       <c r="F98">
-        <v>742.74</v>
+        <v>746.16</v>
       </c>
       <c r="G98">
-        <v>742.74</v>
+        <v>746.16</v>
       </c>
       <c r="H98" s="1">
-        <v>33890559</v>
+        <v>30085237</v>
       </c>
       <c r="I98" t="s">
         <v>110</v>
@@ -4881,22 +4914,22 @@
         <v>109</v>
       </c>
       <c r="C99">
-        <v>742.4</v>
+        <v>747.3099999999999</v>
       </c>
       <c r="D99">
-        <v>746.4400000000001</v>
+        <v>748.65</v>
       </c>
       <c r="E99">
-        <v>739.23</v>
+        <v>741.01</v>
       </c>
       <c r="F99">
-        <v>746.16</v>
+        <v>744.21</v>
       </c>
       <c r="G99">
-        <v>746.16</v>
+        <v>744.21</v>
       </c>
       <c r="H99" s="1">
-        <v>30085237</v>
+        <v>40270198</v>
       </c>
       <c r="I99" t="s">
         <v>110</v>
@@ -4910,22 +4943,22 @@
         <v>109</v>
       </c>
       <c r="C100">
-        <v>747.3099999999999</v>
+        <v>735.48</v>
       </c>
       <c r="D100">
-        <v>748.65</v>
+        <v>743.4988</v>
       </c>
       <c r="E100">
-        <v>741.01</v>
+        <v>732.62</v>
       </c>
       <c r="F100">
-        <v>744.21</v>
+        <v>740.61</v>
       </c>
       <c r="G100">
-        <v>744.21</v>
+        <v>740.61</v>
       </c>
       <c r="H100" s="1">
-        <v>40270198</v>
+        <v>40782580</v>
       </c>
       <c r="I100" t="s">
         <v>110</v>
@@ -4939,22 +4972,22 @@
         <v>109</v>
       </c>
       <c r="C101">
-        <v>735.48</v>
+        <v>730.0599999999999</v>
       </c>
       <c r="D101">
-        <v>743.4988</v>
+        <v>731.6900000000001</v>
       </c>
       <c r="E101">
-        <v>732.62</v>
+        <v>704.3200000000001</v>
       </c>
       <c r="F101">
-        <v>740.61</v>
+        <v>705.0599999999999</v>
       </c>
       <c r="G101">
-        <v>740.61</v>
+        <v>705.0599999999999</v>
       </c>
       <c r="H101" s="1">
-        <v>40782580</v>
+        <v>96721528</v>
       </c>
       <c r="I101" t="s">
         <v>110</v>
@@ -4968,7 +5001,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="12.7109375" customWidth="1"/>
@@ -4986,60 +5019,60 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>408</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B2" t="s">
         <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -5054,7 +5087,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="I2">
         <v>25</v>
@@ -5072,18 +5105,18 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C3" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D3">
         <v>7</v>
@@ -5098,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="I3">
         <v>10</v>
@@ -5107,27 +5140,27 @@
         <v>7</v>
       </c>
       <c r="K3" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="L3" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B4" t="s">
         <v>390</v>
       </c>
       <c r="C4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -5142,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="I4">
         <v>3</v>
@@ -5160,18 +5193,18 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B5" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C5" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -5183,10 +5216,10 @@
         <v>1</v>
       </c>
       <c r="G5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="I5">
         <v>250</v>
@@ -5195,55 +5228,99 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="M5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B6" t="s">
-        <v>462</v>
+        <v>410</v>
       </c>
       <c r="C6" t="s">
+        <v>470</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>474</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
+        <v>478</v>
+      </c>
+      <c r="L6" t="s">
+        <v>478</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>465</v>
+      </c>
+      <c r="B7" t="s">
         <v>466</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>469</v>
-      </c>
-      <c r="I6">
+      <c r="C7" t="s">
+        <v>471</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>475</v>
+      </c>
+      <c r="I7">
         <v>50</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>475</v>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O6"/>
+  <autoFilter ref="A1:O7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5261,13 +5338,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5281,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5295,7 +5372,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5309,7 +5386,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5323,7 +5400,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -5337,7 +5414,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5351,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5365,7 +5442,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5379,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5393,7 +5470,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -5407,7 +5484,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -5421,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5435,7 +5512,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -5449,7 +5526,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -5463,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -5477,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -5491,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -5505,7 +5582,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -5519,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -5533,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -5547,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -5561,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -5575,7 +5652,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5589,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -5603,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -5617,7 +5694,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -5631,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -5645,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -5659,7 +5736,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -5673,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -5687,7 +5764,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -5701,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -5715,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -5729,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -5743,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5757,7 +5834,7 @@
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5771,7 +5848,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -5785,7 +5862,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -5799,7 +5876,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -5813,7 +5890,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -5827,7 +5904,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -5841,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -5855,7 +5932,7 @@
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -5869,7 +5946,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -5883,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -5897,7 +5974,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -5911,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -5925,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -5939,7 +6016,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -5953,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -5967,7 +6044,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -5981,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -5995,7 +6072,7 @@
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -6009,7 +6086,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -6023,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -6037,7 +6114,7 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -6051,7 +6128,7 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -6065,7 +6142,7 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -6079,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -6093,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -6107,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -6121,7 +6198,7 @@
         <v>0</v>
       </c>
       <c r="D62" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -6135,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="D63" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -6149,7 +6226,7 @@
         <v>0</v>
       </c>
       <c r="D64" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -6163,7 +6240,7 @@
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -6177,7 +6254,7 @@
         <v>0</v>
       </c>
       <c r="D66" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -6191,7 +6268,7 @@
         <v>0</v>
       </c>
       <c r="D67" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -6205,7 +6282,7 @@
         <v>0</v>
       </c>
       <c r="D68" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -6219,7 +6296,7 @@
         <v>0</v>
       </c>
       <c r="D69" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -6233,7 +6310,7 @@
         <v>0</v>
       </c>
       <c r="D70" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -6247,7 +6324,7 @@
         <v>0</v>
       </c>
       <c r="D71" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -6261,7 +6338,7 @@
         <v>0</v>
       </c>
       <c r="D72" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -6275,7 +6352,7 @@
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -6289,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="D74" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -6303,7 +6380,7 @@
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -6317,7 +6394,7 @@
         <v>0</v>
       </c>
       <c r="D76" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -6331,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="D77" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -6345,7 +6422,7 @@
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -6359,7 +6436,7 @@
         <v>0</v>
       </c>
       <c r="D79" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -6373,7 +6450,7 @@
         <v>0</v>
       </c>
       <c r="D80" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -6387,7 +6464,7 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -6401,7 +6478,7 @@
         <v>0</v>
       </c>
       <c r="D82" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -6415,7 +6492,7 @@
         <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -6429,7 +6506,7 @@
         <v>0</v>
       </c>
       <c r="D84" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -6443,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -6457,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="D86" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -6471,7 +6548,7 @@
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -6485,7 +6562,7 @@
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -6499,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="D89" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -6513,7 +6590,7 @@
         <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -6527,7 +6604,7 @@
         <v>0</v>
       </c>
       <c r="D91" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -6541,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="D92" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -6555,7 +6632,7 @@
         <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -6569,7 +6646,7 @@
         <v>0</v>
       </c>
       <c r="D94" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -6583,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="D95" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -6597,7 +6674,7 @@
         <v>0</v>
       </c>
       <c r="D96" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -6611,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="D97" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -6625,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="D98" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -6639,7 +6716,7 @@
         <v>0</v>
       </c>
       <c r="D99" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -6650,7 +6727,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -6683,13 +6760,13 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="B2">
-        <v>740.61</v>
+        <v>705.0599999999999</v>
       </c>
       <c r="C2" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="D2" t="s">
         <v>108</v>
@@ -6703,13 +6780,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B3">
-        <v>0.06444658435977413</v>
+        <v>0.01456240826546162</v>
       </c>
       <c r="C3" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="D3" t="s">
         <v>108</v>
@@ -6723,13 +6800,13 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="B4">
-        <v>0.2185695246557087</v>
+        <v>0.1602297223913507</v>
       </c>
       <c r="C4" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="D4" t="s">
         <v>108</v>
@@ -6743,13 +6820,13 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B5">
-        <v>0.1484339798758119</v>
+        <v>0.2346381697618982</v>
       </c>
       <c r="C5" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="D5" t="s">
         <v>108</v>
@@ -6763,13 +6840,13 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="B6">
-        <v>-0.007438082984882577</v>
+        <v>-0.0550820199421036</v>
       </c>
       <c r="C6" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="D6" t="s">
         <v>108</v>
@@ -6783,13 +6860,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B7">
         <v>-0.1183474937620417</v>
       </c>
       <c r="C7" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="D7" t="s">
         <v>108</v>
@@ -6803,13 +6880,13 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B8">
-        <v>665.4643999999998</v>
+        <v>667.8092</v>
       </c>
       <c r="C8" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="D8" t="s">
         <v>108</v>
@@ -6823,10 +6900,10 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="C9" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="D9" t="s">
         <v>108</v>
@@ -6843,10 +6920,10 @@
         <v>142</v>
       </c>
       <c r="B10">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="C10" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="D10" t="s">
         <v>107</v>
@@ -6860,13 +6937,13 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B11">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="C11" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="D11" t="s">
         <v>107</v>
@@ -6880,13 +6957,13 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B12">
         <v>3.78</v>
       </c>
       <c r="C12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="D12" t="s">
         <v>107</v>
@@ -6900,13 +6977,13 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B13">
         <v>3.62</v>
       </c>
       <c r="C13" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="D13" t="s">
         <v>107</v>
@@ -6920,16 +6997,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B14">
         <v>332.407</v>
       </c>
       <c r="C14" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>137</v>
@@ -6940,16 +7017,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B15">
         <v>130.902</v>
       </c>
       <c r="C15" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
         <v>137</v>
@@ -6960,16 +7037,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B16">
         <v>4.3</v>
       </c>
       <c r="C16" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
         <v>137</v>
@@ -6983,7 +7060,7 @@
         <v>142</v>
       </c>
       <c r="B17">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="C17" t="s">
         <v>156</v>
@@ -7023,7 +7100,7 @@
         <v>144</v>
       </c>
       <c r="B19">
-        <v>-0.4100000000000001</v>
+        <v>-0.4199999999999999</v>
       </c>
       <c r="C19" t="s">
         <v>158</v>
@@ -7043,7 +7120,7 @@
         <v>145</v>
       </c>
       <c r="B20">
-        <v>0.4100000000000001</v>
+        <v>0.4199999999999999</v>
       </c>
       <c r="C20" t="s">
         <v>159</v>
@@ -7063,7 +7140,7 @@
         <v>146</v>
       </c>
       <c r="B21">
-        <v>-0.08999999999999986</v>
+        <v>-0.07999999999999963</v>
       </c>
       <c r="C21" t="s">
         <v>160</v>
@@ -7089,7 +7166,7 @@
         <v>161</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
         <v>137</v>
@@ -7109,7 +7186,7 @@
         <v>161</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E23" t="s">
         <v>137</v>
@@ -7129,7 +7206,7 @@
         <v>161</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E24" t="s">
         <v>137</v>
@@ -7149,7 +7226,7 @@
         <v>162</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E25" t="s">
         <v>137</v>
@@ -7169,7 +7246,7 @@
         <v>163</v>
       </c>
       <c r="D26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s">
         <v>137</v>
@@ -7189,7 +7266,7 @@
         <v>163</v>
       </c>
       <c r="D27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E27" t="s">
         <v>137</v>
@@ -7209,7 +7286,7 @@
         <v>163</v>
       </c>
       <c r="D28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E28" t="s">
         <v>137</v>
@@ -7229,7 +7306,7 @@
         <v>164</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E29" t="s">
         <v>137</v>
@@ -7249,7 +7326,7 @@
         <v>165</v>
       </c>
       <c r="D30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s">
         <v>137</v>
@@ -7260,19 +7337,19 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="D31" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E31" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
@@ -7283,10 +7360,10 @@
         <v>393</v>
       </c>
       <c r="B32">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="D32" t="s">
         <v>108</v>
@@ -7303,10 +7380,10 @@
         <v>394</v>
       </c>
       <c r="B33">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="D33" t="s">
         <v>108</v>
@@ -7323,10 +7400,10 @@
         <v>395</v>
       </c>
       <c r="B34">
-        <v>0.58</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="C34" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="D34" t="s">
         <v>108</v>
@@ -7343,10 +7420,10 @@
         <v>396</v>
       </c>
       <c r="B35">
-        <v>0.58</v>
+        <v>0.5849056603773585</v>
       </c>
       <c r="C35" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="D35" t="s">
         <v>108</v>
@@ -7363,10 +7440,10 @@
         <v>397</v>
       </c>
       <c r="B36">
-        <v>0.58</v>
+        <v>0.6037735849056604</v>
       </c>
       <c r="C36" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="D36" t="s">
         <v>108</v>
@@ -7383,10 +7460,10 @@
         <v>398</v>
       </c>
       <c r="B37">
-        <v>0.66</v>
+        <v>0.660377358490566</v>
       </c>
       <c r="C37" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="D37" t="s">
         <v>108</v>
@@ -7406,7 +7483,7 @@
         <v>7</v>
       </c>
       <c r="C38" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="D38" t="s">
         <v>108</v>
@@ -7423,10 +7500,10 @@
         <v>400</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -7440,16 +7517,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="D40" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E40" t="s">
         <v>110</v>
@@ -7460,16 +7537,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="D41" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E41" t="s">
         <v>110</v>
@@ -7480,16 +7557,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D42" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E42" t="s">
         <v>110</v>
@@ -7500,19 +7577,19 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="D43" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E43" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F43" t="b">
         <v>0</v>
@@ -7520,19 +7597,19 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="D44" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E44" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
@@ -7540,19 +7617,19 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D45" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E45" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -7560,19 +7637,19 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="D46" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E46" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
@@ -7580,19 +7657,19 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="D47" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E47" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -7600,19 +7677,19 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D48" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E48" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
@@ -7620,19 +7697,19 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="D49" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E49" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
@@ -7640,19 +7717,19 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="D50" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E50" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
@@ -7660,19 +7737,19 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
       <c r="C51" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D51" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E51" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F51" t="b">
         <v>0</v>
@@ -7680,19 +7757,19 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="D52" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E52" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
@@ -7700,19 +7777,19 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="D53" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E53" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
@@ -7720,19 +7797,19 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
       <c r="C54" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D54" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E54" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
@@ -7740,19 +7817,19 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="D55" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E55" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F55" t="b">
         <v>0</v>
@@ -7760,19 +7837,19 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="D56" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E56" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
@@ -7780,19 +7857,19 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="B57">
         <v>0</v>
       </c>
       <c r="C57" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D57" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E57" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
@@ -7800,19 +7877,19 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B58">
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="D58" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E58" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
@@ -7820,19 +7897,19 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="D59" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E59" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F59" t="b">
         <v>0</v>
@@ -7840,19 +7917,19 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="B60">
         <v>0</v>
       </c>
       <c r="C60" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D60" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E60" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F60" t="b">
         <v>0</v>
@@ -7860,19 +7937,19 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B61">
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="D61" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E61" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F61" t="b">
         <v>0</v>
@@ -7880,19 +7957,19 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="D62" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E62" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F62" t="b">
         <v>0</v>
@@ -7900,19 +7977,19 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D63" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E63" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F63" t="b">
         <v>0</v>
@@ -7920,16 +7997,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="D64" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E64" t="s">
         <v>390</v>
@@ -7940,16 +8017,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="D65" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E65" t="s">
         <v>390</v>
@@ -7960,16 +8037,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D66" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E66" t="s">
         <v>390</v>
@@ -7980,19 +8057,19 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="B67">
         <v>0.9423076923076923</v>
       </c>
       <c r="C67" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="D67" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E67" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F67" t="b">
         <v>0</v>
@@ -8000,19 +8077,19 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B68">
         <v>0.9876091402011571</v>
       </c>
       <c r="C68" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="D68" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E68" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F68" t="b">
         <v>0</v>
@@ -8020,19 +8097,19 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
       <c r="C69" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D69" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E69" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
@@ -8040,19 +8117,19 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="D70" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E70" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
@@ -8060,19 +8137,19 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
       <c r="C71" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="D71" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E71" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F71" t="b">
         <v>0</v>
@@ -8080,19 +8157,19 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="D72" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E72" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F72" t="b">
         <v>0</v>
@@ -8100,19 +8177,19 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="B73">
-        <v>0.5102040816326531</v>
+        <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="D73" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E73" t="s">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="F73" t="b">
         <v>0</v>
@@ -8120,19 +8197,19 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B74">
-        <v>0.294784807805392</v>
+        <v>1</v>
       </c>
       <c r="C74" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="D74" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E74" t="s">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
@@ -8140,26 +8217,86 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D75" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E75" t="s">
+        <v>435</v>
+      </c>
+      <c r="F75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" t="s">
+        <v>517</v>
+      </c>
+      <c r="B76">
+        <v>0.5408163265306123</v>
+      </c>
+      <c r="C76" t="s">
+        <v>540</v>
+      </c>
+      <c r="D76" t="s">
+        <v>465</v>
+      </c>
+      <c r="E76" t="s">
         <v>401</v>
       </c>
-      <c r="F75" t="b">
+      <c r="F76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" t="s">
+        <v>518</v>
+      </c>
+      <c r="B77">
+        <v>0.4689190577470169</v>
+      </c>
+      <c r="C77" t="s">
+        <v>541</v>
+      </c>
+      <c r="D77" t="s">
+        <v>465</v>
+      </c>
+      <c r="E77" t="s">
+        <v>401</v>
+      </c>
+      <c r="F77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" t="s">
+        <v>519</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78" t="s">
+        <v>533</v>
+      </c>
+      <c r="D78" t="s">
+        <v>465</v>
+      </c>
+      <c r="E78" t="s">
+        <v>401</v>
+      </c>
+      <c r="F78" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F75"/>
+  <autoFilter ref="A1:F78"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8177,16 +8314,16 @@
         <v>408</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8194,7 +8331,7 @@
         <v>110</v>
       </c>
       <c r="B2" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="C2" t="s">
         <v>109</v>
@@ -8203,15 +8340,15 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B3" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="C3" t="s">
         <v>123</v>
@@ -8220,15 +8357,15 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="C4" t="s">
         <v>124</v>
@@ -8237,15 +8374,15 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B5" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="C5" t="s">
         <v>125</v>
@@ -8254,15 +8391,15 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B6" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="C6" t="s">
         <v>126</v>
@@ -8271,15 +8408,15 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B7" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="C7" t="s">
         <v>127</v>
@@ -8288,15 +8425,15 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B8" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="C8" t="s">
         <v>128</v>
@@ -8305,15 +8442,15 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B9" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="C9" t="s">
         <v>129</v>
@@ -8322,7 +8459,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8330,7 +8467,7 @@
         <v>390</v>
       </c>
       <c r="B10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C10" t="s">
         <v>109</v>
@@ -8339,41 +8476,41 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B11" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C11" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="B12" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="C12" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -8442,25 +8579,25 @@
         <v>108</v>
       </c>
       <c r="D2">
-        <v>740.61</v>
+        <v>705.0599999999999</v>
       </c>
       <c r="E2" s="1">
-        <v>0.06444658435977413</v>
+        <v>0.01456240826546162</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2185695246557087</v>
+        <v>0.1602297223913507</v>
       </c>
       <c r="G2" s="1">
-        <v>0.1484339798758119</v>
+        <v>0.2346381697618982</v>
       </c>
       <c r="H2" s="1">
-        <v>-0.007438082984882577</v>
+        <v>-0.0550820199421036</v>
       </c>
       <c r="I2" s="1">
         <v>-0.1183474937620417</v>
       </c>
       <c r="J2">
-        <v>665.4643999999998</v>
+        <v>667.8092</v>
       </c>
     </row>
   </sheetData>
@@ -8509,7 +8646,7 @@
         <v>107</v>
       </c>
       <c r="D2">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="E2" t="s">
         <v>137</v>
@@ -8526,7 +8663,7 @@
         <v>107</v>
       </c>
       <c r="D3">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="E3" t="s">
         <v>137</v>
@@ -8574,7 +8711,7 @@
         <v>134</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6">
         <v>332.407</v>
@@ -8591,7 +8728,7 @@
         <v>135</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D7">
         <v>130.902</v>
@@ -8608,7 +8745,7 @@
         <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8">
         <v>4.3</v>
@@ -8657,7 +8794,7 @@
         <v>142</v>
       </c>
       <c r="B2">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="C2" t="s">
         <v>156</v>
@@ -8691,7 +8828,7 @@
         <v>144</v>
       </c>
       <c r="B4">
-        <v>-0.4100000000000001</v>
+        <v>-0.4199999999999999</v>
       </c>
       <c r="C4" t="s">
         <v>158</v>
@@ -8708,7 +8845,7 @@
         <v>145</v>
       </c>
       <c r="B5">
-        <v>0.4100000000000001</v>
+        <v>0.4199999999999999</v>
       </c>
       <c r="C5" t="s">
         <v>159</v>
@@ -8725,7 +8862,7 @@
         <v>146</v>
       </c>
       <c r="B6">
-        <v>-0.08999999999999986</v>
+        <v>-0.07999999999999963</v>
       </c>
       <c r="C6" t="s">
         <v>160</v>
@@ -8748,7 +8885,7 @@
         <v>161</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
         <v>137</v>
@@ -8765,7 +8902,7 @@
         <v>161</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
         <v>137</v>
@@ -8782,7 +8919,7 @@
         <v>161</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>137</v>
@@ -8799,7 +8936,7 @@
         <v>162</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
         <v>137</v>
@@ -8816,7 +8953,7 @@
         <v>163</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
         <v>137</v>
@@ -8833,7 +8970,7 @@
         <v>163</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
         <v>137</v>
@@ -8850,7 +8987,7 @@
         <v>163</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>137</v>
@@ -8867,7 +9004,7 @@
         <v>164</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>137</v>
@@ -8884,7 +9021,7 @@
         <v>165</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
         <v>137</v>
@@ -8936,7 +9073,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s">
         <v>171</v>
@@ -8959,7 +9096,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B3" t="s">
         <v>172</v>
@@ -8982,7 +9119,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B4" t="s">
         <v>173</v>
@@ -9005,7 +9142,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
         <v>174</v>
@@ -9028,7 +9165,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s">
         <v>175</v>
@@ -9051,7 +9188,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s">
         <v>176</v>
@@ -9074,7 +9211,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
         <v>177</v>
@@ -9097,7 +9234,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s">
         <v>178</v>
@@ -9120,7 +9257,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B10" t="s">
         <v>179</v>
@@ -9143,7 +9280,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s">
         <v>180</v>
@@ -9166,7 +9303,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B12" t="s">
         <v>181</v>
@@ -9189,7 +9326,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B13" t="s">
         <v>182</v>
@@ -9212,7 +9349,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B14" t="s">
         <v>183</v>
@@ -9235,7 +9372,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s">
         <v>184</v>
@@ -9258,7 +9395,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B16" t="s">
         <v>185</v>
@@ -9281,7 +9418,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B17" t="s">
         <v>186</v>
@@ -9304,7 +9441,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B18" t="s">
         <v>187</v>
@@ -9327,7 +9464,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B19" t="s">
         <v>188</v>
@@ -9350,7 +9487,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B20" t="s">
         <v>189</v>
@@ -9373,7 +9510,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B21" t="s">
         <v>190</v>
@@ -9396,7 +9533,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B22" t="s">
         <v>191</v>
@@ -9419,7 +9556,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B23" t="s">
         <v>192</v>
@@ -9442,7 +9579,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B24" t="s">
         <v>193</v>
@@ -9465,7 +9602,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B25" t="s">
         <v>194</v>
@@ -9488,7 +9625,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B26" t="s">
         <v>195</v>
@@ -9511,7 +9648,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B27" t="s">
         <v>196</v>
@@ -9534,7 +9671,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
         <v>197</v>
@@ -9557,7 +9694,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" t="s">
         <v>198</v>
@@ -9580,7 +9717,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B30" t="s">
         <v>199</v>
@@ -9603,7 +9740,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B31" t="s">
         <v>200</v>
@@ -9626,7 +9763,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B32" t="s">
         <v>201</v>
@@ -9649,7 +9786,7 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B33" t="s">
         <v>202</v>
@@ -9672,7 +9809,7 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B34" t="s">
         <v>203</v>
@@ -9695,7 +9832,7 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
         <v>204</v>
@@ -9718,7 +9855,7 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B36" t="s">
         <v>205</v>
@@ -9741,7 +9878,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B37" t="s">
         <v>206</v>
@@ -9764,7 +9901,7 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B38" t="s">
         <v>207</v>
@@ -9787,7 +9924,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B39" t="s">
         <v>208</v>
@@ -9810,7 +9947,7 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B40" t="s">
         <v>209</v>
@@ -9833,7 +9970,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B41" t="s">
         <v>210</v>
@@ -9856,7 +9993,7 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B42" t="s">
         <v>211</v>
@@ -9879,7 +10016,7 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B43" t="s">
         <v>212</v>
@@ -9902,7 +10039,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B44" t="s">
         <v>213</v>
@@ -9925,7 +10062,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B45" t="s">
         <v>214</v>
@@ -9948,7 +10085,7 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B46" t="s">
         <v>215</v>
@@ -9971,7 +10108,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B47" t="s">
         <v>216</v>
@@ -9994,7 +10131,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B48" t="s">
         <v>217</v>
@@ -10017,7 +10154,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
         <v>218</v>
@@ -10040,7 +10177,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B50" t="s">
         <v>219</v>
@@ -10063,7 +10200,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B51" t="s">
         <v>220</v>
@@ -10086,7 +10223,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B52" t="s">
         <v>221</v>
@@ -10109,7 +10246,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B53" t="s">
         <v>222</v>
@@ -10132,7 +10269,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
         <v>223</v>
@@ -10155,7 +10292,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B55" t="s">
         <v>224</v>
@@ -10178,7 +10315,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B56" t="s">
         <v>225</v>
@@ -10201,7 +10338,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B57" t="s">
         <v>226</v>
@@ -10224,7 +10361,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B58" t="s">
         <v>227</v>
@@ -10247,7 +10384,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B59" t="s">
         <v>228</v>
@@ -10270,7 +10407,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B60" t="s">
         <v>229</v>
@@ -10293,7 +10430,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B61" t="s">
         <v>230</v>
@@ -10316,7 +10453,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B62" t="s">
         <v>231</v>
@@ -10339,7 +10476,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B63" t="s">
         <v>232</v>
@@ -10362,7 +10499,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B64" t="s">
         <v>233</v>
@@ -10385,7 +10522,7 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B65" t="s">
         <v>234</v>
@@ -10408,7 +10545,7 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B66" t="s">
         <v>235</v>
@@ -10431,7 +10568,7 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B67" t="s">
         <v>236</v>
@@ -10454,7 +10591,7 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B68" t="s">
         <v>237</v>
@@ -10477,7 +10614,7 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B69" t="s">
         <v>238</v>
@@ -10500,7 +10637,7 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B70" t="s">
         <v>239</v>
@@ -10523,7 +10660,7 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B71" t="s">
         <v>240</v>
@@ -10546,7 +10683,7 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B72" t="s">
         <v>241</v>
@@ -10569,7 +10706,7 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B73" t="s">
         <v>242</v>
@@ -10592,7 +10729,7 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B74" t="s">
         <v>243</v>
@@ -10615,7 +10752,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B75" t="s">
         <v>244</v>
@@ -10638,7 +10775,7 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B76" t="s">
         <v>245</v>
@@ -10661,7 +10798,7 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B77" t="s">
         <v>246</v>
@@ -10684,7 +10821,7 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B78" t="s">
         <v>247</v>
@@ -10707,7 +10844,7 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B79" t="s">
         <v>248</v>
@@ -10730,7 +10867,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B80" t="s">
         <v>249</v>
@@ -10753,7 +10890,7 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B81" t="s">
         <v>250</v>
@@ -10776,7 +10913,7 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B82" t="s">
         <v>251</v>
@@ -10799,7 +10936,7 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B83" t="s">
         <v>252</v>
@@ -10822,7 +10959,7 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B84" t="s">
         <v>253</v>
@@ -10845,7 +10982,7 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B85" t="s">
         <v>254</v>
@@ -10868,7 +11005,7 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B86" t="s">
         <v>255</v>
@@ -10891,7 +11028,7 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B87" t="s">
         <v>256</v>
@@ -10914,7 +11051,7 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B88" t="s">
         <v>257</v>
@@ -10937,7 +11074,7 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B89" t="s">
         <v>258</v>
@@ -10960,7 +11097,7 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B90" t="s">
         <v>259</v>
@@ -10983,7 +11120,7 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B91" t="s">
         <v>260</v>
@@ -11006,7 +11143,7 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B92" t="s">
         <v>261</v>
@@ -11029,7 +11166,7 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B93" t="s">
         <v>262</v>
@@ -11052,7 +11189,7 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B94" t="s">
         <v>263</v>
@@ -11075,7 +11212,7 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B95" t="s">
         <v>264</v>
@@ -11098,7 +11235,7 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B96" t="s">
         <v>265</v>
@@ -11121,7 +11258,7 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B97" t="s">
         <v>266</v>
@@ -11144,7 +11281,7 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B98" t="s">
         <v>267</v>
@@ -11167,7 +11304,7 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B99" t="s">
         <v>268</v>
@@ -11190,7 +11327,7 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B100" t="s">
         <v>269</v>
@@ -11213,7 +11350,7 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B101" t="s">
         <v>270</v>
@@ -11236,7 +11373,7 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B102" t="s">
         <v>271</v>
@@ -11259,7 +11396,7 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B103" t="s">
         <v>272</v>
@@ -11282,7 +11419,7 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B104" t="s">
         <v>273</v>
@@ -11305,7 +11442,7 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B105" t="s">
         <v>274</v>
@@ -11372,7 +11509,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s">
         <v>171</v>
@@ -11395,7 +11532,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B3" t="s">
         <v>172</v>
@@ -11418,7 +11555,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B4" t="s">
         <v>173</v>
@@ -11441,7 +11578,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
         <v>174</v>
@@ -11464,7 +11601,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s">
         <v>175</v>
@@ -11487,7 +11624,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s">
         <v>176</v>
@@ -11510,7 +11647,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
         <v>177</v>
@@ -11533,7 +11670,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s">
         <v>178</v>
@@ -11556,7 +11693,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B10" t="s">
         <v>179</v>
@@ -11579,7 +11716,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s">
         <v>180</v>
@@ -11602,7 +11739,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B12" t="s">
         <v>181</v>
@@ -11625,7 +11762,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B13" t="s">
         <v>182</v>
@@ -11648,7 +11785,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B14" t="s">
         <v>183</v>
@@ -11671,7 +11808,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s">
         <v>184</v>
@@ -11694,7 +11831,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B16" t="s">
         <v>185</v>
@@ -11717,7 +11854,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B17" t="s">
         <v>186</v>
@@ -11740,7 +11877,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B18" t="s">
         <v>187</v>
@@ -11763,7 +11900,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B19" t="s">
         <v>188</v>
@@ -11786,7 +11923,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B20" t="s">
         <v>189</v>
@@ -11809,7 +11946,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B21" t="s">
         <v>190</v>
@@ -11832,7 +11969,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B22" t="s">
         <v>191</v>
@@ -11855,7 +11992,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B23" t="s">
         <v>192</v>
@@ -11878,7 +12015,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B24" t="s">
         <v>193</v>
@@ -11901,7 +12038,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B25" t="s">
         <v>194</v>
@@ -11924,7 +12061,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B26" t="s">
         <v>195</v>
@@ -11947,7 +12084,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B27" t="s">
         <v>196</v>
@@ -11970,7 +12107,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
         <v>197</v>
@@ -11993,7 +12130,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" t="s">
         <v>198</v>
@@ -12016,7 +12153,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B30" t="s">
         <v>199</v>
@@ -12039,7 +12176,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B31" t="s">
         <v>200</v>
@@ -12062,7 +12199,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B32" t="s">
         <v>201</v>
@@ -12085,7 +12222,7 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B33" t="s">
         <v>202</v>
@@ -12108,7 +12245,7 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B34" t="s">
         <v>203</v>
@@ -12131,7 +12268,7 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
         <v>204</v>
@@ -12154,7 +12291,7 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B36" t="s">
         <v>205</v>
@@ -12177,7 +12314,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B37" t="s">
         <v>207</v>
@@ -12200,7 +12337,7 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B38" t="s">
         <v>208</v>
@@ -12223,7 +12360,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B39" t="s">
         <v>209</v>
@@ -12246,7 +12383,7 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B40" t="s">
         <v>210</v>
@@ -12269,7 +12406,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B41" t="s">
         <v>211</v>
@@ -12292,7 +12429,7 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B42" t="s">
         <v>212</v>
@@ -12315,7 +12452,7 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B43" t="s">
         <v>213</v>
@@ -12338,7 +12475,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B44" t="s">
         <v>214</v>
@@ -12361,7 +12498,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B45" t="s">
         <v>215</v>
@@ -12384,7 +12521,7 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B46" t="s">
         <v>216</v>
@@ -12407,7 +12544,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B47" t="s">
         <v>217</v>
@@ -12430,7 +12567,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B48" t="s">
         <v>218</v>
@@ -12453,7 +12590,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
         <v>219</v>
@@ -12476,7 +12613,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B50" t="s">
         <v>220</v>
@@ -12499,7 +12636,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B51" t="s">
         <v>221</v>
@@ -12522,7 +12659,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B52" t="s">
         <v>222</v>
@@ -12545,7 +12682,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B53" t="s">
         <v>223</v>
@@ -12568,7 +12705,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
         <v>224</v>
@@ -12591,7 +12728,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B55" t="s">
         <v>225</v>
@@ -12614,7 +12751,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B56" t="s">
         <v>226</v>
@@ -12637,7 +12774,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B57" t="s">
         <v>227</v>
@@ -12660,7 +12797,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B58" t="s">
         <v>228</v>
@@ -12683,7 +12820,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B59" t="s">
         <v>229</v>
@@ -12706,7 +12843,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B60" t="s">
         <v>230</v>
@@ -12729,7 +12866,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B61" t="s">
         <v>231</v>
@@ -12752,7 +12889,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B62" t="s">
         <v>232</v>
@@ -12775,7 +12912,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B63" t="s">
         <v>233</v>
@@ -12798,7 +12935,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B64" t="s">
         <v>234</v>
@@ -12821,7 +12958,7 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B65" t="s">
         <v>235</v>
@@ -12844,7 +12981,7 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B66" t="s">
         <v>236</v>
@@ -12867,7 +13004,7 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B67" t="s">
         <v>237</v>
@@ -12890,7 +13027,7 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B68" t="s">
         <v>238</v>
@@ -12913,7 +13050,7 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B69" t="s">
         <v>240</v>
@@ -12936,7 +13073,7 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B70" t="s">
         <v>241</v>
@@ -12959,7 +13096,7 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B71" t="s">
         <v>243</v>
@@ -12982,7 +13119,7 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B72" t="s">
         <v>244</v>
@@ -13005,7 +13142,7 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B73" t="s">
         <v>245</v>
@@ -13028,7 +13165,7 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B74" t="s">
         <v>246</v>
@@ -13051,7 +13188,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B75" t="s">
         <v>247</v>
@@ -13074,7 +13211,7 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B76" t="s">
         <v>248</v>
@@ -13097,7 +13234,7 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B77" t="s">
         <v>249</v>
@@ -13120,7 +13257,7 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B78" t="s">
         <v>250</v>
@@ -13143,7 +13280,7 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B79" t="s">
         <v>251</v>
@@ -13166,7 +13303,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B80" t="s">
         <v>252</v>
@@ -13189,7 +13326,7 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B81" t="s">
         <v>253</v>
@@ -13212,7 +13349,7 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B82" t="s">
         <v>254</v>
@@ -13235,7 +13372,7 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B83" t="s">
         <v>255</v>
@@ -13258,7 +13395,7 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B84" t="s">
         <v>256</v>
@@ -13281,7 +13418,7 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B85" t="s">
         <v>257</v>
@@ -13304,7 +13441,7 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B86" t="s">
         <v>258</v>
@@ -13327,7 +13464,7 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B87" t="s">
         <v>259</v>
@@ -13350,7 +13487,7 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B88" t="s">
         <v>260</v>
@@ -13373,7 +13510,7 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B89" t="s">
         <v>261</v>
@@ -13396,7 +13533,7 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B90" t="s">
         <v>262</v>
@@ -13419,7 +13556,7 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B91" t="s">
         <v>263</v>
@@ -13442,7 +13579,7 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B92" t="s">
         <v>264</v>
@@ -13465,7 +13602,7 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B93" t="s">
         <v>265</v>
@@ -13488,7 +13625,7 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B94" t="s">
         <v>266</v>
@@ -13511,7 +13648,7 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B95" t="s">
         <v>267</v>
@@ -13534,7 +13671,7 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B96" t="s">
         <v>268</v>
@@ -13557,7 +13694,7 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B97" t="s">
         <v>269</v>
@@ -13580,7 +13717,7 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B98" t="s">
         <v>270</v>
@@ -13603,7 +13740,7 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B99" t="s">
         <v>272</v>
@@ -13668,10 +13805,10 @@
         <v>393</v>
       </c>
       <c r="B2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
         <v>108</v>
@@ -13688,10 +13825,10 @@
         <v>394</v>
       </c>
       <c r="B3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
         <v>108</v>
@@ -13708,10 +13845,10 @@
         <v>395</v>
       </c>
       <c r="B4">
-        <v>0.58</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="C4">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
         <v>108</v>
@@ -13728,10 +13865,10 @@
         <v>396</v>
       </c>
       <c r="B5">
-        <v>0.58</v>
+        <v>0.5849056603773585</v>
       </c>
       <c r="C5">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
         <v>108</v>
@@ -13748,10 +13885,10 @@
         <v>397</v>
       </c>
       <c r="B6">
-        <v>0.58</v>
+        <v>0.6037735849056604</v>
       </c>
       <c r="C6">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
         <v>108</v>
@@ -13768,10 +13905,10 @@
         <v>398</v>
       </c>
       <c r="B7">
-        <v>0.66</v>
+        <v>0.660377358490566</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
         <v>108</v>
@@ -13791,7 +13928,7 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
         <v>108</v>
@@ -13808,10 +13945,10 @@
         <v>400</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
         <v>108</v>
@@ -13891,8 +14028,23 @@
       <c r="C2">
         <v>0.08433591</v>
       </c>
+      <c r="D2">
+        <v>205.10001</v>
+      </c>
+      <c r="E2">
+        <v>-13.56</v>
+      </c>
+      <c r="F2">
+        <v>-6.20141</v>
+      </c>
+      <c r="J2" t="s">
+        <v>410</v>
+      </c>
+      <c r="K2">
+        <v>1780666200</v>
+      </c>
       <c r="L2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -13905,8 +14057,23 @@
       <c r="C3">
         <v>0.07244038999999999</v>
       </c>
+      <c r="D3">
+        <v>307.34</v>
+      </c>
+      <c r="E3">
+        <v>-3.89001</v>
+      </c>
+      <c r="F3">
+        <v>-1.24988</v>
+      </c>
+      <c r="J3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K3">
+        <v>1780666200</v>
+      </c>
       <c r="L3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -13919,8 +14086,23 @@
       <c r="C4">
         <v>0.05049571</v>
       </c>
+      <c r="D4">
+        <v>416.67001</v>
+      </c>
+      <c r="E4">
+        <v>-11.37997</v>
+      </c>
+      <c r="F4">
+        <v>-2.65856</v>
+      </c>
+      <c r="J4" t="s">
+        <v>410</v>
+      </c>
+      <c r="K4">
+        <v>1780666200</v>
+      </c>
       <c r="L4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -13933,8 +14115,23 @@
       <c r="C5">
         <v>0.04905769</v>
       </c>
+      <c r="D5">
+        <v>864.01001</v>
+      </c>
+      <c r="E5">
+        <v>-131.98999</v>
+      </c>
+      <c r="F5">
+        <v>-13.25201</v>
+      </c>
+      <c r="J5" t="s">
+        <v>410</v>
+      </c>
+      <c r="K5">
+        <v>1780666200</v>
+      </c>
       <c r="L5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -13947,8 +14144,23 @@
       <c r="C6">
         <v>0.04319211</v>
       </c>
+      <c r="D6">
+        <v>246.029999</v>
+      </c>
+      <c r="E6">
+        <v>-7.75999</v>
+      </c>
+      <c r="F6">
+        <v>-3.057644</v>
+      </c>
+      <c r="J6" t="s">
+        <v>410</v>
+      </c>
+      <c r="K6">
+        <v>1780666200</v>
+      </c>
       <c r="L6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -13961,8 +14173,23 @@
       <c r="C7">
         <v>0.03732949</v>
       </c>
+      <c r="D7">
+        <v>466.38</v>
+      </c>
+      <c r="E7">
+        <v>-56.82001</v>
+      </c>
+      <c r="F7">
+        <v>-10.86009</v>
+      </c>
+      <c r="J7" t="s">
+        <v>410</v>
+      </c>
+      <c r="K7">
+        <v>1780666200</v>
+      </c>
       <c r="L7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -13975,8 +14202,23 @@
       <c r="C8">
         <v>0.03434837</v>
       </c>
+      <c r="D8">
+        <v>368.53</v>
+      </c>
+      <c r="E8">
+        <v>-3.66</v>
+      </c>
+      <c r="F8">
+        <v>-0.98336969</v>
+      </c>
+      <c r="J8" t="s">
+        <v>410</v>
+      </c>
+      <c r="K8">
+        <v>1780666200</v>
+      </c>
       <c r="L8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -13989,8 +14231,23 @@
       <c r="C9">
         <v>0.03310853</v>
       </c>
+      <c r="D9">
+        <v>391</v>
+      </c>
+      <c r="E9">
+        <v>-27.45001</v>
+      </c>
+      <c r="F9">
+        <v>-6.55993</v>
+      </c>
+      <c r="J9" t="s">
+        <v>410</v>
+      </c>
+      <c r="K9">
+        <v>1780666200</v>
+      </c>
       <c r="L9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -14003,8 +14260,23 @@
       <c r="C10">
         <v>0.03183849</v>
       </c>
+      <c r="D10">
+        <v>365.76001</v>
+      </c>
+      <c r="E10">
+        <v>-3.50998</v>
+      </c>
+      <c r="F10">
+        <v>-0.95051842</v>
+      </c>
+      <c r="J10" t="s">
+        <v>410</v>
+      </c>
+      <c r="K10">
+        <v>1780666200</v>
+      </c>
       <c r="L10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -14017,8 +14289,23 @@
       <c r="C11">
         <v>0.0314861</v>
       </c>
+      <c r="D11">
+        <v>385.73001</v>
+      </c>
+      <c r="E11">
+        <v>-33.17999</v>
+      </c>
+      <c r="F11">
+        <v>-7.92055</v>
+      </c>
+      <c r="J11" t="s">
+        <v>410</v>
+      </c>
+      <c r="K11">
+        <v>1780666200</v>
+      </c>
       <c r="L11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -14031,8 +14318,23 @@
       <c r="C12">
         <v>0.02934593</v>
       </c>
+      <c r="D12">
+        <v>593</v>
+      </c>
+      <c r="E12">
+        <v>-34.57001</v>
+      </c>
+      <c r="F12">
+        <v>-5.50855</v>
+      </c>
+      <c r="J12" t="s">
+        <v>410</v>
+      </c>
+      <c r="K12">
+        <v>1780666200</v>
+      </c>
       <c r="L12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -14045,8 +14347,23 @@
       <c r="C13">
         <v>0.02518224</v>
       </c>
+      <c r="D13">
+        <v>118.88</v>
+      </c>
+      <c r="E13">
+        <v>1.14</v>
+      </c>
+      <c r="F13">
+        <v>0.96823459</v>
+      </c>
+      <c r="J13" t="s">
+        <v>410</v>
+      </c>
+      <c r="K13">
+        <v>1780666200</v>
+      </c>
       <c r="L13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -14059,8 +14376,23 @@
       <c r="C14">
         <v>0.0244368</v>
       </c>
+      <c r="D14">
+        <v>99.17</v>
+      </c>
+      <c r="E14">
+        <v>-12.61</v>
+      </c>
+      <c r="F14">
+        <v>-11.28109</v>
+      </c>
+      <c r="J14" t="s">
+        <v>410</v>
+      </c>
+      <c r="K14">
+        <v>1780666200</v>
+      </c>
       <c r="L14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -14073,8 +14405,23 @@
       <c r="C15">
         <v>0.02247381</v>
       </c>
+      <c r="D15">
+        <v>121.64</v>
+      </c>
+      <c r="E15">
+        <v>-8.359999999999999</v>
+      </c>
+      <c r="F15">
+        <v>-6.43077</v>
+      </c>
+      <c r="J15" t="s">
+        <v>410</v>
+      </c>
+      <c r="K15">
+        <v>1780666200</v>
+      </c>
       <c r="L15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -14087,8 +14434,23 @@
       <c r="C16">
         <v>0.01889016</v>
       </c>
+      <c r="D16">
+        <v>971.87</v>
+      </c>
+      <c r="E16">
+        <v>-0.47998047</v>
+      </c>
+      <c r="F16">
+        <v>-0.049362933</v>
+      </c>
+      <c r="J16" t="s">
+        <v>410</v>
+      </c>
+      <c r="K16">
+        <v>1780666200</v>
+      </c>
       <c r="L16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -14101,8 +14463,23 @@
       <c r="C17">
         <v>0.01837787</v>
       </c>
+      <c r="D17">
+        <v>303.28</v>
+      </c>
+      <c r="E17">
+        <v>-33.13</v>
+      </c>
+      <c r="F17">
+        <v>-9.848100000000001</v>
+      </c>
+      <c r="J17" t="s">
+        <v>410</v>
+      </c>
+      <c r="K17">
+        <v>1780666200</v>
+      </c>
       <c r="L17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -14115,8 +14492,23 @@
       <c r="C18">
         <v>0.01743618</v>
       </c>
+      <c r="D18">
+        <v>453.01001</v>
+      </c>
+      <c r="E18">
+        <v>-48.69</v>
+      </c>
+      <c r="F18">
+        <v>-9.705</v>
+      </c>
+      <c r="J18" t="s">
+        <v>410</v>
+      </c>
+      <c r="K18">
+        <v>1780666200</v>
+      </c>
       <c r="L18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -14129,8 +14521,23 @@
       <c r="C19">
         <v>0.01506454</v>
       </c>
+      <c r="D19">
+        <v>82.18000000000001</v>
+      </c>
+      <c r="E19">
+        <v>0.62000275</v>
+      </c>
+      <c r="F19">
+        <v>0.76017995</v>
+      </c>
+      <c r="J19" t="s">
+        <v>410</v>
+      </c>
+      <c r="K19">
+        <v>1780666200</v>
+      </c>
       <c r="L19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -14143,8 +14550,23 @@
       <c r="C20">
         <v>0.01420458</v>
       </c>
+      <c r="D20">
+        <v>135.53</v>
+      </c>
+      <c r="E20">
+        <v>-6.17</v>
+      </c>
+      <c r="F20">
+        <v>-4.35427</v>
+      </c>
+      <c r="J20" t="s">
+        <v>410</v>
+      </c>
+      <c r="K20">
+        <v>1780666200</v>
+      </c>
       <c r="L20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -14157,8 +14579,23 @@
       <c r="C21">
         <v>0.01221992</v>
       </c>
+      <c r="D21">
+        <v>1929.19995</v>
+      </c>
+      <c r="E21">
+        <v>-201.90015</v>
+      </c>
+      <c r="F21">
+        <v>-9.473990000000001</v>
+      </c>
+      <c r="J21" t="s">
+        <v>410</v>
+      </c>
+      <c r="K21">
+        <v>1780666200</v>
+      </c>
       <c r="L21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14169,7 +14606,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="12.7109375" customWidth="1"/>
@@ -14186,54 +14623,54 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>408</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B2" t="s">
         <v>110</v>
@@ -14266,15 +14703,15 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -14304,15 +14741,15 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
@@ -14342,15 +14779,15 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
@@ -14380,15 +14817,15 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -14418,15 +14855,15 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -14456,15 +14893,15 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B8" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
@@ -14494,15 +14931,15 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B9" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -14532,12 +14969,12 @@
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B10" t="s">
         <v>390</v>
@@ -14570,15 +15007,15 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>
@@ -14593,7 +15030,7 @@
         <v>0.9876091402011571</v>
       </c>
       <c r="G11" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -14611,15 +15048,15 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B12" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
@@ -14634,13 +15071,13 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="I12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -14652,58 +15089,99 @@
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B13" t="s">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
       </c>
       <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>410</v>
+      </c>
+      <c r="O13" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>431</v>
+      </c>
+      <c r="B14" t="s">
+        <v>401</v>
+      </c>
+      <c r="C14" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14">
         <v>8</v>
       </c>
-      <c r="E13">
-        <v>0.5102040816326531</v>
-      </c>
-      <c r="F13">
-        <v>0.294784807805392</v>
-      </c>
-      <c r="G13" t="s">
-        <v>435</v>
-      </c>
-      <c r="H13" t="s">
-        <v>436</v>
-      </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>14400</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>437</v>
-      </c>
-      <c r="O13" t="s">
-        <v>449</v>
+      <c r="E14">
+        <v>0.5408163265306123</v>
+      </c>
+      <c r="F14">
+        <v>0.4689190577470169</v>
+      </c>
+      <c r="G14" t="s">
+        <v>438</v>
+      </c>
+      <c r="H14" t="s">
+        <v>439</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>15264</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>440</v>
+      </c>
+      <c r="O14" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O13"/>
+  <autoFilter ref="A1:O14"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/reports/latest/nasdaq100_qqq_daily_tracker.xlsx
+++ b/reports/latest/nasdaq100_qqq_daily_tracker.xlsx
@@ -33,7 +33,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">宏观指标!$A$1:$E$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">市场广度!$A$1:$F$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">数据质量!$A$1:$O$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">模型输入指标!$A$1:$F$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">模型输入指标!$A$1:$H$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">运行日志!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2614" uniqueCount="562">
   <si>
     <t>date</t>
   </si>
@@ -1357,6 +1357,9 @@
     <t>NVDA,AAPL,MSFT,MU,AMZN,AMD,GOOGL,TSLA,GOOG,AVGO,META,WMT,INTC,CSCO,COST,LRCX,AMAT,NFLX,PLTR,KLAC,TXN,MRVL,QCOM,SNDK,LIN,PANW,ADI,STX,TMUS,WDC,PEP,AMGN,CRWD,APP,GILD,ISRG,SHOP,HON,BKNG,CDNS,VRTX,FTNT,SBUX,ADBE,MAR,CEG,SNPS,ADP,MNST,CSX,CMCSA,INTU,MELI,NXPI,MPWR,DDOG,MDLZ,ROST,ORLY,CTAS,AEP,LITE,WBD,DASH,BKR,REGN,PCAR,FANG,ABNB,FAST,MCHP,ODFL,EA,ADSK,XEL,FER,EXC,IDXX,CCEP,AXON,KDP,MSTR,ALNY,TTWO,PYPL,TRI,PAYX,ROP,WDAY,CPRT,GEHC,DXCM,KHC,CTSH,VRSK,INSM,ZS,CHTR</t>
   </si>
   <si>
+    <t>GOOG,AVGO</t>
+  </si>
+  <si>
     <t>ADI,ALNY,AMAT,AMD,AMZN,AVGO,AXON,CCEP,CHTR,COST,CPRT,CSCO,CTSH,DXCM,GEHC,GOOG,GOOGL,IDXX,INSM,INTC,KDP,KHC,KLAC,LIN,LRCX,META,MRVL,MSTR,NFLX,PANW,PAYX,PLTR,PYPL,QCOM,ROP,SNDK,STX,TRI,TSLA,TTWO,TXN,VRSK,WDAY,WMT,ZS</t>
   </si>
   <si>
@@ -1399,7 +1402,7 @@
     <t>0/98 quotes fetched</t>
   </si>
   <si>
-    <t>20/20 top20 quotes available; 10/10 top10 quotes available</t>
+    <t>18/20 top20 quotes available; 8/10 top10 quotes available</t>
   </si>
   <si>
     <t>53/98 symbols with history+quote coverage; coverage insufficient for top-weight symbols</t>
@@ -1480,6 +1483,9 @@
     <t>NVDA,AAPL,MSFT,MU,AMZN,AMD,GOOGL,TSLA,GOOG,AVGO,META,WMT,INTC,CSCO,COST,LRCX,AMAT,NFLX,PLTR,KLAC</t>
   </si>
   <si>
+    <t>NVDA,AAPL,MSFT,MU,AMZN,AMD,GOOGL,TSLA,META,WMT,INTC,CSCO,COST,LRCX,AMAT,NFLX,PLTR,KLAC</t>
+  </si>
+  <si>
     <t>DGS10: DGS10: 365 rows; DGS2: DGS2: 365 rows; DGS3MO: DGS3MO: 365 rows; ...</t>
   </si>
   <si>
@@ -1495,6 +1501,15 @@
     <t>provider not called in this daily pipeline run</t>
   </si>
   <si>
+    <t>metric_date</t>
+  </si>
+  <si>
+    <t>coverage_ratio</t>
+  </si>
+  <si>
+    <t>quality_message</t>
+  </si>
+  <si>
     <t>QQQ_latest_close</t>
   </si>
   <si>
@@ -1603,6 +1618,15 @@
     <t>breadth_metrics_fmp+tiingo_cache_rate_limited</t>
   </si>
   <si>
+    <t>price_metrics</t>
+  </si>
+  <si>
+    <t>macro_metrics</t>
+  </si>
+  <si>
+    <t>data_quality</t>
+  </si>
+  <si>
     <t>latest adjusted close</t>
   </si>
   <si>
@@ -1636,40 +1660,55 @@
     <t>breadth metric; denominator=53</t>
   </si>
   <si>
-    <t>data quality symbol coverage; ok=True; rows=100</t>
-  </si>
-  <si>
-    <t>data quality weight coverage; rate_limited=False; fallback_provider=</t>
-  </si>
-  <si>
-    <t>1 means provider hit 429 and breadth stopped_after_429=False</t>
-  </si>
-  <si>
-    <t>data quality symbol coverage; ok=True; rows=365</t>
-  </si>
-  <si>
-    <t>data quality symbol coverage; ok=True; rows=104</t>
-  </si>
-  <si>
-    <t>data quality symbol coverage; ok=True; rows=98</t>
-  </si>
-  <si>
-    <t>data quality symbol coverage; ok=False; rows=98</t>
-  </si>
-  <si>
-    <t>data quality symbol coverage; ok=True; rows=20</t>
-  </si>
-  <si>
-    <t>data quality weight coverage; rate_limited=False; fallback_provider=twelve_data</t>
-  </si>
-  <si>
-    <t>data quality symbol coverage; ok=True; rows=8</t>
-  </si>
-  <si>
-    <t>data quality weight coverage; rate_limited=False; fallback_provider=mixed_fmp+tiingo_history_only</t>
-  </si>
-  <si>
-    <t>FMP</t>
+    <t>symbol coverage; ok=True; rows=100; message=QQQ: 100 rows</t>
+  </si>
+  <si>
+    <t>weight coverage; rate_limited=False; fallback_provider=</t>
+  </si>
+  <si>
+    <t>1 means provider hit a limit; stopped_after_429=False</t>
+  </si>
+  <si>
+    <t>symbol coverage; ok=True; rows=365; message=DGS10: 365 rows</t>
+  </si>
+  <si>
+    <t>symbol coverage; ok=True; rows=365; message=DGS2: 365 rows</t>
+  </si>
+  <si>
+    <t>symbol coverage; ok=True; rows=365; message=DGS3MO: 365 rows</t>
+  </si>
+  <si>
+    <t>symbol coverage; ok=True; rows=365; message=DFF: 365 rows</t>
+  </si>
+  <si>
+    <t>symbol coverage; ok=True; rows=365; message=CPIAUCSL: 365 rows</t>
+  </si>
+  <si>
+    <t>symbol coverage; ok=True; rows=365; message=PCEPI: 365 rows</t>
+  </si>
+  <si>
+    <t>symbol coverage; ok=True; rows=365; message=UNRATE: 365 rows</t>
+  </si>
+  <si>
+    <t>symbol coverage; ok=True; rows=104; message=QQQ: holdings rows=104 effective_date=2026-06-04</t>
+  </si>
+  <si>
+    <t>symbol coverage; ok=True; rows=98; message=equity filter applied for breadth stock pool</t>
+  </si>
+  <si>
+    <t>symbol coverage; ok=False; rows=98; message=0/98 quotes fetched</t>
+  </si>
+  <si>
+    <t>symbol coverage; ok=True; rows=20; message=18/20 top20 quotes available; 8/10 top10 quotes available</t>
+  </si>
+  <si>
+    <t>weight coverage; rate_limited=False; fallback_provider=twelve_data</t>
+  </si>
+  <si>
+    <t>symbol coverage; ok=True; rows=8; message=53/98 symbols with history+quote coverage; coverage insufficient for top-weight symbols</t>
+  </si>
+  <si>
+    <t>weight coverage; rate_limited=False; fallback_provider=mixed_fmp+tiingo_history_only</t>
   </si>
   <si>
     <t>method</t>
@@ -5019,46 +5058,46 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>408</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>418</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>419</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>424</v>
@@ -5066,13 +5105,13 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B2" t="s">
         <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -5087,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I2">
         <v>25</v>
@@ -5105,18 +5144,18 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B3" t="s">
         <v>432</v>
       </c>
       <c r="C3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D3">
         <v>7</v>
@@ -5131,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I3">
         <v>10</v>
@@ -5140,21 +5179,21 @@
         <v>7</v>
       </c>
       <c r="K3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B4" t="s">
         <v>390</v>
@@ -5175,7 +5214,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I4">
         <v>3</v>
@@ -5193,18 +5232,18 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B5" t="s">
         <v>434</v>
       </c>
       <c r="C5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -5219,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I5">
         <v>250</v>
@@ -5228,39 +5267,39 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B6" t="s">
         <v>410</v>
       </c>
       <c r="C6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D6">
         <v>20</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I6">
         <v>8</v>
@@ -5269,27 +5308,27 @@
         <v>20</v>
       </c>
       <c r="K6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M6" t="b">
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -5304,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I7">
         <v>50</v>
@@ -5316,7 +5355,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -5358,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5372,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5386,7 +5425,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5400,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -5414,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5428,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5442,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5456,7 +5495,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5470,7 +5509,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -5484,7 +5523,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -5498,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5512,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -5526,7 +5565,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -5540,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -5554,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -5568,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -5582,7 +5621,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -5596,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -5610,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -5624,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -5638,7 +5677,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -5652,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5666,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -5680,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -5694,7 +5733,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -5708,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -5722,7 +5761,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -5736,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -5750,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -5764,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -5778,7 +5817,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -5792,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -5806,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -5820,7 +5859,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5834,7 +5873,7 @@
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5848,7 +5887,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -5862,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -5876,7 +5915,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -5890,7 +5929,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -5904,7 +5943,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -5918,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -5932,7 +5971,7 @@
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -5946,7 +5985,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -5960,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -5974,7 +6013,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -5988,7 +6027,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -6002,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -6016,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -6030,7 +6069,7 @@
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -6044,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -6058,7 +6097,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -6072,7 +6111,7 @@
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -6086,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -6100,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -6114,7 +6153,7 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -6128,7 +6167,7 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -6142,7 +6181,7 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -6156,7 +6195,7 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -6170,7 +6209,7 @@
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -6184,7 +6223,7 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -6198,7 +6237,7 @@
         <v>0</v>
       </c>
       <c r="D62" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -6212,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="D63" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -6226,7 +6265,7 @@
         <v>0</v>
       </c>
       <c r="D64" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -6240,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -6254,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="D66" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -6268,7 +6307,7 @@
         <v>0</v>
       </c>
       <c r="D67" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -6282,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="D68" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -6296,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="D69" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -6310,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="D70" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -6324,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="D71" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -6338,7 +6377,7 @@
         <v>0</v>
       </c>
       <c r="D72" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -6352,7 +6391,7 @@
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -6366,7 +6405,7 @@
         <v>0</v>
       </c>
       <c r="D74" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -6380,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -6394,7 +6433,7 @@
         <v>0</v>
       </c>
       <c r="D76" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -6408,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="D77" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -6422,7 +6461,7 @@
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -6436,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="D79" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -6450,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="D80" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -6464,7 +6503,7 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -6478,7 +6517,7 @@
         <v>0</v>
       </c>
       <c r="D82" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -6492,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -6506,7 +6545,7 @@
         <v>0</v>
       </c>
       <c r="D84" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -6520,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -6534,7 +6573,7 @@
         <v>0</v>
       </c>
       <c r="D86" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -6548,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -6562,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -6576,7 +6615,7 @@
         <v>0</v>
       </c>
       <c r="D89" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -6590,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -6604,7 +6643,7 @@
         <v>0</v>
       </c>
       <c r="D91" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -6618,7 +6657,7 @@
         <v>0</v>
       </c>
       <c r="D92" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -6632,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -6646,7 +6685,7 @@
         <v>0</v>
       </c>
       <c r="D94" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -6660,7 +6699,7 @@
         <v>0</v>
       </c>
       <c r="D95" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -6674,7 +6713,7 @@
         <v>0</v>
       </c>
       <c r="D96" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -6688,7 +6727,7 @@
         <v>0</v>
       </c>
       <c r="D97" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -6702,7 +6741,7 @@
         <v>0</v>
       </c>
       <c r="D98" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -6716,7 +6755,7 @@
         <v>0</v>
       </c>
       <c r="D99" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -6727,18 +6766,19 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>138</v>
       </c>
@@ -6746,176 +6786,206 @@
         <v>139</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>140</v>
+        <v>486</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>141</v>
+        <v>8</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>8</v>
+        <v>408</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="H1" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B2">
         <v>705.0599999999999</v>
       </c>
       <c r="C2" t="s">
-        <v>520</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>525</v>
       </c>
       <c r="E2" t="s">
         <v>110</v>
       </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B3">
         <v>0.01456240826546162</v>
       </c>
       <c r="C3" t="s">
-        <v>521</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>525</v>
       </c>
       <c r="E3" t="s">
         <v>110</v>
       </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B4">
         <v>0.1602297223913507</v>
       </c>
       <c r="C4" t="s">
-        <v>522</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>525</v>
       </c>
       <c r="E4" t="s">
         <v>110</v>
       </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B5">
         <v>0.2346381697618982</v>
       </c>
       <c r="C5" t="s">
-        <v>523</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>525</v>
       </c>
       <c r="E5" t="s">
         <v>110</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B6">
         <v>-0.0550820199421036</v>
       </c>
       <c r="C6" t="s">
-        <v>524</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>525</v>
       </c>
       <c r="E6" t="s">
         <v>110</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B7">
         <v>-0.1183474937620417</v>
       </c>
       <c r="C7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" t="s">
         <v>525</v>
-      </c>
-      <c r="D7" t="s">
-        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>110</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B8">
         <v>667.8092</v>
       </c>
       <c r="C8" t="s">
-        <v>526</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>525</v>
       </c>
       <c r="E8" t="s">
         <v>110</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="C9" t="s">
-        <v>527</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>525</v>
       </c>
       <c r="E9" t="s">
         <v>110</v>
       </c>
-      <c r="F9" t="b">
+      <c r="G9" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="H9" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>142</v>
       </c>
@@ -6923,139 +6993,160 @@
         <v>4.47</v>
       </c>
       <c r="C10" t="s">
-        <v>528</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>426</v>
       </c>
       <c r="E10" t="s">
         <v>137</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B11">
         <v>4.05</v>
       </c>
       <c r="C11" t="s">
-        <v>528</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>426</v>
       </c>
       <c r="E11" t="s">
         <v>137</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B12">
         <v>3.78</v>
       </c>
       <c r="C12" t="s">
-        <v>528</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>426</v>
       </c>
       <c r="E12" t="s">
         <v>137</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B13">
         <v>3.62</v>
       </c>
       <c r="C13" t="s">
-        <v>528</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>426</v>
       </c>
       <c r="E13" t="s">
         <v>137</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B14">
         <v>332.407</v>
       </c>
       <c r="C14" t="s">
-        <v>528</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>426</v>
       </c>
       <c r="E14" t="s">
         <v>137</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B15">
         <v>130.902</v>
       </c>
       <c r="C15" t="s">
-        <v>528</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>426</v>
       </c>
       <c r="E15" t="s">
         <v>137</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B16">
         <v>4.3</v>
       </c>
       <c r="C16" t="s">
-        <v>528</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>426</v>
       </c>
       <c r="E16" t="s">
         <v>137</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>142</v>
       </c>
@@ -7063,19 +7154,22 @@
         <v>4.47</v>
       </c>
       <c r="C17" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>526</v>
       </c>
       <c r="E17" t="s">
         <v>137</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>143</v>
       </c>
@@ -7083,19 +7177,22 @@
         <v>0.04000000000000004</v>
       </c>
       <c r="C18" t="s">
-        <v>157</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>526</v>
       </c>
       <c r="E18" t="s">
         <v>137</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>144</v>
       </c>
@@ -7103,19 +7200,22 @@
         <v>-0.4199999999999999</v>
       </c>
       <c r="C19" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>526</v>
       </c>
       <c r="E19" t="s">
         <v>137</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>145</v>
       </c>
@@ -7123,19 +7223,22 @@
         <v>0.4199999999999999</v>
       </c>
       <c r="C20" t="s">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>526</v>
       </c>
       <c r="E20" t="s">
         <v>137</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>146</v>
       </c>
@@ -7143,19 +7246,22 @@
         <v>-0.07999999999999963</v>
       </c>
       <c r="C21" t="s">
-        <v>160</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>526</v>
       </c>
       <c r="E21" t="s">
         <v>137</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>147</v>
       </c>
@@ -7163,19 +7269,22 @@
         <v>0.00267003074209704</v>
       </c>
       <c r="C22" t="s">
-        <v>161</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>526</v>
       </c>
       <c r="E22" t="s">
         <v>137</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>148</v>
       </c>
@@ -7183,19 +7292,22 @@
         <v>0.008651438343614481</v>
       </c>
       <c r="C23" t="s">
-        <v>161</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>526</v>
       </c>
       <c r="E23" t="s">
         <v>137</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>149</v>
       </c>
@@ -7203,19 +7315,22 @@
         <v>0.006400377846336402</v>
       </c>
       <c r="C24" t="s">
-        <v>161</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>526</v>
       </c>
       <c r="E24" t="s">
         <v>137</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>150</v>
       </c>
@@ -7223,19 +7338,22 @@
         <v>0.006400377846336402</v>
       </c>
       <c r="C25" t="s">
-        <v>162</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>63</v>
+        <v>526</v>
       </c>
       <c r="E25" t="s">
         <v>137</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>151</v>
       </c>
@@ -7243,19 +7361,22 @@
         <v>0.004015441621060045</v>
       </c>
       <c r="C26" t="s">
-        <v>163</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>526</v>
       </c>
       <c r="E26" t="s">
         <v>137</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>152</v>
       </c>
@@ -7263,19 +7384,22 @@
         <v>0.006647621988882024</v>
       </c>
       <c r="C27" t="s">
-        <v>163</v>
+        <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>526</v>
       </c>
       <c r="E27" t="s">
         <v>137</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>153</v>
       </c>
@@ -7283,19 +7407,22 @@
         <v>0.003995981009502714</v>
       </c>
       <c r="C28" t="s">
-        <v>163</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s">
-        <v>63</v>
+        <v>526</v>
       </c>
       <c r="E28" t="s">
         <v>137</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
         <v>154</v>
       </c>
@@ -7303,19 +7430,22 @@
         <v>0.003995981009502714</v>
       </c>
       <c r="C29" t="s">
-        <v>164</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>526</v>
       </c>
       <c r="E29" t="s">
         <v>137</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
         <v>155</v>
       </c>
@@ -7323,39 +7453,48 @@
         <v>-0.1000000000000005</v>
       </c>
       <c r="C30" t="s">
-        <v>165</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>526</v>
       </c>
       <c r="E30" t="s">
         <v>137</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>529</v>
+        <v>466</v>
       </c>
       <c r="D31" t="s">
-        <v>465</v>
+        <v>429</v>
       </c>
       <c r="E31" t="s">
-        <v>542</v>
-      </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>434</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
         <v>393</v>
       </c>
@@ -7363,19 +7502,22 @@
         <v>28</v>
       </c>
       <c r="C32" t="s">
-        <v>530</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>431</v>
       </c>
       <c r="E32" t="s">
         <v>401</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
         <v>394</v>
       </c>
@@ -7383,19 +7525,22 @@
         <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>530</v>
+        <v>108</v>
       </c>
       <c r="D33" t="s">
-        <v>108</v>
+        <v>431</v>
       </c>
       <c r="E33" t="s">
         <v>401</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
         <v>395</v>
       </c>
@@ -7403,19 +7548,22 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="C34" t="s">
-        <v>530</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
-        <v>108</v>
+        <v>431</v>
       </c>
       <c r="E34" t="s">
         <v>401</v>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
         <v>396</v>
       </c>
@@ -7423,19 +7571,22 @@
         <v>0.5849056603773585</v>
       </c>
       <c r="C35" t="s">
-        <v>530</v>
+        <v>108</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>431</v>
       </c>
       <c r="E35" t="s">
         <v>401</v>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
         <v>397</v>
       </c>
@@ -7443,19 +7594,22 @@
         <v>0.6037735849056604</v>
       </c>
       <c r="C36" t="s">
-        <v>530</v>
+        <v>108</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>431</v>
       </c>
       <c r="E36" t="s">
         <v>401</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
         <v>398</v>
       </c>
@@ -7463,19 +7617,22 @@
         <v>0.660377358490566</v>
       </c>
       <c r="C37" t="s">
-        <v>530</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>431</v>
       </c>
       <c r="E37" t="s">
         <v>401</v>
       </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" t="s">
         <v>399</v>
       </c>
@@ -7483,19 +7640,22 @@
         <v>7</v>
       </c>
       <c r="C38" t="s">
-        <v>530</v>
+        <v>108</v>
       </c>
       <c r="D38" t="s">
-        <v>108</v>
+        <v>431</v>
       </c>
       <c r="E38" t="s">
         <v>401</v>
       </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
         <v>400</v>
       </c>
@@ -7503,800 +7663,998 @@
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>530</v>
+        <v>108</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
+        <v>431</v>
       </c>
       <c r="E39" t="s">
         <v>401</v>
       </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>531</v>
+        <v>466</v>
       </c>
       <c r="D40" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E40" t="s">
         <v>110</v>
       </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="D41" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E41" t="s">
         <v>110</v>
       </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42" t="s">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="D42" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E42" t="s">
         <v>110</v>
       </c>
-      <c r="F42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>534</v>
+        <v>466</v>
       </c>
       <c r="D43" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E43" t="s">
         <v>432</v>
       </c>
-      <c r="F43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="D44" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E44" t="s">
         <v>432</v>
       </c>
-      <c r="F44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45" t="s">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="D45" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E45" t="s">
         <v>432</v>
       </c>
-      <c r="F45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>534</v>
+        <v>466</v>
       </c>
       <c r="D46" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E46" t="s">
         <v>432</v>
       </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="D47" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E47" t="s">
         <v>432</v>
       </c>
-      <c r="F47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48" t="s">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="D48" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E48" t="s">
         <v>432</v>
       </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>534</v>
+        <v>466</v>
       </c>
       <c r="D49" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E49" t="s">
         <v>432</v>
       </c>
-      <c r="F49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="D50" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E50" t="s">
         <v>432</v>
       </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
       <c r="C51" t="s">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="D51" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E51" t="s">
         <v>432</v>
       </c>
-      <c r="F51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>534</v>
+        <v>466</v>
       </c>
       <c r="D52" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E52" t="s">
         <v>432</v>
       </c>
-      <c r="F52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="D53" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E53" t="s">
         <v>432</v>
       </c>
-      <c r="F53" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
       <c r="C54" t="s">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="D54" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E54" t="s">
         <v>432</v>
       </c>
-      <c r="F54" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>534</v>
+        <v>466</v>
       </c>
       <c r="D55" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E55" t="s">
         <v>432</v>
       </c>
-      <c r="F55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="D56" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E56" t="s">
         <v>432</v>
       </c>
-      <c r="F56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B57">
         <v>0</v>
       </c>
       <c r="C57" t="s">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="D57" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E57" t="s">
         <v>432</v>
       </c>
-      <c r="F57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B58">
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>534</v>
+        <v>466</v>
       </c>
       <c r="D58" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E58" t="s">
         <v>432</v>
       </c>
-      <c r="F58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="D59" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E59" t="s">
         <v>432</v>
       </c>
-      <c r="F59" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B60">
         <v>0</v>
       </c>
       <c r="C60" t="s">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="D60" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E60" t="s">
         <v>432</v>
       </c>
-      <c r="F60" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B61">
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>534</v>
+        <v>466</v>
       </c>
       <c r="D61" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E61" t="s">
         <v>432</v>
       </c>
-      <c r="F61" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="D62" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E62" t="s">
         <v>432</v>
       </c>
-      <c r="F62" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63" t="s">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="D63" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E63" t="s">
         <v>432</v>
       </c>
-      <c r="F63" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>535</v>
+        <v>466</v>
       </c>
       <c r="D64" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E64" t="s">
         <v>390</v>
       </c>
-      <c r="F64" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="D65" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E65" t="s">
         <v>390</v>
       </c>
-      <c r="F65" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66" t="s">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="D66" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E66" t="s">
         <v>390</v>
       </c>
-      <c r="F66" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B67">
         <v>0.9423076923076923</v>
       </c>
       <c r="C67" t="s">
-        <v>536</v>
+        <v>466</v>
       </c>
       <c r="D67" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E67" t="s">
         <v>433</v>
       </c>
-      <c r="F67" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="F67">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="B68">
         <v>0.9876091402011571</v>
       </c>
       <c r="C68" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="D68" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E68" t="s">
         <v>433</v>
       </c>
-      <c r="F68" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="F68">
+        <v>0.9876091402011571</v>
+      </c>
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
       <c r="C69" t="s">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="D69" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E69" t="s">
         <v>433</v>
       </c>
-      <c r="F69" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+      <c r="G69" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70" t="s">
-        <v>537</v>
+        <v>466</v>
       </c>
       <c r="D70" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E70" t="s">
         <v>434</v>
       </c>
-      <c r="F70" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
       <c r="C71" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="D71" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E71" t="s">
         <v>434</v>
       </c>
-      <c r="F71" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
       <c r="C72" t="s">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="D72" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E72" t="s">
         <v>434</v>
       </c>
-      <c r="F72" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C73" t="s">
-        <v>538</v>
+        <v>466</v>
       </c>
       <c r="D73" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E73" t="s">
         <v>435</v>
       </c>
-      <c r="F73" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="F73">
+        <v>0.9</v>
+      </c>
+      <c r="G73" t="b">
+        <v>0</v>
+      </c>
+      <c r="H73" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C74" t="s">
-        <v>539</v>
+        <v>466</v>
       </c>
       <c r="D74" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E74" t="s">
         <v>435</v>
       </c>
-      <c r="F74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+      <c r="F74">
+        <v>0.9</v>
+      </c>
+      <c r="G74" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75" t="s">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="D75" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E75" t="s">
         <v>435</v>
       </c>
-      <c r="F75" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="G75" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B76">
         <v>0.5408163265306123</v>
       </c>
       <c r="C76" t="s">
-        <v>540</v>
+        <v>466</v>
       </c>
       <c r="D76" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E76" t="s">
         <v>401</v>
       </c>
-      <c r="F76" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+      <c r="F76">
+        <v>0.5408163265306123</v>
+      </c>
+      <c r="G76" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B77">
         <v>0.4689190577470169</v>
       </c>
       <c r="C77" t="s">
-        <v>541</v>
+        <v>466</v>
       </c>
       <c r="D77" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E77" t="s">
         <v>401</v>
       </c>
-      <c r="F77" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="F77">
+        <v>0.4689190577470169</v>
+      </c>
+      <c r="G77" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78" t="s">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="D78" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="E78" t="s">
         <v>401</v>
       </c>
-      <c r="F78" t="b">
-        <v>0</v>
+      <c r="G78" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" t="s">
+        <v>541</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F78"/>
+  <autoFilter ref="A1:H78"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8314,7 +8672,7 @@
         <v>408</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -8331,7 +8689,7 @@
         <v>110</v>
       </c>
       <c r="B2" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="C2" t="s">
         <v>109</v>
@@ -8340,7 +8698,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -8348,7 +8706,7 @@
         <v>432</v>
       </c>
       <c r="B3" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="C3" t="s">
         <v>123</v>
@@ -8357,7 +8715,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8365,7 +8723,7 @@
         <v>432</v>
       </c>
       <c r="B4" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="C4" t="s">
         <v>124</v>
@@ -8374,7 +8732,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8382,7 +8740,7 @@
         <v>432</v>
       </c>
       <c r="B5" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="C5" t="s">
         <v>125</v>
@@ -8391,7 +8749,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8399,7 +8757,7 @@
         <v>432</v>
       </c>
       <c r="B6" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="C6" t="s">
         <v>126</v>
@@ -8408,7 +8766,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8416,7 +8774,7 @@
         <v>432</v>
       </c>
       <c r="B7" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="C7" t="s">
         <v>127</v>
@@ -8425,7 +8783,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8433,7 +8791,7 @@
         <v>432</v>
       </c>
       <c r="B8" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="C8" t="s">
         <v>128</v>
@@ -8442,7 +8800,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8450,7 +8808,7 @@
         <v>432</v>
       </c>
       <c r="B9" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="C9" t="s">
         <v>129</v>
@@ -8459,7 +8817,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8476,7 +8834,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8484,33 +8842,33 @@
         <v>434</v>
       </c>
       <c r="B11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="B12" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="C12" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>548</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -14260,23 +14618,8 @@
       <c r="C10">
         <v>0.03183849</v>
       </c>
-      <c r="D10">
-        <v>365.76001</v>
-      </c>
-      <c r="E10">
-        <v>-3.50998</v>
-      </c>
-      <c r="F10">
-        <v>-0.95051842</v>
-      </c>
-      <c r="J10" t="s">
-        <v>410</v>
-      </c>
-      <c r="K10">
-        <v>1780666200</v>
-      </c>
       <c r="L10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -14289,23 +14632,8 @@
       <c r="C11">
         <v>0.0314861</v>
       </c>
-      <c r="D11">
-        <v>385.73001</v>
-      </c>
-      <c r="E11">
-        <v>-33.17999</v>
-      </c>
-      <c r="F11">
-        <v>-7.92055</v>
-      </c>
-      <c r="J11" t="s">
-        <v>410</v>
-      </c>
-      <c r="K11">
-        <v>1780666200</v>
-      </c>
       <c r="L11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -14703,7 +15031,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -14741,7 +15069,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -14779,7 +15107,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -14817,7 +15145,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -14855,7 +15183,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -14893,7 +15221,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -14931,7 +15259,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -14969,7 +15297,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -15007,7 +15335,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -15048,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -15089,7 +15417,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -15106,10 +15434,16 @@
         <v>20</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0.9</v>
+      </c>
+      <c r="G13" t="s">
+        <v>438</v>
+      </c>
+      <c r="H13" t="s">
+        <v>438</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -15130,7 +15464,7 @@
         <v>410</v>
       </c>
       <c r="O13" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -15153,10 +15487,10 @@
         <v>0.4689190577470169</v>
       </c>
       <c r="G14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -15174,10 +15508,10 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/nasdaq100_qqq_daily_tracker.xlsx
+++ b/reports/latest/nasdaq100_qqq_daily_tracker.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3108" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3110" uniqueCount="742">
   <si>
     <t>date</t>
   </si>
@@ -1936,7 +1936,7 @@
     <t>20/20 top20 quotes available; 10/10 top10 quotes available</t>
   </si>
   <si>
-    <t>98/98 symbols with history coverage; 20/98 history symbols with Twelve Data quote overlay</t>
+    <t>97/98 symbols with history coverage; 19/97 history symbols with Twelve Data quote overlay; coverage insufficient for top-weight symbols</t>
   </si>
   <si>
     <t>run_date</t>
@@ -2194,7 +2194,7 @@
     <t>latest FRED observation value</t>
   </si>
   <si>
-    <t>breadth metric; denominator=98</t>
+    <t>breadth metric; denominator=97</t>
   </si>
   <si>
     <t>symbol coverage; ok=True; rows=260; message=QQQ cache ready</t>
@@ -2242,7 +2242,7 @@
     <t>weight coverage; rate_limited=False; fallback_provider=quote_cache</t>
   </si>
   <si>
-    <t>symbol coverage; ok=True; rows=8; message=98/98 symbols with history coverage; 20/98 history symbols with Twelve Data quote overlay</t>
+    <t>symbol coverage; ok=True; rows=8; message=97/98 symbols with history coverage; 19/97 history symbols with Twelve Data quote overlay; coverage insufficient for top-weight symbols</t>
   </si>
   <si>
     <t>weight coverage; rate_limited=False; fallback_provider=twelve_data_quote</t>
@@ -2266,7 +2266,7 @@
     <t>98 symbols</t>
   </si>
   <si>
-    <t>98/98 symbols loaded from local cache/raw seed</t>
+    <t>97/98 symbols loaded from local cache/raw seed</t>
   </si>
 </sst>
 </file>
@@ -7825,13 +7825,13 @@
         <v>609.65</v>
       </c>
       <c r="G179">
-        <v>608.8911435241999</v>
+        <v>609.65</v>
       </c>
       <c r="H179" s="1">
         <v>78019338</v>
       </c>
       <c r="I179" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -9252,7 +9252,7 @@
         <v>37138511</v>
       </c>
       <c r="I228" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="229" spans="1:9">
@@ -9774,7 +9774,7 @@
         <v>33327545</v>
       </c>
       <c r="I246" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="247" spans="1:9">
@@ -10771,10 +10771,16 @@
         <v>8</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0.9897959183673469</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0.9146145309607144</v>
+      </c>
+      <c r="G13" t="s">
+        <v>333</v>
+      </c>
+      <c r="H13" t="s">
+        <v>333</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -10786,7 +10792,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>28168</v>
+        <v>27880</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -10795,10 +10801,10 @@
         <v>618</v>
       </c>
       <c r="O13">
-        <v>1</v>
+        <v>0.9897959183673469</v>
       </c>
       <c r="P13">
-        <v>0.2040816326530612</v>
+        <v>0.1958762886597938</v>
       </c>
       <c r="T13" t="s">
         <v>577</v>
@@ -11496,7 +11502,7 @@
         <v>680</v>
       </c>
       <c r="B9">
-        <v>621.0349008439025</v>
+        <v>621.0386951262815</v>
       </c>
       <c r="C9" t="s">
         <v>268</v>
@@ -12025,7 +12031,7 @@
         <v>556</v>
       </c>
       <c r="B32">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
         <v>268</v>
@@ -12048,7 +12054,7 @@
         <v>557</v>
       </c>
       <c r="B33">
-        <v>0.4285714285714285</v>
+        <v>0.4329896907216495</v>
       </c>
       <c r="C33" t="s">
         <v>268</v>
@@ -12071,7 +12077,7 @@
         <v>558</v>
       </c>
       <c r="B34">
-        <v>0.5306122448979592</v>
+        <v>0.5360824742268041</v>
       </c>
       <c r="C34" t="s">
         <v>268</v>
@@ -12094,7 +12100,7 @@
         <v>559</v>
       </c>
       <c r="B35">
-        <v>0.5714285714285714</v>
+        <v>0.5670103092783505</v>
       </c>
       <c r="C35" t="s">
         <v>268</v>
@@ -12117,7 +12123,7 @@
         <v>560</v>
       </c>
       <c r="B36">
-        <v>0.5918367346938775</v>
+        <v>0.5876288659793815</v>
       </c>
       <c r="C36" t="s">
         <v>268</v>
@@ -12163,7 +12169,7 @@
         <v>562</v>
       </c>
       <c r="B38">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
         <v>268</v>
@@ -13011,7 +13017,7 @@
         <v>702</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>0.9897959183673469</v>
       </c>
       <c r="C72" t="s">
         <v>648</v>
@@ -13023,7 +13029,7 @@
         <v>563</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>0.9897959183673469</v>
       </c>
       <c r="G72" t="b">
         <v>0</v>
@@ -13037,7 +13043,7 @@
         <v>703</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>0.9146145309607144</v>
       </c>
       <c r="C73" t="s">
         <v>648</v>
@@ -13049,7 +13055,7 @@
         <v>563</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>0.9146145309607144</v>
       </c>
       <c r="G73" t="b">
         <v>0</v>
@@ -13369,7 +13375,7 @@
         <v>667.8092</v>
       </c>
       <c r="K2">
-        <v>621.0349008439025</v>
+        <v>621.0386951262815</v>
       </c>
     </row>
   </sheetData>
@@ -18580,7 +18586,7 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
         <v>268</v>
@@ -18597,10 +18603,10 @@
         <v>556</v>
       </c>
       <c r="B3">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
         <v>268</v>
@@ -18617,10 +18623,10 @@
         <v>557</v>
       </c>
       <c r="B4">
-        <v>0.4285714285714285</v>
+        <v>0.4329896907216495</v>
       </c>
       <c r="C4">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
         <v>268</v>
@@ -18637,10 +18643,10 @@
         <v>558</v>
       </c>
       <c r="B5">
-        <v>0.5306122448979592</v>
+        <v>0.5360824742268041</v>
       </c>
       <c r="C5">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
         <v>268</v>
@@ -18657,10 +18663,10 @@
         <v>559</v>
       </c>
       <c r="B6">
-        <v>0.5714285714285714</v>
+        <v>0.5670103092783505</v>
       </c>
       <c r="C6">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
         <v>268</v>
@@ -18677,10 +18683,10 @@
         <v>560</v>
       </c>
       <c r="B7">
-        <v>0.5918367346938775</v>
+        <v>0.5876288659793815</v>
       </c>
       <c r="C7">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
         <v>268</v>
@@ -18700,7 +18706,7 @@
         <v>9</v>
       </c>
       <c r="C8">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
         <v>268</v>
@@ -18717,10 +18723,10 @@
         <v>562</v>
       </c>
       <c r="B9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
         <v>268</v>

--- a/reports/latest/nasdaq100_qqq_daily_tracker.xlsx
+++ b/reports/latest/nasdaq100_qqq_daily_tracker.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3090" uniqueCount="740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3088" uniqueCount="740">
   <si>
     <t>date</t>
   </si>
@@ -1939,7 +1939,7 @@
     <t>20/20 top20 quotes available; 10/10 top10 quotes available</t>
   </si>
   <si>
-    <t>97/98 symbols with history coverage; 19/97 history symbols with Twelve Data quote overlay; coverage insufficient for top-weight symbols</t>
+    <t>98/98 symbols with history coverage; 20/98 history symbols with Twelve Data quote overlay</t>
   </si>
   <si>
     <t>run_date</t>
@@ -2188,7 +2188,7 @@
     <t>latest FRED observation value</t>
   </si>
   <si>
-    <t>breadth metric; denominator=97</t>
+    <t>breadth metric; denominator=98</t>
   </si>
   <si>
     <t>symbol coverage; ok=True; rows=260; message=QQQ cache ready</t>
@@ -2236,7 +2236,7 @@
     <t>weight coverage; rate_limited=False; fallback_provider=quote_cache</t>
   </si>
   <si>
-    <t>symbol coverage; ok=True; rows=8; message=97/98 symbols with history coverage; 19/97 history symbols with Twelve Data quote overlay; coverage insufficient for top-weight symbols</t>
+    <t>symbol coverage; ok=True; rows=8; message=98/98 symbols with history coverage; 20/98 history symbols with Twelve Data quote overlay</t>
   </si>
   <si>
     <t>weight coverage; rate_limited=False; fallback_provider=twelve_data_quote</t>
@@ -2260,7 +2260,7 @@
     <t>98 symbols</t>
   </si>
   <si>
-    <t>97/98 symbols loaded from local cache/raw seed</t>
+    <t>98/98 symbols loaded from local cache/raw seed</t>
   </si>
 </sst>
 </file>
@@ -10765,16 +10765,10 @@
         <v>8</v>
       </c>
       <c r="E13">
-        <v>0.9897959183673469</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>0.9159165601145549</v>
-      </c>
-      <c r="G13" t="s">
-        <v>334</v>
-      </c>
-      <c r="H13" t="s">
-        <v>334</v>
+        <v>1</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -10786,7 +10780,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>27880</v>
+        <v>28168</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -10795,10 +10789,10 @@
         <v>619</v>
       </c>
       <c r="O13">
-        <v>0.9897959183673469</v>
+        <v>1</v>
       </c>
       <c r="P13">
-        <v>0.1958762886597938</v>
+        <v>0.2040816326530612</v>
       </c>
       <c r="T13" t="s">
         <v>578</v>
@@ -12028,7 +12022,7 @@
         <v>557</v>
       </c>
       <c r="B32">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
         <v>268</v>
@@ -12051,7 +12045,7 @@
         <v>558</v>
       </c>
       <c r="B33">
-        <v>0.4329896907216495</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="C33" t="s">
         <v>268</v>
@@ -12074,7 +12068,7 @@
         <v>559</v>
       </c>
       <c r="B34">
-        <v>0.5360824742268041</v>
+        <v>0.5306122448979592</v>
       </c>
       <c r="C34" t="s">
         <v>268</v>
@@ -12097,7 +12091,7 @@
         <v>560</v>
       </c>
       <c r="B35">
-        <v>0.5670103092783505</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="C35" t="s">
         <v>268</v>
@@ -12120,7 +12114,7 @@
         <v>561</v>
       </c>
       <c r="B36">
-        <v>0.5876288659793815</v>
+        <v>0.5918367346938775</v>
       </c>
       <c r="C36" t="s">
         <v>268</v>
@@ -12166,7 +12160,7 @@
         <v>563</v>
       </c>
       <c r="B38">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
         <v>268</v>
@@ -13014,7 +13008,7 @@
         <v>700</v>
       </c>
       <c r="B72">
-        <v>0.9897959183673469</v>
+        <v>1</v>
       </c>
       <c r="C72" t="s">
         <v>333</v>
@@ -13026,7 +13020,7 @@
         <v>564</v>
       </c>
       <c r="F72">
-        <v>0.9897959183673469</v>
+        <v>1</v>
       </c>
       <c r="G72" t="b">
         <v>0</v>
@@ -13040,7 +13034,7 @@
         <v>701</v>
       </c>
       <c r="B73">
-        <v>0.9159165601145549</v>
+        <v>1</v>
       </c>
       <c r="C73" t="s">
         <v>333</v>
@@ -13052,7 +13046,7 @@
         <v>564</v>
       </c>
       <c r="F73">
-        <v>0.9159165601145549</v>
+        <v>1</v>
       </c>
       <c r="G73" t="b">
         <v>0</v>
@@ -18583,7 +18577,7 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
         <v>268</v>
@@ -18600,10 +18594,10 @@
         <v>557</v>
       </c>
       <c r="B3">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
         <v>268</v>
@@ -18620,10 +18614,10 @@
         <v>558</v>
       </c>
       <c r="B4">
-        <v>0.4329896907216495</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="C4">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
         <v>268</v>
@@ -18640,10 +18634,10 @@
         <v>559</v>
       </c>
       <c r="B5">
-        <v>0.5360824742268041</v>
+        <v>0.5306122448979592</v>
       </c>
       <c r="C5">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
         <v>268</v>
@@ -18660,10 +18654,10 @@
         <v>560</v>
       </c>
       <c r="B6">
-        <v>0.5670103092783505</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="C6">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
         <v>268</v>
@@ -18680,10 +18674,10 @@
         <v>561</v>
       </c>
       <c r="B7">
-        <v>0.5876288659793815</v>
+        <v>0.5918367346938775</v>
       </c>
       <c r="C7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
         <v>268</v>
@@ -18703,7 +18697,7 @@
         <v>9</v>
       </c>
       <c r="C8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
         <v>268</v>
@@ -18720,10 +18714,10 @@
         <v>563</v>
       </c>
       <c r="B9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
         <v>268</v>

--- a/reports/latest/nasdaq100_qqq_daily_tracker.xlsx
+++ b/reports/latest/nasdaq100_qqq_daily_tracker.xlsx
@@ -1939,7 +1939,7 @@
     <t>20/20 top20 quotes available; 10/10 top10 quotes available</t>
   </si>
   <si>
-    <t>98/98 symbols with history coverage; 20/98 history symbols with Twelve Data quote overlay; target_date=2026-06-05; target_aligned=88/98; non_target_aligned=10/98; min_latest_date=2026-06-04; max_latest_date=2026-06-05; target_date_source=current price_daily</t>
+    <t>98/98 symbols with history coverage; 20/98 history symbols with Twelve Data quote overlay; target_date=2026-06-05; target_aligned=98/98; non_target_aligned=0/98; min_latest_date=2026-06-05; max_latest_date=2026-06-05; target_date_source=current price_daily</t>
   </si>
   <si>
     <t>run_date</t>
@@ -2239,7 +2239,7 @@
     <t>weight coverage; rate_limited=False; fallback_provider=quote_cache</t>
   </si>
   <si>
-    <t>symbol coverage; ok=True; rows=8; message=98/98 symbols with history coverage; 20/98 history symbols with Twelve Data quote overlay; target_date=2026-06-05; target_aligned=88/98; non_target_aligned=10/98; min_latest_date=2026-06-04; max_latest_date=2026-06-05; target_date_source=current price_daily</t>
+    <t>symbol coverage; ok=True; rows=8; message=98/98 symbols with history coverage; 20/98 history symbols with Twelve Data quote overlay; target_date=2026-06-05; target_aligned=98/98; non_target_aligned=0/98; min_latest_date=2026-06-05; max_latest_date=2026-06-05; target_date_source=current price_daily</t>
   </si>
   <si>
     <t>weight coverage; rate_limited=False; fallback_provider=twelve_data_quote</t>
@@ -10783,7 +10783,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>28208</v>
+        <v>28218</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -12002,7 +12002,7 @@
         <v>556</v>
       </c>
       <c r="B31">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
         <v>268</v>
@@ -12025,7 +12025,7 @@
         <v>557</v>
       </c>
       <c r="B32">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s">
         <v>268</v>
@@ -12048,7 +12048,7 @@
         <v>558</v>
       </c>
       <c r="B33">
-        <v>0.3673469387755102</v>
+        <v>0.3265306122448979</v>
       </c>
       <c r="C33" t="s">
         <v>268</v>
@@ -12071,7 +12071,7 @@
         <v>559</v>
       </c>
       <c r="B34">
-        <v>0.5102040816326531</v>
+        <v>0.4897959183673469</v>
       </c>
       <c r="C34" t="s">
         <v>268</v>
@@ -12094,7 +12094,7 @@
         <v>560</v>
       </c>
       <c r="B35">
-        <v>0.5204081632653061</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="C35" t="s">
         <v>268</v>
@@ -12117,7 +12117,7 @@
         <v>561</v>
       </c>
       <c r="B36">
-        <v>0.5816326530612245</v>
+        <v>0.5918367346938775</v>
       </c>
       <c r="C36" t="s">
         <v>268</v>
@@ -12140,7 +12140,7 @@
         <v>562</v>
       </c>
       <c r="B37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C37" t="s">
         <v>268</v>
@@ -12163,7 +12163,7 @@
         <v>563</v>
       </c>
       <c r="B38">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
         <v>268</v>
@@ -18577,7 +18577,7 @@
         <v>556</v>
       </c>
       <c r="B2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>98</v>
@@ -18597,7 +18597,7 @@
         <v>557</v>
       </c>
       <c r="B3">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C3">
         <v>98</v>
@@ -18617,7 +18617,7 @@
         <v>558</v>
       </c>
       <c r="B4">
-        <v>0.3673469387755102</v>
+        <v>0.3265306122448979</v>
       </c>
       <c r="C4">
         <v>98</v>
@@ -18637,7 +18637,7 @@
         <v>559</v>
       </c>
       <c r="B5">
-        <v>0.5102040816326531</v>
+        <v>0.4897959183673469</v>
       </c>
       <c r="C5">
         <v>98</v>
@@ -18657,7 +18657,7 @@
         <v>560</v>
       </c>
       <c r="B6">
-        <v>0.5204081632653061</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="C6">
         <v>98</v>
@@ -18677,7 +18677,7 @@
         <v>561</v>
       </c>
       <c r="B7">
-        <v>0.5816326530612245</v>
+        <v>0.5918367346938775</v>
       </c>
       <c r="C7">
         <v>98</v>
@@ -18697,7 +18697,7 @@
         <v>562</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>98</v>
@@ -18717,7 +18717,7 @@
         <v>563</v>
       </c>
       <c r="B9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9">
         <v>98</v>
